--- a/flask_backend/test_output/ie_import_comparison.xlsx
+++ b/flask_backend/test_output/ie_import_comparison.xlsx
@@ -537,13 +537,13 @@
         <v>288.1766</v>
       </c>
       <c r="G2" t="n">
-        <v>596.319</v>
+        <v>1159.3051</v>
       </c>
       <c r="J2" t="n">
-        <v>913.4124</v>
+        <v>932.1124</v>
       </c>
       <c r="M2" t="n">
-        <v>385.64</v>
+        <v>416.44</v>
       </c>
     </row>
     <row r="3">
@@ -561,19 +561,19 @@
         <v>96.39</v>
       </c>
       <c r="D3" t="n">
-        <v>220.7822</v>
+        <v>311.9294</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>124.3922</v>
+        <v>215.5394</v>
       </c>
       <c r="F3" t="n">
         <v>96.39</v>
       </c>
       <c r="G3" t="n">
-        <v>1143.4</v>
+        <v>1624.98</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1047.01</v>
+        <v>1528.59</v>
       </c>
       <c r="I3" t="n">
         <v>66.59999999999999</v>
@@ -588,10 +588,10 @@
         <v>26.82</v>
       </c>
       <c r="M3" t="n">
-        <v>366.74</v>
+        <v>438.24</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>339.92</v>
+        <v>411.42</v>
       </c>
     </row>
     <row r="4">
@@ -606,16 +606,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>333.1822</v>
+        <v>501.1822</v>
       </c>
       <c r="G4" t="n">
-        <v>797.6313</v>
+        <v>1394.3923</v>
       </c>
       <c r="J4" t="n">
-        <v>926.1295</v>
+        <v>946.4795</v>
       </c>
       <c r="M4" t="n">
-        <v>442.64</v>
+        <v>491.04</v>
       </c>
     </row>
     <row r="5">
@@ -975,19 +975,19 @@
         <v>85.09999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>1246.96</v>
+        <v>1264.56</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1161.86</v>
+        <v>1179.46</v>
       </c>
       <c r="L12" t="n">
         <v>9.9</v>
       </c>
       <c r="M12" t="n">
-        <v>122.1</v>
+        <v>138.05</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>112.2</v>
+        <v>128.15</v>
       </c>
     </row>
     <row r="13">
@@ -1023,19 +1023,19 @@
         <v>85.09999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>1246.96</v>
+        <v>1264.56</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1161.86</v>
+        <v>1179.46</v>
       </c>
       <c r="L13" t="n">
         <v>9.9</v>
       </c>
       <c r="M13" t="n">
-        <v>122.1</v>
+        <v>138.05</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>112.2</v>
+        <v>128.15</v>
       </c>
     </row>
     <row r="14">
@@ -1071,19 +1071,19 @@
         <v>48.9</v>
       </c>
       <c r="J14" t="n">
-        <v>1062.05</v>
+        <v>1081.63</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1013.15</v>
+        <v>1032.73</v>
       </c>
       <c r="L14" t="n">
         <v>48.37</v>
       </c>
       <c r="M14" t="n">
-        <v>721.875</v>
+        <v>752.675</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>673.505</v>
+        <v>704.3049999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1125,10 +1125,10 @@
         <v>1577.42</v>
       </c>
       <c r="J16" t="n">
-        <v>1068.98</v>
+        <v>1088.56</v>
       </c>
       <c r="M16" t="n">
-        <v>721.875</v>
+        <v>752.675</v>
       </c>
     </row>
     <row r="17">
@@ -1149,10 +1149,10 @@
         <v>1584.57</v>
       </c>
       <c r="J17" t="n">
-        <v>979.55</v>
+        <v>999.13</v>
       </c>
       <c r="M17" t="n">
-        <v>739.255</v>
+        <v>770.0549999999999</v>
       </c>
     </row>
     <row r="18">
@@ -1239,7 +1239,7 @@
         <v>1606.7771</v>
       </c>
       <c r="M20" t="n">
-        <v>384.56</v>
+        <v>456.94</v>
       </c>
     </row>
     <row r="21">
@@ -1257,10 +1257,10 @@
         <v>179.74</v>
       </c>
       <c r="D21" t="n">
-        <v>156.1234</v>
+        <v>177.6722</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-23.6166</v>
+        <v>-2.0678</v>
       </c>
       <c r="F21" t="n">
         <v>179.74</v>
@@ -1284,10 +1284,10 @@
         <v>24</v>
       </c>
       <c r="M21" t="n">
-        <v>195.58</v>
+        <v>245.916</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>171.58</v>
+        <v>221.916</v>
       </c>
     </row>
     <row r="22">
@@ -1305,10 +1305,10 @@
         <v>99.09</v>
       </c>
       <c r="D22" t="n">
-        <v>210.2827</v>
+        <v>343.9368</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>111.1927</v>
+        <v>244.8468</v>
       </c>
       <c r="F22" t="n">
         <v>99.09</v>
@@ -1332,10 +1332,10 @@
         <v>18.18</v>
       </c>
       <c r="M22" t="n">
-        <v>292.93</v>
+        <v>328.13</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>274.75</v>
+        <v>309.95</v>
       </c>
     </row>
     <row r="23">
@@ -1743,10 +1743,10 @@
         <v>96.02</v>
       </c>
       <c r="D32" t="n">
-        <v>6815.9123</v>
+        <v>6864.1683</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>6719.8923</v>
+        <v>6768.1483</v>
       </c>
       <c r="F32" t="n">
         <v>286</v>
@@ -1875,10 +1875,10 @@
         <v>97.23999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>7073.121</v>
+        <v>7246.753</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>6975.881</v>
+        <v>7149.513</v>
       </c>
       <c r="F35" t="n">
         <v>286</v>
@@ -1917,10 +1917,10 @@
         <v>93.16</v>
       </c>
       <c r="D36" t="n">
-        <v>7222.7638</v>
+        <v>7396.3958</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>7129.6038</v>
+        <v>7303.2358</v>
       </c>
       <c r="F36" t="n">
         <v>286</v>
@@ -1959,10 +1959,10 @@
         <v>93.16</v>
       </c>
       <c r="D37" t="n">
-        <v>7182.7638</v>
+        <v>7356.3958</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>7089.6038</v>
+        <v>7263.2358</v>
       </c>
       <c r="F37" t="n">
         <v>286</v>
@@ -2085,10 +2085,10 @@
         <v>96.16</v>
       </c>
       <c r="D40" t="n">
-        <v>7076.6778</v>
+        <v>7214.9818</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>6980.5178</v>
+        <v>7118.8218</v>
       </c>
       <c r="F40" t="n">
         <v>286</v>
@@ -2148,10 +2148,10 @@
         <v>104.41</v>
       </c>
       <c r="D42" t="n">
-        <v>376.0857</v>
+        <v>491.8817</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>271.6757</v>
+        <v>387.4717</v>
       </c>
       <c r="F42" t="n">
         <v>247.72</v>
@@ -2175,10 +2175,10 @@
         <v>28.67</v>
       </c>
       <c r="M42" t="n">
-        <v>540.5767</v>
+        <v>554.6567</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>511.9067</v>
+        <v>525.9867</v>
       </c>
     </row>
     <row r="43">
@@ -2205,10 +2205,10 @@
         <v>108.46</v>
       </c>
       <c r="G43" t="n">
-        <v>576.26</v>
+        <v>937.08</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>467.8</v>
+        <v>828.62</v>
       </c>
       <c r="I43" t="n">
         <v>47.9</v>
@@ -2241,16 +2241,16 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>338.5638</v>
+        <v>434.5638</v>
       </c>
       <c r="G44" t="n">
-        <v>797.6313</v>
+        <v>1394.3923</v>
       </c>
       <c r="J44" t="n">
-        <v>926.1295</v>
+        <v>946.4795</v>
       </c>
       <c r="M44" t="n">
-        <v>442.64</v>
+        <v>491.04</v>
       </c>
     </row>
     <row r="45">
@@ -2265,16 +2265,16 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>338.7992</v>
+        <v>434.7992</v>
       </c>
       <c r="G45" t="n">
-        <v>811.0977</v>
+        <v>1455.1147</v>
       </c>
       <c r="J45" t="n">
-        <v>926.1295</v>
+        <v>946.4795</v>
       </c>
       <c r="M45" t="n">
-        <v>442.64</v>
+        <v>491.04</v>
       </c>
     </row>
     <row r="46">
@@ -2289,16 +2289,16 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>220.653</v>
+        <v>352.653</v>
       </c>
       <c r="G46" t="n">
-        <v>893.5676999999999</v>
+        <v>1657.7487</v>
       </c>
       <c r="J46" t="n">
-        <v>926.1295</v>
+        <v>946.4795</v>
       </c>
       <c r="M46" t="n">
-        <v>442.64</v>
+        <v>491.04</v>
       </c>
     </row>
     <row r="47">
@@ -2313,16 +2313,16 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>359.0617</v>
+        <v>455.0617</v>
       </c>
       <c r="G47" t="n">
-        <v>811.0676999999999</v>
+        <v>1455.0847</v>
       </c>
       <c r="J47" t="n">
-        <v>926.1295</v>
+        <v>946.4795</v>
       </c>
       <c r="M47" t="n">
-        <v>442.64</v>
+        <v>491.04</v>
       </c>
     </row>
     <row r="48">
@@ -2454,19 +2454,19 @@
         <v>61.12</v>
       </c>
       <c r="J50" t="n">
-        <v>1179.75</v>
+        <v>1199.55</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>1118.63</v>
+        <v>1138.43</v>
       </c>
       <c r="L50" t="n">
         <v>32.32</v>
       </c>
       <c r="M50" t="n">
-        <v>508.64</v>
+        <v>539.4400000000001</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>476.32</v>
+        <v>507.12</v>
       </c>
     </row>
     <row r="51">
@@ -2502,19 +2502,19 @@
         <v>58.1</v>
       </c>
       <c r="J51" t="n">
-        <v>1137.95</v>
+        <v>1157.75</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>1079.85</v>
+        <v>1099.65</v>
       </c>
       <c r="L51" t="n">
         <v>32.32</v>
       </c>
       <c r="M51" t="n">
-        <v>490.82</v>
+        <v>521.62</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>458.5</v>
+        <v>489.3</v>
       </c>
     </row>
     <row r="52">
@@ -2532,13 +2532,13 @@
         <v>450.5075</v>
       </c>
       <c r="G52" t="n">
-        <v>514.3264</v>
+        <v>1455.7614</v>
       </c>
       <c r="J52" t="n">
         <v>850.9593</v>
       </c>
       <c r="M52" t="n">
-        <v>384.56</v>
+        <v>456.94</v>
       </c>
     </row>
     <row r="53">
@@ -2556,13 +2556,13 @@
         <v>402.2575</v>
       </c>
       <c r="G53" t="n">
-        <v>392.8367</v>
+        <v>1146.2817</v>
       </c>
       <c r="J53" t="n">
         <v>952.1043</v>
       </c>
       <c r="M53" t="n">
-        <v>384.56</v>
+        <v>456.94</v>
       </c>
     </row>
     <row r="54">
@@ -2838,10 +2838,10 @@
         <v>70.52</v>
       </c>
       <c r="G60" t="n">
-        <v>469.59</v>
+        <v>857.89</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>399.07</v>
+        <v>787.37</v>
       </c>
       <c r="I60" t="n">
         <v>51.1</v>
@@ -2856,10 +2856,10 @@
         <v>20.88</v>
       </c>
       <c r="M60" t="n">
-        <v>307.34</v>
+        <v>363</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>286.46</v>
+        <v>342.12</v>
       </c>
     </row>
     <row r="61">
@@ -2877,19 +2877,19 @@
         <v>69.13</v>
       </c>
       <c r="D61" t="n">
-        <v>270.8654</v>
+        <v>330.8654</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>201.7354</v>
+        <v>261.7354</v>
       </c>
       <c r="F61" t="n">
         <v>69.13</v>
       </c>
       <c r="G61" t="n">
-        <v>469.5533</v>
+        <v>805.2732999999999</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>400.4233</v>
+        <v>736.1433</v>
       </c>
       <c r="I61" t="n">
         <v>51.1</v>
@@ -2904,10 +2904,10 @@
         <v>17.96</v>
       </c>
       <c r="M61" t="n">
-        <v>307.34</v>
+        <v>363</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>289.38</v>
+        <v>345.04</v>
       </c>
     </row>
     <row r="62">
@@ -2925,10 +2925,10 @@
         <v>104.41</v>
       </c>
       <c r="D62" t="n">
-        <v>346.4794</v>
+        <v>462.2874</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>242.0694</v>
+        <v>357.8774</v>
       </c>
       <c r="F62" t="n">
         <v>247.72</v>
@@ -2952,10 +2952,10 @@
         <v>28.67</v>
       </c>
       <c r="M62" t="n">
-        <v>540.5767</v>
+        <v>554.6567</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>511.9067</v>
+        <v>525.9867</v>
       </c>
     </row>
     <row r="63">
@@ -2973,10 +2973,10 @@
         <v>99.81</v>
       </c>
       <c r="D63" t="n">
-        <v>324.2442</v>
+        <v>440.0522</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>224.4342</v>
+        <v>340.2422</v>
       </c>
       <c r="F63" t="n">
         <v>247.72</v>
@@ -3000,10 +3000,10 @@
         <v>28.67</v>
       </c>
       <c r="M63" t="n">
-        <v>540.5767</v>
+        <v>554.6567</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>511.9067</v>
+        <v>525.9867</v>
       </c>
     </row>
     <row r="64">
@@ -3018,7 +3018,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>167.6339</v>
+        <v>227.6339</v>
       </c>
       <c r="G64" t="n">
         <v>939.917</v>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>177.231</v>
+        <v>261.231</v>
       </c>
       <c r="G65" t="n">
-        <v>851.72</v>
+        <v>1646.91</v>
       </c>
       <c r="J65" t="n">
         <v>1076.68</v>
@@ -3069,7 +3069,7 @@
         <v>274.6938</v>
       </c>
       <c r="G66" t="n">
-        <v>634.53</v>
+        <v>1309.6</v>
       </c>
       <c r="J66" t="n">
         <v>871.42</v>
@@ -3093,19 +3093,19 @@
         <v>89.44</v>
       </c>
       <c r="D67" t="n">
-        <v>164.5673</v>
+        <v>255.7145</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>75.12730000000001</v>
+        <v>166.2745</v>
       </c>
       <c r="F67" t="n">
         <v>89.44</v>
       </c>
       <c r="G67" t="n">
-        <v>1143.4</v>
+        <v>1541.38</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>1053.96</v>
+        <v>1451.94</v>
       </c>
       <c r="I67" t="n">
         <v>66.59999999999999</v>
@@ -3120,10 +3120,10 @@
         <v>26.82</v>
       </c>
       <c r="M67" t="n">
-        <v>366.74</v>
+        <v>438.24</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>339.92</v>
+        <v>411.42</v>
       </c>
     </row>
     <row r="68">
@@ -3141,19 +3141,19 @@
         <v>93.40000000000001</v>
       </c>
       <c r="D68" t="n">
-        <v>180.7798</v>
+        <v>252.7798</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>87.3798</v>
+        <v>159.3798</v>
       </c>
       <c r="F68" t="n">
         <v>102.52</v>
       </c>
       <c r="G68" t="n">
-        <v>798.6799999999999</v>
+        <v>1507.52</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>696.16</v>
+        <v>1405</v>
       </c>
       <c r="I68" t="n">
         <v>49.4</v>
@@ -3207,19 +3207,19 @@
         <v>90.09999999999999</v>
       </c>
       <c r="J69" t="n">
-        <v>1565.52</v>
+        <v>1583.12</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>1475.42</v>
+        <v>1493.02</v>
       </c>
       <c r="L69" t="n">
         <v>9.9</v>
       </c>
       <c r="M69" t="n">
-        <v>145.42</v>
+        <v>161.37</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>135.52</v>
+        <v>151.47</v>
       </c>
     </row>
     <row r="70">
@@ -3255,19 +3255,19 @@
         <v>88.59999999999999</v>
       </c>
       <c r="J70" t="n">
-        <v>1417.02</v>
+        <v>1434.62</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>1328.42</v>
+        <v>1346.02</v>
       </c>
       <c r="L70" t="n">
         <v>9.9</v>
       </c>
       <c r="M70" t="n">
-        <v>145.42</v>
+        <v>161.37</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>135.52</v>
+        <v>151.47</v>
       </c>
     </row>
     <row r="71">
@@ -3303,19 +3303,19 @@
         <v>88.59999999999999</v>
       </c>
       <c r="J71" t="n">
-        <v>1565.52</v>
+        <v>1583.12</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1476.92</v>
+        <v>1494.52</v>
       </c>
       <c r="L71" t="n">
         <v>9.9</v>
       </c>
       <c r="M71" t="n">
-        <v>145.42</v>
+        <v>161.37</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>135.52</v>
+        <v>151.47</v>
       </c>
     </row>
     <row r="72">
@@ -3351,19 +3351,19 @@
         <v>88.59999999999999</v>
       </c>
       <c r="J72" t="n">
-        <v>1417.02</v>
+        <v>1434.62</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>1328.42</v>
+        <v>1346.02</v>
       </c>
       <c r="L72" t="n">
         <v>9.9</v>
       </c>
       <c r="M72" t="n">
-        <v>145.42</v>
+        <v>161.37</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>135.52</v>
+        <v>151.47</v>
       </c>
     </row>
     <row r="73">
@@ -3399,19 +3399,19 @@
         <v>79.59999999999999</v>
       </c>
       <c r="J73" t="n">
-        <v>1668.59</v>
+        <v>1686.19</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1588.99</v>
+        <v>1606.59</v>
       </c>
       <c r="L73" t="n">
         <v>9.9</v>
       </c>
       <c r="M73" t="n">
-        <v>145.42</v>
+        <v>161.37</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>135.52</v>
+        <v>151.47</v>
       </c>
     </row>
     <row r="74">
@@ -3447,19 +3447,19 @@
         <v>50.1</v>
       </c>
       <c r="J74" t="n">
-        <v>1127.94</v>
+        <v>1147.74</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>1077.84</v>
+        <v>1097.64</v>
       </c>
       <c r="L74" t="n">
         <v>45.2</v>
       </c>
       <c r="M74" t="n">
-        <v>803.4400000000001</v>
+        <v>867.24</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>758.24</v>
+        <v>822.04</v>
       </c>
     </row>
     <row r="75">
@@ -3495,19 +3495,19 @@
         <v>45.22</v>
       </c>
       <c r="J75" t="n">
-        <v>1127.94</v>
+        <v>1147.74</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>1082.72</v>
+        <v>1102.52</v>
       </c>
       <c r="L75" t="n">
         <v>50.1</v>
       </c>
       <c r="M75" t="n">
-        <v>782.54</v>
+        <v>857.34</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>732.4400000000001</v>
+        <v>807.24</v>
       </c>
     </row>
     <row r="76">
@@ -3543,19 +3543,19 @@
         <v>50.1</v>
       </c>
       <c r="J76" t="n">
-        <v>1127.94</v>
+        <v>1147.74</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1077.84</v>
+        <v>1097.64</v>
       </c>
       <c r="L76" t="n">
         <v>45.22</v>
       </c>
       <c r="M76" t="n">
-        <v>782.54</v>
+        <v>857.34</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>737.3200000000001</v>
+        <v>812.12</v>
       </c>
     </row>
     <row r="77">
@@ -3591,19 +3591,19 @@
         <v>50.1</v>
       </c>
       <c r="J77" t="n">
-        <v>1133.99</v>
+        <v>1153.79</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>1083.89</v>
+        <v>1103.69</v>
       </c>
       <c r="L77" t="n">
         <v>45.22</v>
       </c>
       <c r="M77" t="n">
-        <v>782.54</v>
+        <v>857.34</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>737.3200000000001</v>
+        <v>812.12</v>
       </c>
     </row>
     <row r="78">
@@ -3621,10 +3621,10 @@
         <v>85.78</v>
       </c>
       <c r="D78" t="n">
-        <v>271.8244</v>
+        <v>320.3386</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>186.0444</v>
+        <v>234.5586</v>
       </c>
       <c r="F78" t="n">
         <v>96.8</v>
@@ -3639,19 +3639,19 @@
         <v>85.09999999999999</v>
       </c>
       <c r="J78" t="n">
-        <v>1398.54</v>
+        <v>1416.14</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>1313.44</v>
+        <v>1331.04</v>
       </c>
       <c r="L78" t="n">
         <v>9.9</v>
       </c>
       <c r="M78" t="n">
-        <v>145.42</v>
+        <v>161.37</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>135.52</v>
+        <v>151.47</v>
       </c>
     </row>
     <row r="79">
@@ -3675,7 +3675,7 @@
         <v>842.039</v>
       </c>
       <c r="M79" t="n">
-        <v>20.68</v>
+        <v>120.516</v>
       </c>
     </row>
     <row r="80">
@@ -3699,7 +3699,7 @@
         <v>773.509</v>
       </c>
       <c r="M80" t="n">
-        <v>20.68</v>
+        <v>120.516</v>
       </c>
     </row>
     <row r="81">
@@ -3951,19 +3951,19 @@
         <v>90.09999999999999</v>
       </c>
       <c r="J86" t="n">
-        <v>1556.72</v>
+        <v>1574.32</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>1466.62</v>
+        <v>1484.22</v>
       </c>
       <c r="L86" t="n">
         <v>9.9</v>
       </c>
       <c r="M86" t="n">
-        <v>145.42</v>
+        <v>161.37</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>135.52</v>
+        <v>151.47</v>
       </c>
     </row>
     <row r="87">
@@ -3999,19 +3999,19 @@
         <v>90.09999999999999</v>
       </c>
       <c r="J87" t="n">
-        <v>1556.72</v>
+        <v>1574.32</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>1466.62</v>
+        <v>1484.22</v>
       </c>
       <c r="L87" t="n">
         <v>9.9</v>
       </c>
       <c r="M87" t="n">
-        <v>145.42</v>
+        <v>161.37</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>135.52</v>
+        <v>151.47</v>
       </c>
     </row>
     <row r="88">
@@ -4047,19 +4047,19 @@
         <v>88.59999999999999</v>
       </c>
       <c r="J88" t="n">
-        <v>1565.52</v>
+        <v>1583.12</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>1476.92</v>
+        <v>1494.52</v>
       </c>
       <c r="L88" t="n">
         <v>9.9</v>
       </c>
       <c r="M88" t="n">
-        <v>122.1</v>
+        <v>138.05</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>112.2</v>
+        <v>128.15</v>
       </c>
     </row>
     <row r="89">
@@ -4137,19 +4137,19 @@
         <v>91.59999999999999</v>
       </c>
       <c r="J90" t="n">
-        <v>1668.59</v>
+        <v>1686.19</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>1576.99</v>
+        <v>1594.59</v>
       </c>
       <c r="L90" t="n">
         <v>9.9</v>
       </c>
       <c r="M90" t="n">
-        <v>145.42</v>
+        <v>161.37</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>135.52</v>
+        <v>151.47</v>
       </c>
     </row>
     <row r="91">
@@ -4209,13 +4209,13 @@
         <v>239.8497</v>
       </c>
       <c r="G92" t="n">
-        <v>464.7459</v>
+        <v>1210.7659</v>
       </c>
       <c r="J92" t="n">
-        <v>892.7831</v>
+        <v>913.1331</v>
       </c>
       <c r="M92" t="n">
-        <v>536.91</v>
+        <v>612.8099999999999</v>
       </c>
     </row>
     <row r="93">
@@ -4233,13 +4233,13 @@
         <v>314.8636</v>
       </c>
       <c r="G93" t="n">
-        <v>516.319</v>
+        <v>970.5151</v>
       </c>
       <c r="J93" t="n">
-        <v>893.6124</v>
+        <v>912.3124</v>
       </c>
       <c r="M93" t="n">
-        <v>385.64</v>
+        <v>416.44</v>
       </c>
     </row>
     <row r="94">
@@ -4266,10 +4266,10 @@
         <v>134.42</v>
       </c>
       <c r="G94" t="n">
-        <v>797.419</v>
+        <v>1509.7851</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>662.999</v>
+        <v>1375.3651</v>
       </c>
       <c r="I94" t="n">
         <v>45.1</v>
@@ -4326,10 +4326,10 @@
         <v>21.59</v>
       </c>
       <c r="M95" t="n">
-        <v>316.261</v>
+        <v>377.641</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>294.671</v>
+        <v>356.051</v>
       </c>
     </row>
     <row r="96">
@@ -4356,10 +4356,10 @@
         <v>197.78</v>
       </c>
       <c r="G96" t="n">
-        <v>608.2</v>
+        <v>943.83</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>410.42</v>
+        <v>746.05</v>
       </c>
       <c r="I96" t="n">
         <v>47.9</v>
@@ -5391,7 +5391,7 @@
         <v>238.1211</v>
       </c>
       <c r="G119" t="n">
-        <v>682.2091</v>
+        <v>1134.5566</v>
       </c>
       <c r="J119" t="n">
         <v>891.5901</v>
@@ -5568,10 +5568,10 @@
         <v>79.40000000000001</v>
       </c>
       <c r="G123" t="n">
-        <v>601.15</v>
+        <v>1209.45</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>521.75</v>
+        <v>1130.05</v>
       </c>
       <c r="I123" t="n">
         <v>93.09999999999999</v>
@@ -5601,10 +5601,10 @@
         <v>73.56</v>
       </c>
       <c r="D124" t="n">
-        <v>5476.909</v>
+        <v>5631.2009</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>5403.349</v>
+        <v>5557.6409</v>
       </c>
       <c r="F124" t="n">
         <v>73.56</v>
@@ -5628,10 +5628,10 @@
         <v>17.96</v>
       </c>
       <c r="M124" t="n">
-        <v>307.34</v>
+        <v>363</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>289.38</v>
+        <v>345.04</v>
       </c>
     </row>
     <row r="125">
@@ -5649,10 +5649,10 @@
         <v>74.25</v>
       </c>
       <c r="D125" t="n">
-        <v>288.0745</v>
+        <v>464.2032</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>213.8245</v>
+        <v>389.9532</v>
       </c>
       <c r="F125" t="n">
         <v>74.25</v>
@@ -5676,10 +5676,10 @@
         <v>20.88</v>
       </c>
       <c r="M125" t="n">
-        <v>307.34</v>
+        <v>363</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>286.46</v>
+        <v>342.12</v>
       </c>
     </row>
     <row r="126">
@@ -5697,10 +5697,10 @@
         <v>96.36</v>
       </c>
       <c r="D126" t="n">
-        <v>291.1968</v>
+        <v>329.3496</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>194.8368</v>
+        <v>232.9896</v>
       </c>
       <c r="F126" t="n">
         <v>183.1133</v>
@@ -5724,10 +5724,10 @@
         <v>26.05</v>
       </c>
       <c r="M126" t="n">
-        <v>384.56</v>
+        <v>456.94</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>358.51</v>
+        <v>430.89</v>
       </c>
     </row>
     <row r="127">
@@ -5745,10 +5745,10 @@
         <v>99.09</v>
       </c>
       <c r="D127" t="n">
-        <v>210.2827</v>
+        <v>367.2197</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>111.1927</v>
+        <v>268.1297</v>
       </c>
       <c r="F127" t="n">
         <v>99.09</v>
@@ -5772,10 +5772,10 @@
         <v>18.18</v>
       </c>
       <c r="M127" t="n">
-        <v>292.93</v>
+        <v>328.13</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>274.75</v>
+        <v>309.95</v>
       </c>
     </row>
     <row r="128">
@@ -5793,10 +5793,10 @@
         <v>110.33</v>
       </c>
       <c r="D128" t="n">
-        <v>141.0953</v>
+        <v>143.8348</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>30.7653</v>
+        <v>33.5048</v>
       </c>
       <c r="F128" t="n">
         <v>110.33</v>
@@ -5862,10 +5862,10 @@
         <v>18.37</v>
       </c>
       <c r="M129" t="n">
-        <v>275.77</v>
+        <v>290.73</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>257.4</v>
+        <v>272.36</v>
       </c>
     </row>
     <row r="130">
@@ -5901,19 +5901,19 @@
         <v>58.1</v>
       </c>
       <c r="J130" t="n">
-        <v>1137.95</v>
+        <v>1157.75</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>1079.85</v>
+        <v>1099.65</v>
       </c>
       <c r="L130" t="n">
         <v>32.32</v>
       </c>
       <c r="M130" t="n">
-        <v>490.82</v>
+        <v>521.62</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>458.5</v>
+        <v>489.3</v>
       </c>
     </row>
     <row r="131">
@@ -6141,7 +6141,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>157.833</v>
+        <v>227.2921</v>
       </c>
       <c r="G136" t="n">
         <v>1665.03</v>
@@ -6165,10 +6165,10 @@
         <v>116.48</v>
       </c>
       <c r="D137" t="n">
-        <v>152.7515</v>
+        <v>236.36</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>36.2715</v>
+        <v>119.88</v>
       </c>
       <c r="F137" t="n">
         <v>190.8133</v>
@@ -6207,19 +6207,19 @@
         <v>88.03</v>
       </c>
       <c r="D138" t="n">
-        <v>165.2274</v>
+        <v>249.1272</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>77.1974</v>
+        <v>161.0972</v>
       </c>
       <c r="F138" t="n">
         <v>183.9933</v>
       </c>
       <c r="G138" t="n">
-        <v>541.5700000000001</v>
+        <v>1295.95</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>357.5767</v>
+        <v>1111.9567</v>
       </c>
       <c r="I138" t="n">
         <v>50.1</v>
@@ -6234,10 +6234,10 @@
         <v>26.05</v>
       </c>
       <c r="M138" t="n">
-        <v>384.34</v>
+        <v>456.72</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>358.29</v>
+        <v>430.67</v>
       </c>
     </row>
     <row r="139">
@@ -6252,7 +6252,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>160.9975</v>
+        <v>243.2455</v>
       </c>
       <c r="G139" t="n">
         <v>939.917</v>
@@ -6321,19 +6321,19 @@
         <v>88.09999999999999</v>
       </c>
       <c r="J141" t="n">
-        <v>1473.34</v>
+        <v>1490.94</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>1385.24</v>
+        <v>1402.84</v>
       </c>
       <c r="L141" t="n">
         <v>9.9</v>
       </c>
       <c r="M141" t="n">
-        <v>145.42</v>
+        <v>161.37</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>135.52</v>
+        <v>151.47</v>
       </c>
     </row>
     <row r="142">
@@ -6750,19 +6750,19 @@
         <v>41.7</v>
       </c>
       <c r="J151" t="n">
-        <v>2025.1</v>
+        <v>2045.45</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>1983.4</v>
+        <v>2003.75</v>
       </c>
       <c r="L151" t="n">
         <v>18.53</v>
       </c>
       <c r="M151" t="n">
-        <v>301.84</v>
+        <v>341.44</v>
       </c>
       <c r="N151" s="2" t="n">
-        <v>283.31</v>
+        <v>322.91</v>
       </c>
     </row>
     <row r="152">
@@ -6798,19 +6798,19 @@
         <v>120.4</v>
       </c>
       <c r="J152" t="n">
-        <v>3292.74</v>
+        <v>3313.09</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>3172.34</v>
+        <v>3192.69</v>
       </c>
       <c r="L152" t="n">
         <v>65.54000000000001</v>
       </c>
       <c r="M152" t="n">
-        <v>1155</v>
+        <v>1185.8</v>
       </c>
       <c r="N152" s="2" t="n">
-        <v>1089.46</v>
+        <v>1120.26</v>
       </c>
     </row>
     <row r="153">
@@ -6846,19 +6846,19 @@
         <v>123.9</v>
       </c>
       <c r="J153" t="n">
-        <v>3362.48</v>
+        <v>3382.83</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>3238.58</v>
+        <v>3258.93</v>
       </c>
       <c r="L153" t="n">
         <v>65.54000000000001</v>
       </c>
       <c r="M153" t="n">
-        <v>1155</v>
+        <v>1185.8</v>
       </c>
       <c r="N153" s="2" t="n">
-        <v>1089.46</v>
+        <v>1120.26</v>
       </c>
     </row>
     <row r="154">
@@ -6894,19 +6894,19 @@
         <v>115.9</v>
       </c>
       <c r="J154" t="n">
-        <v>3122.46</v>
+        <v>3142.81</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>3006.56</v>
+        <v>3026.91</v>
       </c>
       <c r="L154" t="n">
         <v>65.54000000000001</v>
       </c>
       <c r="M154" t="n">
-        <v>1155</v>
+        <v>1185.8</v>
       </c>
       <c r="N154" s="2" t="n">
-        <v>1089.46</v>
+        <v>1120.26</v>
       </c>
     </row>
     <row r="155">
@@ -6942,19 +6942,19 @@
         <v>120.4</v>
       </c>
       <c r="J155" t="n">
-        <v>3285.92</v>
+        <v>3306.27</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>3165.52</v>
+        <v>3185.87</v>
       </c>
       <c r="L155" t="n">
         <v>65.54000000000001</v>
       </c>
       <c r="M155" t="n">
-        <v>1155</v>
+        <v>1185.8</v>
       </c>
       <c r="N155" s="2" t="n">
-        <v>1089.46</v>
+        <v>1120.26</v>
       </c>
     </row>
   </sheetData>

--- a/flask_backend/test_output/ie_import_comparison.xlsx
+++ b/flask_backend/test_output/ie_import_comparison.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="導入對比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="IE人員對比" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,9 +28,15 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -44,7 +50,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFD0D0"/>
+        <fgColor rgb="002E4070"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFB3B3"/>
       </patternFill>
     </fill>
   </fills>
@@ -60,12 +71,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,26 +446,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N155"/>
+  <dimension ref="A1:N156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>鞋型</t>
@@ -461,209 +476,193 @@
           <t>ART</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>裁斷 Cutting</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>針車 Stitching</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>成型 Assembly</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>貼底 Stockfitting</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>鞋型</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>ART</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>SUM裁斷原始</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>導入後裁斷</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>裁斷差異</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>差異</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>SUM針車原始</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>導入後針車</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>針車差異</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>差異</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>SUM成型原始</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>導入後成型</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>成型差異</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>差異</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>SUM貼底原始</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>導入後貼底</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>貼底差異</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OZWEEGO J  Target Output :960 Prs / 8H (120 Prs / </t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IE2779</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>288.1766</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1159.3051</v>
-      </c>
-      <c r="J2" t="n">
-        <v>932.1124</v>
-      </c>
-      <c r="M2" t="n">
-        <v>416.44</v>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>差異</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F50 ADIFRAME W   Target Output : 960 Prs / 8H (120</t>
+          <t xml:space="preserve">OZWEEGO J  Target Output :960 Prs / 8H (120 Prs / </t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KK0176</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>96.39</v>
+          <t>IE2779</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>311.9294</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>215.5394</v>
-      </c>
-      <c r="F3" t="n">
-        <v>96.39</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>1624.98</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>1528.59</v>
-      </c>
-      <c r="I3" t="n">
-        <v>66.59999999999999</v>
+        <v>38.64</v>
       </c>
       <c r="J3" t="n">
-        <v>1413.83</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>1347.23</v>
-      </c>
-      <c r="L3" t="n">
-        <v>26.82</v>
+        <v>31.07</v>
       </c>
       <c r="M3" t="n">
-        <v>438.24</v>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>411.42</v>
+        <v>13.88</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">OZMILLEN  Target Output : 960 Prs / 8H (120 Prs / </t>
+          <t>F50 ADIFRAME W   Target Output : 960 Prs / 8H (120</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JP7827</t>
-        </is>
+          <t>KK0176</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>19</v>
       </c>
       <c r="D4" t="n">
-        <v>501.1822</v>
+        <v>10.4</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>-8.6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>41</v>
       </c>
       <c r="G4" t="n">
-        <v>1394.3923</v>
+        <v>54.17</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="I4" t="n">
+        <v>51</v>
       </c>
       <c r="J4" t="n">
-        <v>946.4795</v>
+        <v>47.13</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>-3.87</v>
+      </c>
+      <c r="L4" t="n">
+        <v>15</v>
       </c>
       <c r="M4" t="n">
-        <v>491.04</v>
+        <v>14.61</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SL 72 RS Target Output : 960 Prs / 8H (120 Prs / H</t>
+          <t xml:space="preserve">OZMILLEN  Target Output : 960 Prs / 8H (120 Prs / </t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JI1282</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>223.3</v>
+          <t>JP7827</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>485.111</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>261.811</v>
-      </c>
-      <c r="F5" t="n">
-        <v>223.3</v>
+        <v>16.71</v>
       </c>
       <c r="G5" t="n">
-        <v>3031.91</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>2808.61</v>
-      </c>
-      <c r="I5" t="n">
-        <v>51.1</v>
+        <v>46.48</v>
       </c>
       <c r="J5" t="n">
-        <v>1033.329</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>982.229</v>
-      </c>
-      <c r="L5" t="n">
-        <v>36.97</v>
+        <v>31.55</v>
       </c>
       <c r="M5" t="n">
-        <v>531.52</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>494.55</v>
+        <v>16.37</v>
       </c>
     </row>
     <row r="6">
@@ -674,320 +673,320 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KH9662</t>
+          <t>JI1282</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>223.3</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
-        <v>218.3292</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>-4.9708</v>
+        <v>16.17</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>-2.83</v>
       </c>
       <c r="F6" t="n">
-        <v>223.3</v>
+        <v>31.5</v>
       </c>
       <c r="G6" t="n">
-        <v>3104.84</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>2881.54</v>
+        <v>101.06</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>69.56</v>
       </c>
       <c r="I6" t="n">
-        <v>51.1</v>
+        <v>38.5</v>
       </c>
       <c r="J6" t="n">
-        <v>1221.44</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>1170.34</v>
+        <v>34.44</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>-4.06</v>
       </c>
       <c r="L6" t="n">
-        <v>36.97</v>
+        <v>21</v>
       </c>
       <c r="M6" t="n">
-        <v>911.02</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>874.05</v>
+        <v>17.72</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>-3.28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SL 72 RS EL C Target Output : 960 Prs / 8H (120 Pr</t>
+          <t>SL 72 RS Target Output : 960 Prs / 8H (120 Prs / H</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IH2982</t>
+          <t>KH9662</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>223.3</v>
+        <v>16.5</v>
       </c>
       <c r="D7" t="n">
-        <v>222.916</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>-0.384</v>
+        <v>7.28</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>-9.220000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>223.3</v>
+        <v>35.5</v>
       </c>
       <c r="G7" t="n">
-        <v>3085.26</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>2861.96</v>
+        <v>103.49</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>67.98999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>50.1</v>
+        <v>42.5</v>
       </c>
       <c r="J7" t="n">
-        <v>1017.17</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>967.0700000000001</v>
+        <v>40.71</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>-1.79</v>
       </c>
       <c r="L7" t="n">
-        <v>27.83</v>
+        <v>21</v>
       </c>
       <c r="M7" t="n">
-        <v>379.5</v>
-      </c>
-      <c r="N7" s="2" t="n">
-        <v>351.67</v>
+        <v>30.37</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SL 72 RS EL I  Target Output : 960 Prs / 8H (120 P</t>
+          <t>SL 72 RS EL C Target Output : 960 Prs / 8H (120 Pr</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IH2978</t>
+          <t>IH2982</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>223.3</v>
+        <v>12.5</v>
       </c>
       <c r="D8" t="n">
-        <v>223.663</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>0.363</v>
+        <v>7.43</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>-5.07</v>
       </c>
       <c r="F8" t="n">
-        <v>223.3</v>
+        <v>35</v>
       </c>
       <c r="G8" t="n">
-        <v>3097.36</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>2874.06</v>
+        <v>102.84</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>67.84</v>
       </c>
       <c r="I8" t="n">
-        <v>50.1</v>
+        <v>38.5</v>
       </c>
       <c r="J8" t="n">
-        <v>1096.48</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>1046.38</v>
+        <v>33.91</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>-4.59</v>
       </c>
       <c r="L8" t="n">
-        <v>27.83</v>
+        <v>16</v>
       </c>
       <c r="M8" t="n">
-        <v>957.4400000000001</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>929.61</v>
+        <v>12.65</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>-3.35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SL 72 RS Target Output : 960 Prs / 8H (120 Prs / H</t>
+          <t>SL 72 RS EL I  Target Output : 960 Prs / 8H (120 P</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JQ9554</t>
+          <t>IH2978</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>223.3</v>
+        <v>12.5</v>
       </c>
       <c r="D9" t="n">
-        <v>301.1273</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>77.82729999999999</v>
+        <v>7.46</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>-5.04</v>
       </c>
       <c r="F9" t="n">
-        <v>223.3</v>
+        <v>36</v>
       </c>
       <c r="G9" t="n">
-        <v>3033.51</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>2810.21</v>
+        <v>103.25</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>67.25</v>
       </c>
       <c r="I9" t="n">
-        <v>51.1</v>
+        <v>39.5</v>
       </c>
       <c r="J9" t="n">
-        <v>1037.9677</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>986.8677</v>
+        <v>36.55</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>-2.95</v>
       </c>
       <c r="L9" t="n">
-        <v>36.97</v>
+        <v>16</v>
       </c>
       <c r="M9" t="n">
-        <v>531.52</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>494.55</v>
+        <v>31.91</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>15.91</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SL 72 RTN  Target Output: 960 Prs/ 8H (120 Prs/ Ho</t>
+          <t>SL 72 RS Target Output : 960 Prs / 8H (120 Prs / H</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HP3714</t>
+          <t>JQ9554</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>377.52</v>
+        <v>19</v>
       </c>
       <c r="D10" t="n">
-        <v>266.1674</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>-111.3526</v>
+        <v>10.04</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>-8.960000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>377.52</v>
+        <v>31.5</v>
       </c>
       <c r="G10" t="n">
-        <v>3392.22</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>3014.7</v>
+        <v>101.12</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>69.62</v>
       </c>
       <c r="I10" t="n">
-        <v>50.1</v>
+        <v>38.5</v>
       </c>
       <c r="J10" t="n">
-        <v>959.42</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>909.3200000000001</v>
+        <v>34.6</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>-3.9</v>
       </c>
       <c r="L10" t="n">
-        <v>36.47</v>
+        <v>21</v>
+      </c>
+      <c r="M10" t="n">
+        <v>17.72</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>-3.28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SL 72 RTN Target Output: 960 Prs / 8H (120 Prs / H</t>
+          <t>SL 72 RTN  Target Output: 960 Prs/ 8H (120 Prs/ Ho</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JR8764</t>
+          <t>HP3714</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>377.52</v>
+        <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>324.6865</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>-52.8335</v>
+        <v>8.869999999999999</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>-15.13</v>
       </c>
       <c r="F11" t="n">
-        <v>377.52</v>
+        <v>39</v>
       </c>
       <c r="G11" t="n">
-        <v>3272.87</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>2895.35</v>
+        <v>113.07</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>74.06999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>50.1</v>
+        <v>37</v>
       </c>
       <c r="J11" t="n">
-        <v>970.86</v>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>920.76</v>
+        <v>31.98</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>-5.02</v>
       </c>
       <c r="L11" t="n">
-        <v>36.47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GHOST SPRINT BALLET Target Output: 960 Prs/8H (120</t>
+          <t>SL 72 RTN Target Output: 960 Prs / 8H (120 Prs / H</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>KI7738</t>
+          <t>JR8764</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>92.58</v>
+        <v>20.5</v>
       </c>
       <c r="D12" t="n">
-        <v>166.5912</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>74.0112</v>
+        <v>10.82</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>-9.68</v>
       </c>
       <c r="F12" t="n">
-        <v>96.8</v>
+        <v>35</v>
       </c>
       <c r="G12" t="n">
-        <v>1414.2712</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>1317.4712</v>
+        <v>109.1</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>74.09999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>85.09999999999999</v>
+        <v>37</v>
       </c>
       <c r="J12" t="n">
-        <v>1264.56</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>1179.46</v>
+        <v>32.36</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>-4.64</v>
       </c>
       <c r="L12" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="M12" t="n">
-        <v>138.05</v>
-      </c>
-      <c r="N12" s="2" t="n">
-        <v>128.15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
@@ -998,92 +997,92 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>KZ7290</t>
+          <t>KI7738</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>92.58</v>
+        <v>20</v>
       </c>
       <c r="D13" t="n">
-        <v>166.5912</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>74.0112</v>
+        <v>5.55</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>-14.45</v>
       </c>
       <c r="F13" t="n">
-        <v>96.8</v>
+        <v>38</v>
       </c>
       <c r="G13" t="n">
-        <v>1414.2712</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>1317.4712</v>
+        <v>47.14</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>9.140000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>85.09999999999999</v>
+        <v>44.5</v>
       </c>
       <c r="J13" t="n">
-        <v>1264.56</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>1179.46</v>
+        <v>42.15</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>-2.35</v>
       </c>
       <c r="L13" t="n">
-        <v>9.9</v>
+        <v>5</v>
       </c>
       <c r="M13" t="n">
-        <v>138.05</v>
-      </c>
-      <c r="N13" s="2" t="n">
-        <v>128.15</v>
+        <v>4.6</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ORGN ULTRA TECH   Target Output : 960 Prs / 8H (12</t>
+          <t>GHOST SPRINT BALLET Target Output: 960 Prs/8H (120</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HQ9484</t>
+          <t>KZ7290</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>112.64</v>
+        <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>1059.4392</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>946.7992</v>
+        <v>5.55</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>-14.45</v>
       </c>
       <c r="F14" t="n">
-        <v>206.9467</v>
+        <v>38</v>
       </c>
       <c r="G14" t="n">
-        <v>1522.53</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>1315.5833</v>
+        <v>47.14</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>9.140000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>48.9</v>
+        <v>44.5</v>
       </c>
       <c r="J14" t="n">
-        <v>1081.63</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>1032.73</v>
+        <v>42.15</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>-2.35</v>
       </c>
       <c r="L14" t="n">
-        <v>48.37</v>
+        <v>5</v>
       </c>
       <c r="M14" t="n">
-        <v>752.675</v>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>704.3049999999999</v>
+        <v>4.6</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="15">
@@ -1094,17 +1093,44 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HQ9485</t>
-        </is>
+          <t>HQ9484</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>746.3200000000001</v>
+        <v>35.31</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="F15" t="n">
+        <v>51</v>
       </c>
       <c r="G15" t="n">
-        <v>1638.25</v>
+        <v>50.75</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="I15" t="n">
+        <v>39.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1027.18</v>
+        <v>36.05</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="L15" t="n">
+        <v>28</v>
+      </c>
+      <c r="M15" t="n">
+        <v>25.09</v>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>-2.91</v>
       </c>
     </row>
     <row r="16">
@@ -1115,20 +1141,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KI7560</t>
+          <t>HQ9485</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>529.3878</v>
+        <v>24.88</v>
       </c>
       <c r="G16" t="n">
-        <v>1577.42</v>
+        <v>54.61</v>
       </c>
       <c r="J16" t="n">
-        <v>1088.56</v>
-      </c>
-      <c r="M16" t="n">
-        <v>752.675</v>
+        <v>34.24</v>
       </c>
     </row>
     <row r="17">
@@ -1139,20 +1162,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KI9862</t>
+          <t>KI7560</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>468.4319</v>
+        <v>17.65</v>
       </c>
       <c r="G17" t="n">
-        <v>1584.57</v>
+        <v>52.58</v>
       </c>
       <c r="J17" t="n">
-        <v>999.13</v>
+        <v>36.29</v>
       </c>
       <c r="M17" t="n">
-        <v>770.0549999999999</v>
+        <v>25.09</v>
       </c>
     </row>
     <row r="18">
@@ -1163,263 +1186,221 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>KZ6381</t>
+          <t>KI9862</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>376.2051</v>
+        <v>15.61</v>
       </c>
       <c r="G18" t="n">
-        <v>1770.83</v>
+        <v>52.82</v>
       </c>
       <c r="J18" t="n">
-        <v>1027.18</v>
+        <v>33.3</v>
+      </c>
+      <c r="M18" t="n">
+        <v>25.67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OZGAIA W Target Output : 960 Prs / 8H (120 Prs / H</t>
+          <t>ORGN ULTRA TECH   Target Output : 960 Prs / 8H (12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>KZ7071</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>86.84</v>
+          <t>KZ6381</t>
+        </is>
       </c>
       <c r="D19" t="n">
-        <v>262.5895</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>175.7495</v>
-      </c>
-      <c r="F19" t="n">
-        <v>194.6188</v>
+        <v>12.54</v>
       </c>
       <c r="G19" t="n">
-        <v>1215.6659</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>1021.0471</v>
-      </c>
-      <c r="I19" t="n">
-        <v>50.1</v>
+        <v>59.03</v>
       </c>
       <c r="J19" t="n">
-        <v>923.5830999999999</v>
-      </c>
-      <c r="K19" s="2" t="n">
-        <v>873.4831</v>
-      </c>
-      <c r="L19" t="n">
-        <v>19.56</v>
+        <v>34.24</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R2C MID/ WD  Target Output : 960 Prs / 8H (120 Prs</t>
+          <t>OZGAIA W Target Output : 960 Prs / 8H (120 Prs / H</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KI0352</t>
-        </is>
+          <t>KZ7071</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>12.5</v>
       </c>
       <c r="D20" t="n">
-        <v>507.4631</v>
+        <v>8.75</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="F20" t="n">
+        <v>44</v>
       </c>
       <c r="G20" t="n">
-        <v>1599.52</v>
+        <v>40.52</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>-3.48</v>
+      </c>
+      <c r="I20" t="n">
+        <v>37</v>
       </c>
       <c r="J20" t="n">
-        <v>1606.7771</v>
-      </c>
-      <c r="M20" t="n">
-        <v>456.94</v>
+        <v>30.79</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>-6.21</v>
+      </c>
+      <c r="L20" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SPEZIAL GOLF Target Output : 960 Prs / 8H (120 Prs</t>
+          <t>R2C MID/ WD  Target Output : 960 Prs / 8H (120 Prs</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>KJ0849</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>179.74</v>
+          <t>KI0352</t>
+        </is>
       </c>
       <c r="D21" t="n">
-        <v>177.6722</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>-2.0678</v>
-      </c>
-      <c r="F21" t="n">
-        <v>179.74</v>
+        <v>16.92</v>
       </c>
       <c r="G21" t="n">
-        <v>1215.34</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>1035.6</v>
-      </c>
-      <c r="I21" t="n">
-        <v>50.1</v>
+        <v>53.32</v>
       </c>
       <c r="J21" t="n">
-        <v>959.189</v>
-      </c>
-      <c r="K21" s="2" t="n">
-        <v>909.0890000000001</v>
-      </c>
-      <c r="L21" t="n">
-        <v>24</v>
+        <v>53.56</v>
       </c>
       <c r="M21" t="n">
-        <v>245.916</v>
-      </c>
-      <c r="N21" s="2" t="n">
-        <v>221.916</v>
+        <v>15.23</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JR CODECHAOS BOA 27 Target Output : 480 Prs / 8H (</t>
+          <t>SPEZIAL GOLF Target Output : 960 Prs / 8H (120 Prs</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KI5746</t>
+          <t>KJ0849</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>99.09</v>
+        <v>16</v>
       </c>
       <c r="D22" t="n">
-        <v>343.9368</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>244.8468</v>
+        <v>5.92</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>-10.08</v>
       </c>
       <c r="F22" t="n">
-        <v>99.09</v>
+        <v>39.5</v>
       </c>
       <c r="G22" t="n">
-        <v>771.54</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>672.45</v>
+        <v>40.51</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>1.01</v>
       </c>
       <c r="I22" t="n">
-        <v>45.6</v>
+        <v>37</v>
       </c>
       <c r="J22" t="n">
-        <v>919.6</v>
-      </c>
-      <c r="K22" s="2" t="n">
-        <v>874</v>
+        <v>31.97</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>-5.03</v>
       </c>
       <c r="L22" t="n">
-        <v>18.18</v>
+        <v>11</v>
       </c>
       <c r="M22" t="n">
-        <v>328.13</v>
-      </c>
-      <c r="N22" s="2" t="n">
-        <v>309.95</v>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="N22" s="4" t="n">
+        <v>-2.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SL 72 RS ( STROBEL) Target Output : 960 Prs / 8H (</t>
+          <t>JR CODECHAOS BOA 27 Target Output : 960 Prs / 8H (</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>KH9643</t>
+          <t>KI5746</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>223.3</v>
-      </c>
-      <c r="D23" t="n">
-        <v>165.2021</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>-58.0979</v>
+        <v>14.5</v>
       </c>
       <c r="F23" t="n">
-        <v>223.3</v>
-      </c>
-      <c r="G23" t="n">
-        <v>3026.19</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>2802.89</v>
+        <v>30</v>
       </c>
       <c r="I23" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1015.74</v>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>965.64</v>
+        <v>38</v>
       </c>
       <c r="L23" t="n">
-        <v>36.97</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SL 72 RS Target Output : 960 Prs / 8H (120 Prs / H</t>
+          <t>SL 72 RS ( STROBEL) Target Output : 960 Prs / 8H (</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>KJ0690</t>
+          <t>KH9643</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>223.3</v>
+        <v>17</v>
       </c>
       <c r="D24" t="n">
-        <v>350.8862</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>127.5862</v>
+        <v>5.51</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>-11.49</v>
       </c>
       <c r="F24" t="n">
-        <v>223.3</v>
+        <v>31.5</v>
       </c>
       <c r="G24" t="n">
-        <v>3248.83</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>3025.53</v>
+        <v>100.87</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>69.37</v>
       </c>
       <c r="I24" t="n">
-        <v>51.1</v>
+        <v>39</v>
       </c>
       <c r="J24" t="n">
-        <v>984.159</v>
-      </c>
-      <c r="K24" s="2" t="n">
-        <v>933.059</v>
+        <v>33.86</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>-5.14</v>
       </c>
       <c r="L24" t="n">
-        <v>36.97</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
@@ -1430,44 +1411,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>KH9651</t>
+          <t>KJ0690</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>223.3</v>
+        <v>18</v>
       </c>
       <c r="D25" t="n">
-        <v>219.0389</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>-4.2611</v>
+        <v>11.7</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>-6.3</v>
       </c>
       <c r="F25" t="n">
-        <v>223.3</v>
+        <v>33</v>
       </c>
       <c r="G25" t="n">
-        <v>3064.69</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>2841.39</v>
+        <v>108.29</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>75.29000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>50.1</v>
+        <v>38.5</v>
       </c>
       <c r="J25" t="n">
-        <v>1147.179</v>
-      </c>
-      <c r="K25" s="2" t="n">
-        <v>1097.079</v>
+        <v>32.81</v>
+      </c>
+      <c r="K25" s="4" t="n">
+        <v>-5.69</v>
       </c>
       <c r="L25" t="n">
-        <v>36.97</v>
-      </c>
-      <c r="M25" t="n">
-        <v>531.52</v>
-      </c>
-      <c r="N25" s="2" t="n">
-        <v>494.55</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
@@ -1478,44 +1453,44 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>KH9658</t>
+          <t>KH9651</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>81.90000000000001</v>
+        <v>18.5</v>
       </c>
       <c r="D26" t="n">
-        <v>373.0286</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>291.1286</v>
+        <v>7.3</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>-11.2</v>
       </c>
       <c r="F26" t="n">
-        <v>251.68</v>
+        <v>32.5</v>
       </c>
       <c r="G26" t="n">
-        <v>3141.68</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>2890</v>
+        <v>102.16</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>69.66</v>
       </c>
       <c r="I26" t="n">
-        <v>51.1</v>
+        <v>38.5</v>
       </c>
       <c r="J26" t="n">
-        <v>1045.979</v>
-      </c>
-      <c r="K26" s="2" t="n">
-        <v>994.879</v>
+        <v>38.24</v>
+      </c>
+      <c r="K26" s="4" t="n">
+        <v>-0.26</v>
       </c>
       <c r="L26" t="n">
-        <v>36.97</v>
+        <v>21</v>
       </c>
       <c r="M26" t="n">
-        <v>531.52</v>
-      </c>
-      <c r="N26" s="2" t="n">
-        <v>494.55</v>
+        <v>17.72</v>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>-3.28</v>
       </c>
     </row>
     <row r="27">
@@ -1526,164 +1501,170 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>KJ1674</t>
+          <t>KH9658</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>223.3</v>
+        <v>22.5</v>
       </c>
       <c r="D27" t="n">
-        <v>331.3127</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>108.0127</v>
+        <v>12.43</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>-10.07</v>
       </c>
       <c r="F27" t="n">
-        <v>223.3</v>
+        <v>34.5</v>
       </c>
       <c r="G27" t="n">
-        <v>3313.62</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>3090.32</v>
+        <v>104.72</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>70.22</v>
       </c>
       <c r="I27" t="n">
-        <v>51.1</v>
+        <v>38.5</v>
       </c>
       <c r="J27" t="n">
-        <v>954.899</v>
-      </c>
-      <c r="K27" s="2" t="n">
-        <v>903.799</v>
+        <v>34.87</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>-3.63</v>
       </c>
       <c r="L27" t="n">
-        <v>36.97</v>
+        <v>21</v>
+      </c>
+      <c r="M27" t="n">
+        <v>17.72</v>
+      </c>
+      <c r="N27" s="4" t="n">
+        <v>-3.28</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">SL 72 RS  Target Output : 960 Prs / 8H (120 Prs / </t>
+          <t>SL 72 RS Target Output : 960 Prs / 8H (120 Prs / H</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>KJ1669</t>
+          <t>KJ1674</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>223.3</v>
+        <v>18</v>
       </c>
       <c r="D28" t="n">
-        <v>253.7657</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>30.4657</v>
+        <v>11.04</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>-6.96</v>
       </c>
       <c r="F28" t="n">
-        <v>223.3</v>
+        <v>35.5</v>
       </c>
       <c r="G28" t="n">
-        <v>3370.82</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>3147.52</v>
+        <v>110.45</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>74.95</v>
       </c>
       <c r="I28" t="n">
-        <v>51.1</v>
+        <v>37.5</v>
       </c>
       <c r="J28" t="n">
-        <v>967.769</v>
-      </c>
-      <c r="K28" s="2" t="n">
-        <v>916.669</v>
+        <v>31.83</v>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>-5.67</v>
       </c>
       <c r="L28" t="n">
-        <v>36.97</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SL 72 RTN Target Output: 960 Prs / 8H (120 Prs / H</t>
+          <t xml:space="preserve">SL 72 RS  Target Output : 960 Prs / 8H (120 Prs / </t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>KZ9819</t>
+          <t>KJ1669</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>377.52</v>
+        <v>19</v>
       </c>
       <c r="D29" t="n">
-        <v>347.7715</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>-29.7485</v>
+        <v>8.460000000000001</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>-10.54</v>
       </c>
       <c r="F29" t="n">
-        <v>377.52</v>
+        <v>42.5</v>
       </c>
       <c r="G29" t="n">
-        <v>3385.29</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>3007.77</v>
+        <v>112.36</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>69.86</v>
       </c>
       <c r="I29" t="n">
-        <v>51.6</v>
+        <v>37.5</v>
       </c>
       <c r="J29" t="n">
-        <v>970.86</v>
-      </c>
-      <c r="K29" s="2" t="n">
-        <v>919.26</v>
+        <v>32.26</v>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>-5.24</v>
       </c>
       <c r="L29" t="n">
-        <v>36.47</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">LA TRAINER   Target Output : 480 Prs / 8H (60 Prs </t>
+          <t>SL 72 RTN Target Output: 960 Prs / 8H (120 Prs / H</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>KJ8686</t>
+          <t>KZ9819</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>91.56</v>
+        <v>21.5</v>
       </c>
       <c r="D30" t="n">
-        <v>6467.6937</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>6376.1337</v>
+        <v>11.59</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>-9.91</v>
       </c>
       <c r="F30" t="n">
-        <v>193.2333</v>
+        <v>39</v>
       </c>
       <c r="G30" t="n">
-        <v>1119.812</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>926.5787</v>
+        <v>112.84</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>73.84</v>
       </c>
       <c r="I30" t="n">
-        <v>48.95</v>
+        <v>37</v>
       </c>
       <c r="J30" t="n">
-        <v>1004.96</v>
-      </c>
-      <c r="K30" s="2" t="n">
-        <v>956.01</v>
+        <v>32.36</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>-4.64</v>
       </c>
       <c r="L30" t="n">
-        <v>19.11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31">
@@ -1694,38 +1675,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KK4495</t>
+          <t>KJ8686</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>97.23999999999999</v>
+        <v>17.5</v>
       </c>
       <c r="D31" t="n">
-        <v>6515.4305</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>6418.1905</v>
+        <v>215.59</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>198.09</v>
       </c>
       <c r="F31" t="n">
-        <v>286</v>
+        <v>37</v>
       </c>
       <c r="G31" t="n">
-        <v>1068.722</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>782.722</v>
+        <v>37.33</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>0.33</v>
       </c>
       <c r="I31" t="n">
-        <v>47.45</v>
+        <v>40.5</v>
       </c>
       <c r="J31" t="n">
-        <v>1019.92</v>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>972.47</v>
+        <v>33.5</v>
+      </c>
+      <c r="K31" s="4" t="n">
+        <v>-7</v>
       </c>
       <c r="L31" t="n">
-        <v>26.25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
@@ -1736,38 +1717,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HQ9499</t>
+          <t>KK4495</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>96.02</v>
+        <v>18.5</v>
       </c>
       <c r="D32" t="n">
-        <v>6864.1683</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>6768.1483</v>
+        <v>217.18</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>198.68</v>
       </c>
       <c r="F32" t="n">
-        <v>286</v>
+        <v>33</v>
       </c>
       <c r="G32" t="n">
-        <v>1114.627</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>828.627</v>
+        <v>35.62</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>2.62</v>
       </c>
       <c r="I32" t="n">
-        <v>50.4</v>
+        <v>41.5</v>
       </c>
       <c r="J32" t="n">
-        <v>1139.05</v>
-      </c>
-      <c r="K32" s="2" t="n">
-        <v>1088.65</v>
+        <v>34</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>-7.5</v>
       </c>
       <c r="L32" t="n">
-        <v>24.8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33">
@@ -1778,38 +1759,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IH1650</t>
+          <t>HQ9499</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>91.56</v>
+        <v>21</v>
       </c>
       <c r="D33" t="n">
-        <v>6444.8034</v>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>6353.2434</v>
+        <v>228.81</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>207.81</v>
       </c>
       <c r="F33" t="n">
-        <v>283.58</v>
+        <v>35</v>
       </c>
       <c r="G33" t="n">
-        <v>1072.99</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>789.41</v>
+        <v>37.15</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>2.15</v>
       </c>
       <c r="I33" t="n">
-        <v>50.4</v>
+        <v>45.5</v>
       </c>
       <c r="J33" t="n">
-        <v>1062.16</v>
-      </c>
-      <c r="K33" s="2" t="n">
-        <v>1011.76</v>
+        <v>37.97</v>
+      </c>
+      <c r="K33" s="4" t="n">
+        <v>-7.53</v>
       </c>
       <c r="L33" t="n">
-        <v>17.66</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34">
@@ -1820,44 +1801,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JQ5715</t>
+          <t>IH1650</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>96.84999999999999</v>
+        <v>18</v>
       </c>
       <c r="D34" t="n">
-        <v>6241.5628</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>6144.7128</v>
+        <v>214.83</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>196.83</v>
       </c>
       <c r="F34" t="n">
-        <v>297.88</v>
+        <v>32</v>
       </c>
       <c r="G34" t="n">
-        <v>1130.722</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>832.842</v>
+        <v>35.77</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>3.77</v>
       </c>
       <c r="I34" t="n">
-        <v>50.4</v>
+        <v>42.5</v>
       </c>
       <c r="J34" t="n">
-        <v>1064.91</v>
-      </c>
-      <c r="K34" s="2" t="n">
-        <v>1014.51</v>
+        <v>35.41</v>
+      </c>
+      <c r="K34" s="4" t="n">
+        <v>-7.09</v>
       </c>
       <c r="L34" t="n">
-        <v>19.11</v>
-      </c>
-      <c r="M34" t="n">
-        <v>440.275</v>
-      </c>
-      <c r="N34" s="2" t="n">
-        <v>421.165</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35">
@@ -1868,38 +1843,44 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>KH9679</t>
+          <t>JQ5715</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>97.23999999999999</v>
+        <v>19</v>
       </c>
       <c r="D35" t="n">
-        <v>7246.753</v>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>7149.513</v>
+        <v>208.05</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>189.05</v>
       </c>
       <c r="F35" t="n">
-        <v>286</v>
+        <v>34</v>
       </c>
       <c r="G35" t="n">
-        <v>1065.422</v>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>779.422</v>
+        <v>37.69</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>3.69</v>
       </c>
       <c r="I35" t="n">
-        <v>48.9</v>
+        <v>42.5</v>
       </c>
       <c r="J35" t="n">
-        <v>1019.92</v>
-      </c>
-      <c r="K35" s="2" t="n">
-        <v>971.02</v>
+        <v>35.5</v>
+      </c>
+      <c r="K35" s="4" t="n">
+        <v>-7</v>
       </c>
       <c r="L35" t="n">
-        <v>24.8</v>
+        <v>15</v>
+      </c>
+      <c r="M35" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="N35" s="4" t="n">
+        <v>-0.32</v>
       </c>
     </row>
     <row r="36">
@@ -1910,38 +1891,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>KH9682</t>
+          <t>KH9679</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>93.16</v>
+        <v>18.5</v>
       </c>
       <c r="D36" t="n">
-        <v>7396.3958</v>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>7303.2358</v>
+        <v>241.56</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>223.06</v>
       </c>
       <c r="F36" t="n">
-        <v>286</v>
+        <v>33</v>
       </c>
       <c r="G36" t="n">
-        <v>1065.422</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>779.422</v>
+        <v>35.51</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>2.51</v>
       </c>
       <c r="I36" t="n">
-        <v>50.4</v>
+        <v>41.5</v>
       </c>
       <c r="J36" t="n">
-        <v>981.8111</v>
-      </c>
-      <c r="K36" s="2" t="n">
-        <v>931.4111</v>
+        <v>34</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>-7.5</v>
       </c>
       <c r="L36" t="n">
-        <v>24.8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37">
@@ -1956,34 +1937,34 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>93.16</v>
+        <v>17</v>
       </c>
       <c r="D37" t="n">
-        <v>7356.3958</v>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>7263.2358</v>
+        <v>245.21</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>228.21</v>
       </c>
       <c r="F37" t="n">
-        <v>286</v>
+        <v>33</v>
       </c>
       <c r="G37" t="n">
-        <v>1065.422</v>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>779.422</v>
+        <v>35.51</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>2.51</v>
       </c>
       <c r="I37" t="n">
-        <v>50.4</v>
+        <v>40.5</v>
       </c>
       <c r="J37" t="n">
-        <v>965.4211</v>
-      </c>
-      <c r="K37" s="2" t="n">
-        <v>915.0211</v>
+        <v>32.18</v>
+      </c>
+      <c r="K37" s="4" t="n">
+        <v>-8.32</v>
       </c>
       <c r="L37" t="n">
-        <v>24.8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38">
@@ -1994,38 +1975,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>KI0450</t>
+          <t>KH9682</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>96.84999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="D38" t="n">
-        <v>6248.8997</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>6152.0497</v>
+        <v>245.21</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>229.71</v>
       </c>
       <c r="F38" t="n">
-        <v>297.88</v>
+        <v>33</v>
       </c>
       <c r="G38" t="n">
-        <v>1020.812</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>722.932</v>
+        <v>35.51</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>2.51</v>
       </c>
       <c r="I38" t="n">
-        <v>50.4</v>
+        <v>39.5</v>
       </c>
       <c r="J38" t="n">
-        <v>1019.92</v>
-      </c>
-      <c r="K38" s="2" t="n">
-        <v>969.52</v>
+        <v>32.18</v>
+      </c>
+      <c r="K38" s="4" t="n">
+        <v>-7.32</v>
       </c>
       <c r="L38" t="n">
-        <v>24.8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39">
@@ -2036,38 +2017,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>KI2513</t>
+          <t>KI0450</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>92.77</v>
+        <v>19</v>
       </c>
       <c r="D39" t="n">
-        <v>6201.4137</v>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>6108.6437</v>
+        <v>208.3</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>189.3</v>
       </c>
       <c r="F39" t="n">
-        <v>283.58</v>
+        <v>31</v>
       </c>
       <c r="G39" t="n">
-        <v>1015.812</v>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>732.232</v>
+        <v>34.03</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>3.03</v>
       </c>
       <c r="I39" t="n">
-        <v>48.95</v>
+        <v>41.5</v>
       </c>
       <c r="J39" t="n">
-        <v>989.12</v>
-      </c>
-      <c r="K39" s="2" t="n">
-        <v>940.17</v>
+        <v>34</v>
+      </c>
+      <c r="K39" s="4" t="n">
+        <v>-7.5</v>
       </c>
       <c r="L39" t="n">
-        <v>26.25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40">
@@ -2078,38 +2059,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>KJ4387</t>
+          <t>KI2513</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>96.16</v>
+        <v>17.5</v>
       </c>
       <c r="D40" t="n">
-        <v>7214.9818</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>7118.8218</v>
+        <v>206.71</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>189.21</v>
       </c>
       <c r="F40" t="n">
-        <v>286</v>
+        <v>31</v>
       </c>
       <c r="G40" t="n">
-        <v>1065.422</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>779.422</v>
+        <v>33.86</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>2.86</v>
       </c>
       <c r="I40" t="n">
-        <v>50.4</v>
+        <v>40.5</v>
       </c>
       <c r="J40" t="n">
-        <v>967.12</v>
-      </c>
-      <c r="K40" s="2" t="n">
-        <v>916.72</v>
+        <v>32.97</v>
+      </c>
+      <c r="K40" s="4" t="n">
+        <v>-7.53</v>
       </c>
       <c r="L40" t="n">
-        <v>24.8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41">
@@ -2120,185 +2101,203 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>KK4435</t>
-        </is>
+          <t>KJ4387</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>17.5</v>
       </c>
       <c r="D41" t="n">
-        <v>6713.4631</v>
+        <v>240.5</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>223</v>
+      </c>
+      <c r="F41" t="n">
+        <v>33</v>
       </c>
       <c r="G41" t="n">
-        <v>1063.222</v>
+        <v>35.51</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="I41" t="n">
+        <v>39.5</v>
       </c>
       <c r="J41" t="n">
-        <v>989.12</v>
+        <v>32.24</v>
+      </c>
+      <c r="K41" s="4" t="n">
+        <v>-7.26</v>
+      </c>
+      <c r="L41" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>W/ RETROCROSS 25 Target Output : 960 Prs / 8H (120</t>
+          <t xml:space="preserve">LA TRAINER   Target Output : 480 Prs / 8H (60 Prs </t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JI4025</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>104.41</v>
+          <t>KK4435</t>
+        </is>
       </c>
       <c r="D42" t="n">
-        <v>491.8817</v>
-      </c>
-      <c r="E42" s="2" t="n">
-        <v>387.4717</v>
-      </c>
-      <c r="F42" t="n">
-        <v>247.72</v>
+        <v>223.78</v>
       </c>
       <c r="G42" t="n">
-        <v>1592.05</v>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>1344.33</v>
-      </c>
-      <c r="I42" t="n">
-        <v>47.9</v>
+        <v>35.44</v>
       </c>
       <c r="J42" t="n">
-        <v>821.8099999999999</v>
-      </c>
-      <c r="K42" s="2" t="n">
-        <v>773.91</v>
-      </c>
-      <c r="L42" t="n">
-        <v>28.67</v>
-      </c>
-      <c r="M42" t="n">
-        <v>554.6567</v>
-      </c>
-      <c r="N42" s="2" t="n">
-        <v>525.9867</v>
+        <v>32.97</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SAMBA J Target Output : 960 Prs / 8H (120 Prs / Ho</t>
+          <t>W/ RETROCROSS 25 Target Output : 960 Prs / 8H (120</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IF1944</t>
+          <t>JI4025</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>108.46</v>
+        <v>34</v>
       </c>
       <c r="D43" t="n">
-        <v>362.7204</v>
-      </c>
-      <c r="E43" s="2" t="n">
-        <v>254.2604</v>
+        <v>16.4</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>-17.6</v>
       </c>
       <c r="F43" t="n">
-        <v>108.46</v>
+        <v>48.5</v>
       </c>
       <c r="G43" t="n">
-        <v>937.08</v>
-      </c>
-      <c r="H43" s="2" t="n">
-        <v>828.62</v>
+        <v>53.07</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>4.57</v>
       </c>
       <c r="I43" t="n">
-        <v>47.9</v>
+        <v>33</v>
       </c>
       <c r="J43" t="n">
-        <v>931.109</v>
-      </c>
-      <c r="K43" s="2" t="n">
-        <v>883.2089999999999</v>
+        <v>27.39</v>
+      </c>
+      <c r="K43" s="4" t="n">
+        <v>-5.61</v>
       </c>
       <c r="L43" t="n">
-        <v>4.9</v>
+        <v>20</v>
       </c>
       <c r="M43" t="n">
-        <v>22.7293</v>
-      </c>
-      <c r="N43" s="2" t="n">
-        <v>17.8293</v>
+        <v>18.49</v>
+      </c>
+      <c r="N43" s="4" t="n">
+        <v>-1.51</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>OZMILLEN W Target Output : 960 Prs / 8H (120 Prs /</t>
+          <t>SAMBA J Target Output : 960 Prs / 8H (120 Prs / Ho</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JH5642</t>
-        </is>
+          <t>IF1944</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>16</v>
       </c>
       <c r="D44" t="n">
-        <v>434.5638</v>
+        <v>12.09</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>-3.91</v>
+      </c>
+      <c r="F44" t="n">
+        <v>32</v>
       </c>
       <c r="G44" t="n">
-        <v>1394.3923</v>
+        <v>31.24</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="I44" t="n">
+        <v>38</v>
       </c>
       <c r="J44" t="n">
-        <v>946.4795</v>
+        <v>31.04</v>
+      </c>
+      <c r="K44" s="4" t="n">
+        <v>-6.96</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>491.04</v>
+        <v>0.76</v>
+      </c>
+      <c r="N44" s="4" t="n">
+        <v>-0.24</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">OZMILLEN/ W Target Output : 960 Prs / 8H (120 Prs </t>
+          <t>OZMILLEN W Target Output : 960 Prs / 8H (120 Prs /</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JH7592</t>
+          <t>JH5642</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>434.7992</v>
+        <v>14.49</v>
       </c>
       <c r="G45" t="n">
-        <v>1455.1147</v>
+        <v>46.48</v>
       </c>
       <c r="J45" t="n">
-        <v>946.4795</v>
+        <v>31.55</v>
       </c>
       <c r="M45" t="n">
-        <v>491.04</v>
+        <v>16.37</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>OZMILLEN Target Output : 960 Prs / 8H (120 Prs / H</t>
+          <t xml:space="preserve">OZMILLEN/ W Target Output : 960 Prs / 8H (120 Prs </t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JI2628</t>
+          <t>JH7592</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>352.653</v>
+        <v>14.49</v>
       </c>
       <c r="G46" t="n">
-        <v>1657.7487</v>
+        <v>48.5</v>
       </c>
       <c r="J46" t="n">
-        <v>946.4795</v>
+        <v>31.55</v>
       </c>
       <c r="M46" t="n">
-        <v>491.04</v>
+        <v>16.37</v>
       </c>
     </row>
     <row r="47">
@@ -2309,413 +2308,338 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JI2632</t>
+          <t>JI2628</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>455.0617</v>
+        <v>11.76</v>
       </c>
       <c r="G47" t="n">
-        <v>1455.0847</v>
+        <v>55.26</v>
       </c>
       <c r="J47" t="n">
-        <v>946.4795</v>
+        <v>31.55</v>
       </c>
       <c r="M47" t="n">
-        <v>491.04</v>
+        <v>16.37</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SL 72 RS J Target Output: 960 Prs/ 8H (120 Prs / H</t>
+          <t>OZMILLEN Target Output : 960 Prs / 8H (120 Prs / H</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IH8078</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>223.3</v>
+          <t>JI2632</t>
+        </is>
       </c>
       <c r="D48" t="n">
-        <v>275.4954</v>
-      </c>
-      <c r="E48" s="2" t="n">
-        <v>52.1954</v>
-      </c>
-      <c r="F48" t="n">
-        <v>223.3</v>
+        <v>15.17</v>
       </c>
       <c r="G48" t="n">
-        <v>3031.91</v>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>2808.61</v>
-      </c>
-      <c r="I48" t="n">
-        <v>51.1</v>
+        <v>48.5</v>
       </c>
       <c r="J48" t="n">
-        <v>1035.749</v>
-      </c>
-      <c r="K48" s="2" t="n">
-        <v>984.649</v>
-      </c>
-      <c r="L48" t="n">
-        <v>36.97</v>
+        <v>31.55</v>
       </c>
       <c r="M48" t="n">
-        <v>560.5599999999999</v>
-      </c>
-      <c r="N48" s="2" t="n">
-        <v>523.59</v>
+        <v>16.37</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SL 72 RS Target Output : 960 Prs / 8H (120 Prs / H</t>
+          <t>SL 72 RS J Target Output: 960 Prs/ 8H (120 Prs / H</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IG2132</t>
+          <t>IH8078</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>223.3</v>
+        <v>18.5</v>
       </c>
       <c r="D49" t="n">
-        <v>282.0371</v>
-      </c>
-      <c r="E49" s="2" t="n">
-        <v>58.7371</v>
+        <v>9.18</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>-9.32</v>
       </c>
       <c r="F49" t="n">
-        <v>223.3</v>
+        <v>31.5</v>
       </c>
       <c r="G49" t="n">
-        <v>3035.76</v>
-      </c>
-      <c r="H49" s="2" t="n">
-        <v>2812.46</v>
+        <v>101.06</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>69.56</v>
       </c>
       <c r="I49" t="n">
-        <v>51.1</v>
+        <v>38.5</v>
       </c>
       <c r="J49" t="n">
-        <v>1055.549</v>
-      </c>
-      <c r="K49" s="2" t="n">
-        <v>1004.449</v>
+        <v>34.52</v>
+      </c>
+      <c r="K49" s="4" t="n">
+        <v>-3.98</v>
       </c>
       <c r="L49" t="n">
-        <v>36.97</v>
+        <v>21</v>
       </c>
       <c r="M49" t="n">
-        <v>531.52</v>
-      </c>
-      <c r="N49" s="2" t="n">
-        <v>494.55</v>
+        <v>18.69</v>
+      </c>
+      <c r="N49" s="4" t="n">
+        <v>-2.31</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ADIPOWER 26/ W Target Output : 480 Prs / 8H (60 Pr</t>
+          <t>SL 72 RS Target Output : 960 Prs / 8H (120 Prs / H</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JP8402</t>
+          <t>IG2132</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>128.19</v>
+        <v>19</v>
       </c>
       <c r="D50" t="n">
-        <v>192.4317</v>
-      </c>
-      <c r="E50" s="2" t="n">
-        <v>64.24169999999999</v>
+        <v>9.4</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>-9.6</v>
       </c>
       <c r="F50" t="n">
-        <v>121.66</v>
+        <v>31.5</v>
       </c>
       <c r="G50" t="n">
-        <v>3455.67</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>3334.01</v>
+        <v>101.19</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>69.69</v>
       </c>
       <c r="I50" t="n">
-        <v>61.12</v>
+        <v>38.5</v>
       </c>
       <c r="J50" t="n">
-        <v>1199.55</v>
-      </c>
-      <c r="K50" s="2" t="n">
-        <v>1138.43</v>
+        <v>35.18</v>
+      </c>
+      <c r="K50" s="4" t="n">
+        <v>-3.32</v>
       </c>
       <c r="L50" t="n">
-        <v>32.32</v>
+        <v>21</v>
       </c>
       <c r="M50" t="n">
-        <v>539.4400000000001</v>
-      </c>
-      <c r="N50" s="2" t="n">
-        <v>507.12</v>
+        <v>17.72</v>
+      </c>
+      <c r="N50" s="4" t="n">
+        <v>-3.28</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ADIPOWER 26 SL Target Output : 480 Prs / 8H (60 Pr</t>
+          <t xml:space="preserve">ADIPOWER 26/ WD Target Output : 960 Prs / 8H (120 </t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JP8395</t>
+          <t>JP8402</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>128.19</v>
-      </c>
-      <c r="D51" t="n">
-        <v>192.4317</v>
-      </c>
-      <c r="E51" s="2" t="n">
-        <v>64.24169999999999</v>
+        <v>22.5</v>
       </c>
       <c r="F51" t="n">
-        <v>121.66</v>
-      </c>
-      <c r="G51" t="n">
-        <v>3455.67</v>
-      </c>
-      <c r="H51" s="2" t="n">
-        <v>3334.01</v>
+        <v>49</v>
       </c>
       <c r="I51" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="J51" t="n">
-        <v>1157.75</v>
-      </c>
-      <c r="K51" s="2" t="n">
-        <v>1099.65</v>
+        <v>46</v>
       </c>
       <c r="L51" t="n">
-        <v>32.32</v>
-      </c>
-      <c r="M51" t="n">
-        <v>521.62</v>
-      </c>
-      <c r="N51" s="2" t="n">
-        <v>489.3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>W/ R2C BOA Target Output : 960 Prs / 8H (120 Prs /</t>
+          <t>ADIPOWER 26 SL Target Output : 960 Prs / 8H (120 P</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JQ3439</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>450.5075</v>
-      </c>
-      <c r="G52" t="n">
-        <v>1455.7614</v>
-      </c>
-      <c r="J52" t="n">
-        <v>850.9593</v>
-      </c>
-      <c r="M52" t="n">
-        <v>456.94</v>
+          <t>JP8395</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F52" t="n">
+        <v>49</v>
+      </c>
+      <c r="I52" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="L52" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>R2C  Target Output : 960 Prs / 8H (120 Prs / Hour)</t>
+          <t>W/ R2C BOA Target Output : 960 Prs / 8H (120 Prs /</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JQ0904</t>
+          <t>JQ3439</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>402.2575</v>
+        <v>15.02</v>
       </c>
       <c r="G53" t="n">
-        <v>1146.2817</v>
+        <v>48.53</v>
       </c>
       <c r="J53" t="n">
-        <v>952.1043</v>
+        <v>28.37</v>
       </c>
       <c r="M53" t="n">
-        <v>456.94</v>
+        <v>15.23</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>W/ ADIPOWER 26 SL BOA Target Output : 480 Prs / 8H</t>
+          <t>R2C  Target Output : 960 Prs / 8H (120 Prs / Hour)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JS4140</t>
+          <t>JQ0904</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>283.0558</v>
+        <v>13.41</v>
       </c>
       <c r="G54" t="n">
-        <v>1285.13</v>
+        <v>38.21</v>
       </c>
       <c r="J54" t="n">
-        <v>1100.11</v>
+        <v>31.74</v>
+      </c>
+      <c r="M54" t="n">
+        <v>15.23</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1609ER RS Target Output: 960 Prs / 8H (120 Prs / H</t>
+          <t>W/ ADIPOWER 26 SL BOA Target Output : 960 Prs / 8H</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>KI9853</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>202.4</v>
-      </c>
-      <c r="D55" t="n">
-        <v>160.7054</v>
-      </c>
-      <c r="E55" s="2" t="n">
-        <v>-41.6946</v>
-      </c>
-      <c r="F55" t="n">
-        <v>202.4</v>
-      </c>
-      <c r="G55" t="n">
-        <v>3083.5</v>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>2881.1</v>
-      </c>
-      <c r="I55" t="n">
-        <v>51.1</v>
-      </c>
-      <c r="J55" t="n">
-        <v>1020.129</v>
-      </c>
-      <c r="K55" s="2" t="n">
-        <v>969.029</v>
-      </c>
-      <c r="L55" t="n">
-        <v>21.03</v>
-      </c>
-      <c r="M55" t="n">
-        <v>318.78</v>
-      </c>
-      <c r="N55" s="2" t="n">
-        <v>297.75</v>
+          <t>JS4140</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">SL 72 RS  Target Output : 960 Prs / 8H (120 Prs / </t>
+          <t>1609ER RS Target Output: 960 Prs / 8H (120 Prs / H</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HQ4909</t>
+          <t>KI9853</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>97.73</v>
+        <v>12.5</v>
       </c>
       <c r="D56" t="n">
-        <v>313.0437</v>
-      </c>
-      <c r="E56" s="2" t="n">
-        <v>215.3137</v>
+        <v>5.36</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>-7.14</v>
       </c>
       <c r="F56" t="n">
-        <v>238.48</v>
+        <v>33.5</v>
       </c>
       <c r="G56" t="n">
-        <v>3442.08</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>3203.6</v>
+        <v>102.78</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>69.28</v>
       </c>
       <c r="I56" t="n">
-        <v>51.1</v>
+        <v>38.5</v>
       </c>
       <c r="J56" t="n">
-        <v>973.489</v>
-      </c>
-      <c r="K56" s="2" t="n">
-        <v>922.389</v>
+        <v>34</v>
+      </c>
+      <c r="K56" s="4" t="n">
+        <v>-4.5</v>
       </c>
       <c r="L56" t="n">
-        <v>36.97</v>
+        <v>13</v>
+      </c>
+      <c r="M56" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="N56" s="4" t="n">
+        <v>-2.37</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SL 72 RS Target Output : 960 Prs / 8H (120 Prs / H</t>
+          <t xml:space="preserve">SL 72 RS  Target Output : 960 Prs / 8H (120 Prs / </t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JQ9795</t>
+          <t>HQ4909</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>223.3</v>
+        <v>21</v>
       </c>
       <c r="D57" t="n">
-        <v>316.5548</v>
-      </c>
-      <c r="E57" s="2" t="n">
-        <v>93.2548</v>
+        <v>10.43</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>-10.57</v>
       </c>
       <c r="F57" t="n">
-        <v>223.3</v>
+        <v>44.5</v>
       </c>
       <c r="G57" t="n">
-        <v>3031.86</v>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>2808.56</v>
+        <v>114.74</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>70.23999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>52.6</v>
+        <v>37.5</v>
       </c>
       <c r="J57" t="n">
-        <v>989.879</v>
-      </c>
-      <c r="K57" s="2" t="n">
-        <v>937.279</v>
+        <v>32.45</v>
+      </c>
+      <c r="K57" s="4" t="n">
+        <v>-5.05</v>
       </c>
       <c r="L57" t="n">
-        <v>36.97</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58">
@@ -2726,500 +2650,494 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JQ9823</t>
+          <t>JQ9795</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>223.3</v>
+        <v>18</v>
       </c>
       <c r="D58" t="n">
-        <v>227.382</v>
-      </c>
-      <c r="E58" s="2" t="n">
-        <v>4.082</v>
+        <v>10.55</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>-7.45</v>
       </c>
       <c r="F58" t="n">
-        <v>223.3</v>
+        <v>31.5</v>
       </c>
       <c r="G58" t="n">
-        <v>3164.68</v>
-      </c>
-      <c r="H58" s="2" t="n">
-        <v>2941.38</v>
+        <v>101.06</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>69.56</v>
       </c>
       <c r="I58" t="n">
-        <v>52.6</v>
+        <v>38.5</v>
       </c>
       <c r="J58" t="n">
-        <v>1055.879</v>
-      </c>
-      <c r="K58" s="2" t="n">
-        <v>1003.279</v>
+        <v>33</v>
+      </c>
+      <c r="K58" s="4" t="n">
+        <v>-5.5</v>
       </c>
       <c r="L58" t="n">
-        <v>36.97</v>
-      </c>
-      <c r="M58" t="n">
-        <v>531.52</v>
-      </c>
-      <c r="N58" s="2" t="n">
-        <v>494.55</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">SL 72 RS  Target Output : 960 Prs / 8H (120 Prs / </t>
+          <t>SL 72 RS Target Output : 960 Prs / 8H (120 Prs / H</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>KJ1666</t>
+          <t>JQ9823</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>88.23999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="D59" t="n">
-        <v>374.9739</v>
-      </c>
-      <c r="E59" s="2" t="n">
-        <v>286.7339</v>
+        <v>7.58</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>-11.92</v>
       </c>
       <c r="F59" t="n">
-        <v>238.48</v>
+        <v>35.5</v>
       </c>
       <c r="G59" t="n">
-        <v>3230.88</v>
-      </c>
-      <c r="H59" s="2" t="n">
-        <v>2992.4</v>
+        <v>105.49</v>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>69.98999999999999</v>
       </c>
       <c r="I59" t="n">
-        <v>51.1</v>
+        <v>38.5</v>
       </c>
       <c r="J59" t="n">
-        <v>1041.579</v>
-      </c>
-      <c r="K59" s="2" t="n">
-        <v>990.479</v>
+        <v>35.2</v>
+      </c>
+      <c r="K59" s="4" t="n">
+        <v>-3.3</v>
       </c>
       <c r="L59" t="n">
-        <v>36.97</v>
+        <v>21</v>
       </c>
       <c r="M59" t="n">
-        <v>531.52</v>
-      </c>
-      <c r="N59" s="2" t="n">
-        <v>494.55</v>
+        <v>17.72</v>
+      </c>
+      <c r="N59" s="4" t="n">
+        <v>-3.28</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>W/ TECH RESPONSE 3.0/ (WD) Target Output : 960 Prs</t>
+          <t xml:space="preserve">SL 72 RS  Target Output : 960 Prs / 8H (120 Prs / </t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GV6889</t>
+          <t>KJ1666</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>70.52</v>
+        <v>22.5</v>
       </c>
       <c r="D60" t="n">
-        <v>92.97199999999999</v>
-      </c>
-      <c r="E60" s="2" t="n">
-        <v>22.452</v>
+        <v>12.5</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>-10</v>
       </c>
       <c r="F60" t="n">
-        <v>70.52</v>
+        <v>38</v>
       </c>
       <c r="G60" t="n">
-        <v>857.89</v>
-      </c>
-      <c r="H60" s="2" t="n">
-        <v>787.37</v>
+        <v>107.7</v>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>69.7</v>
       </c>
       <c r="I60" t="n">
-        <v>51.1</v>
+        <v>37.5</v>
       </c>
       <c r="J60" t="n">
-        <v>963.215</v>
-      </c>
-      <c r="K60" s="2" t="n">
-        <v>912.115</v>
+        <v>34.72</v>
+      </c>
+      <c r="K60" s="4" t="n">
+        <v>-2.78</v>
       </c>
       <c r="L60" t="n">
-        <v>20.88</v>
+        <v>21</v>
       </c>
       <c r="M60" t="n">
-        <v>363</v>
-      </c>
-      <c r="N60" s="2" t="n">
-        <v>342.12</v>
+        <v>17.72</v>
+      </c>
+      <c r="N60" s="4" t="n">
+        <v>-3.28</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>W/ TECH RESPONSE SL 3/(WD) Target Output : 960 Prs</t>
+          <t>W/ TECH RESPONSE 3.0/ (WD) Target Output : 960 Prs</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GV6897</t>
+          <t>GV6889</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>69.13</v>
+        <v>11.5</v>
       </c>
       <c r="D61" t="n">
-        <v>330.8654</v>
-      </c>
-      <c r="E61" s="2" t="n">
-        <v>261.7354</v>
+        <v>3.1</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>-8.4</v>
       </c>
       <c r="F61" t="n">
-        <v>69.13</v>
+        <v>34</v>
       </c>
       <c r="G61" t="n">
-        <v>805.2732999999999</v>
-      </c>
-      <c r="H61" s="2" t="n">
-        <v>736.1433</v>
+        <v>28.6</v>
+      </c>
+      <c r="H61" s="4" t="n">
+        <v>-5.4</v>
       </c>
       <c r="I61" t="n">
-        <v>51.1</v>
+        <v>38.5</v>
       </c>
       <c r="J61" t="n">
-        <v>876.095</v>
-      </c>
-      <c r="K61" s="2" t="n">
-        <v>824.995</v>
+        <v>32.11</v>
+      </c>
+      <c r="K61" s="4" t="n">
+        <v>-6.39</v>
       </c>
       <c r="L61" t="n">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="M61" t="n">
-        <v>363</v>
-      </c>
-      <c r="N61" s="2" t="n">
-        <v>345.04</v>
+        <v>12.1</v>
+      </c>
+      <c r="N61" s="4" t="n">
+        <v>-1.9</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>W/ RETROCROSS 25   Target Output : 960 Prs / 8H (1</t>
+          <t>W/ TECH RESPONSE SL 3/(WD) Target Output : 960 Prs</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JI4024</t>
+          <t>GV6897</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>104.41</v>
+        <v>11.5</v>
       </c>
       <c r="D62" t="n">
-        <v>462.2874</v>
-      </c>
-      <c r="E62" s="2" t="n">
-        <v>357.8774</v>
+        <v>11.03</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>-0.47</v>
       </c>
       <c r="F62" t="n">
-        <v>247.72</v>
+        <v>33</v>
       </c>
       <c r="G62" t="n">
-        <v>1543.65</v>
-      </c>
-      <c r="H62" s="2" t="n">
-        <v>1295.93</v>
+        <v>26.84</v>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>-6.16</v>
       </c>
       <c r="I62" t="n">
-        <v>47.9</v>
+        <v>36</v>
       </c>
       <c r="J62" t="n">
-        <v>971.3</v>
-      </c>
-      <c r="K62" s="2" t="n">
-        <v>923.4</v>
+        <v>29.2</v>
+      </c>
+      <c r="K62" s="4" t="n">
+        <v>-6.8</v>
       </c>
       <c r="L62" t="n">
-        <v>28.67</v>
+        <v>14</v>
       </c>
       <c r="M62" t="n">
-        <v>554.6567</v>
-      </c>
-      <c r="N62" s="2" t="n">
-        <v>525.9867</v>
+        <v>12.1</v>
+      </c>
+      <c r="N62" s="4" t="n">
+        <v>-1.9</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">RETROCROSS 25   Target Output : 960 Prs / 8H (120 </t>
+          <t>W/ RETROCROSS 25   Target Output : 960 Prs / 8H (1</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>KJ5770</t>
+          <t>JI4024</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>99.81</v>
+        <v>32</v>
       </c>
       <c r="D63" t="n">
-        <v>440.0522</v>
-      </c>
-      <c r="E63" s="2" t="n">
-        <v>340.2422</v>
+        <v>15.41</v>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>-16.59</v>
       </c>
       <c r="F63" t="n">
-        <v>247.72</v>
+        <v>48.5</v>
       </c>
       <c r="G63" t="n">
-        <v>1493.05</v>
-      </c>
-      <c r="H63" s="2" t="n">
-        <v>1245.33</v>
+        <v>51.46</v>
+      </c>
+      <c r="H63" s="4" t="n">
+        <v>2.96</v>
       </c>
       <c r="I63" t="n">
-        <v>47.9</v>
+        <v>38</v>
       </c>
       <c r="J63" t="n">
-        <v>971.3</v>
-      </c>
-      <c r="K63" s="2" t="n">
-        <v>923.4</v>
+        <v>32.38</v>
+      </c>
+      <c r="K63" s="4" t="n">
+        <v>-5.62</v>
       </c>
       <c r="L63" t="n">
-        <v>28.67</v>
+        <v>20</v>
       </c>
       <c r="M63" t="n">
-        <v>554.6567</v>
-      </c>
-      <c r="N63" s="2" t="n">
-        <v>525.9867</v>
+        <v>18.49</v>
+      </c>
+      <c r="N63" s="4" t="n">
+        <v>-1.51</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>W/CODECHAOS 27 Target Output : 960 Prs / 8H (120 P</t>
+          <t xml:space="preserve">RETROCROSS 25   Target Output : 960 Prs / 8H (120 </t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>KI5734</t>
-        </is>
+          <t>KJ5770</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>31.5</v>
       </c>
       <c r="D64" t="n">
-        <v>227.6339</v>
+        <v>14.67</v>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>-16.83</v>
+      </c>
+      <c r="F64" t="n">
+        <v>46.5</v>
       </c>
       <c r="G64" t="n">
-        <v>939.917</v>
+        <v>49.77</v>
+      </c>
+      <c r="H64" s="4" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="I64" t="n">
+        <v>38</v>
       </c>
       <c r="J64" t="n">
-        <v>1015.52</v>
+        <v>32.38</v>
+      </c>
+      <c r="K64" s="4" t="n">
+        <v>-5.62</v>
+      </c>
+      <c r="L64" t="n">
+        <v>20</v>
       </c>
       <c r="M64" t="n">
-        <v>663.3</v>
+        <v>18.49</v>
+      </c>
+      <c r="N64" s="4" t="n">
+        <v>-1.51</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>W/CODECHAOS BOA 27  Target Output : 960 Prs / 8H (</t>
+          <t>W/CODECHAOS 27 Target Output : 960 Prs / 8H (120 P</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>KI1387</t>
+          <t>KI5734</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>261.231</v>
+        <v>7.59</v>
       </c>
       <c r="G65" t="n">
-        <v>1646.91</v>
+        <v>31.33</v>
       </c>
       <c r="J65" t="n">
-        <v>1076.68</v>
+        <v>33.85</v>
       </c>
       <c r="M65" t="n">
-        <v>821.04</v>
+        <v>22.11</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAMBA GOLF  Target Output : 960 Prs / 8H (120 Prs </t>
+          <t>W/CODECHAOS BOA 27  Target Output : 960 Prs / 8H (</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JH6149</t>
+          <t>KI1387</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>274.6938</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G66" t="n">
-        <v>1309.6</v>
+        <v>54.9</v>
       </c>
       <c r="J66" t="n">
-        <v>871.42</v>
+        <v>35.89</v>
       </c>
       <c r="M66" t="n">
-        <v>200.86</v>
+        <v>27.37</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">adidas F50 ADIFRAME W   Target Output : 960 Prs / </t>
+          <t xml:space="preserve">SAMBA GOLF  Target Output : 960 Prs / 8H (120 Prs </t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JQ9556</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>89.44</v>
+          <t>JH6149</t>
+        </is>
       </c>
       <c r="D67" t="n">
-        <v>255.7145</v>
-      </c>
-      <c r="E67" s="2" t="n">
-        <v>166.2745</v>
-      </c>
-      <c r="F67" t="n">
-        <v>89.44</v>
+        <v>9.16</v>
       </c>
       <c r="G67" t="n">
-        <v>1541.38</v>
-      </c>
-      <c r="H67" s="2" t="n">
-        <v>1451.94</v>
-      </c>
-      <c r="I67" t="n">
-        <v>66.59999999999999</v>
+        <v>43.65</v>
       </c>
       <c r="J67" t="n">
-        <v>1413.83</v>
-      </c>
-      <c r="K67" s="2" t="n">
-        <v>1347.23</v>
-      </c>
-      <c r="L67" t="n">
-        <v>26.82</v>
+        <v>29.05</v>
       </c>
       <c r="M67" t="n">
-        <v>438.24</v>
-      </c>
-      <c r="N67" s="2" t="n">
-        <v>411.42</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SAMBA GOLF QUIET GOLF  Target Output : 960 Prs / 8</t>
+          <t xml:space="preserve">adidas F50 ADIFRAME W   Target Output : 960 Prs / </t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JP6885</t>
+          <t>JQ9556</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>93.40000000000001</v>
+        <v>17</v>
       </c>
       <c r="D68" t="n">
-        <v>252.7798</v>
-      </c>
-      <c r="E68" s="2" t="n">
-        <v>159.3798</v>
+        <v>8.52</v>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>-8.48</v>
       </c>
       <c r="F68" t="n">
-        <v>102.52</v>
+        <v>38</v>
       </c>
       <c r="G68" t="n">
-        <v>1507.52</v>
-      </c>
-      <c r="H68" s="2" t="n">
-        <v>1405</v>
+        <v>51.38</v>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>13.38</v>
       </c>
       <c r="I68" t="n">
-        <v>49.4</v>
+        <v>51</v>
       </c>
       <c r="J68" t="n">
-        <v>981.3099999999999</v>
-      </c>
-      <c r="K68" s="2" t="n">
-        <v>931.91</v>
+        <v>47.13</v>
+      </c>
+      <c r="K68" s="4" t="n">
+        <v>-3.87</v>
       </c>
       <c r="L68" t="n">
-        <v>16.03</v>
+        <v>15</v>
       </c>
       <c r="M68" t="n">
-        <v>165.44</v>
-      </c>
-      <c r="N68" s="2" t="n">
-        <v>149.41</v>
+        <v>14.61</v>
+      </c>
+      <c r="N68" s="4" t="n">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W Target Output : 960 Prs / 8H (120 P</t>
+          <t>SAMBA GOLF QUIET GOLF  Target Output : 960 Prs / 8</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>HQ7638</t>
+          <t>JP6885</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>123.25</v>
+        <v>16.5</v>
       </c>
       <c r="D69" t="n">
-        <v>597.8519</v>
-      </c>
-      <c r="E69" s="2" t="n">
-        <v>474.6019</v>
+        <v>8.43</v>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>-8.07</v>
       </c>
       <c r="F69" t="n">
-        <v>260.92</v>
+        <v>45</v>
       </c>
       <c r="G69" t="n">
-        <v>1674.95</v>
-      </c>
-      <c r="H69" s="2" t="n">
-        <v>1414.03</v>
+        <v>50.25</v>
+      </c>
+      <c r="H69" s="4" t="n">
+        <v>5.25</v>
       </c>
       <c r="I69" t="n">
-        <v>90.09999999999999</v>
+        <v>38.5</v>
       </c>
       <c r="J69" t="n">
-        <v>1583.12</v>
-      </c>
-      <c r="K69" s="2" t="n">
-        <v>1493.02</v>
+        <v>32.71</v>
+      </c>
+      <c r="K69" s="4" t="n">
+        <v>-5.79</v>
       </c>
       <c r="L69" t="n">
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="M69" t="n">
-        <v>161.37</v>
-      </c>
-      <c r="N69" s="2" t="n">
-        <v>151.47</v>
+        <v>5.51</v>
+      </c>
+      <c r="N69" s="4" t="n">
+        <v>-3.49</v>
       </c>
     </row>
     <row r="70">
@@ -3230,44 +3148,44 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HQ9304</t>
+          <t>HQ7638</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>114.51</v>
+        <v>24.5</v>
       </c>
       <c r="D70" t="n">
-        <v>459.1417</v>
-      </c>
-      <c r="E70" s="2" t="n">
-        <v>344.6317</v>
+        <v>19.93</v>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>-4.57</v>
       </c>
       <c r="F70" t="n">
-        <v>96.8</v>
+        <v>45</v>
       </c>
       <c r="G70" t="n">
-        <v>1516.95</v>
-      </c>
-      <c r="H70" s="2" t="n">
-        <v>1420.15</v>
+        <v>55.83</v>
+      </c>
+      <c r="H70" s="4" t="n">
+        <v>10.83</v>
       </c>
       <c r="I70" t="n">
-        <v>88.59999999999999</v>
+        <v>58</v>
       </c>
       <c r="J70" t="n">
-        <v>1434.62</v>
-      </c>
-      <c r="K70" s="2" t="n">
-        <v>1346.02</v>
+        <v>52.77</v>
+      </c>
+      <c r="K70" s="4" t="n">
+        <v>-5.23</v>
       </c>
       <c r="L70" t="n">
-        <v>9.9</v>
+        <v>5</v>
       </c>
       <c r="M70" t="n">
-        <v>161.37</v>
-      </c>
-      <c r="N70" s="2" t="n">
-        <v>151.47</v>
+        <v>5.38</v>
+      </c>
+      <c r="N70" s="4" t="n">
+        <v>0.38</v>
       </c>
     </row>
     <row r="71">
@@ -3278,44 +3196,44 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>KJ0644</t>
+          <t>HQ9304</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>121.17</v>
+        <v>25</v>
       </c>
       <c r="D71" t="n">
-        <v>597.7916</v>
-      </c>
-      <c r="E71" s="2" t="n">
-        <v>476.6216</v>
+        <v>15.3</v>
+      </c>
+      <c r="E71" s="4" t="n">
+        <v>-9.699999999999999</v>
       </c>
       <c r="F71" t="n">
-        <v>225.7933</v>
+        <v>45</v>
       </c>
       <c r="G71" t="n">
-        <v>1665.38</v>
-      </c>
-      <c r="H71" s="2" t="n">
-        <v>1439.5867</v>
+        <v>50.57</v>
+      </c>
+      <c r="H71" s="4" t="n">
+        <v>5.57</v>
       </c>
       <c r="I71" t="n">
-        <v>88.59999999999999</v>
+        <v>53</v>
       </c>
       <c r="J71" t="n">
-        <v>1583.12</v>
-      </c>
-      <c r="K71" s="2" t="n">
-        <v>1494.52</v>
+        <v>47.82</v>
+      </c>
+      <c r="K71" s="4" t="n">
+        <v>-5.18</v>
       </c>
       <c r="L71" t="n">
-        <v>9.9</v>
+        <v>5</v>
       </c>
       <c r="M71" t="n">
-        <v>161.37</v>
-      </c>
-      <c r="N71" s="2" t="n">
-        <v>151.47</v>
+        <v>5.38</v>
+      </c>
+      <c r="N71" s="4" t="n">
+        <v>0.38</v>
       </c>
     </row>
     <row r="72">
@@ -3326,44 +3244,44 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>LA7682</t>
+          <t>KJ0644</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>114.51</v>
+        <v>25</v>
       </c>
       <c r="D72" t="n">
-        <v>459.1417</v>
-      </c>
-      <c r="E72" s="2" t="n">
-        <v>344.6317</v>
+        <v>19.93</v>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>-5.07</v>
       </c>
       <c r="F72" t="n">
-        <v>96.8</v>
+        <v>46</v>
       </c>
       <c r="G72" t="n">
-        <v>1516.95</v>
-      </c>
-      <c r="H72" s="2" t="n">
-        <v>1420.15</v>
+        <v>55.51</v>
+      </c>
+      <c r="H72" s="4" t="n">
+        <v>9.51</v>
       </c>
       <c r="I72" t="n">
-        <v>88.59999999999999</v>
+        <v>58</v>
       </c>
       <c r="J72" t="n">
-        <v>1434.62</v>
-      </c>
-      <c r="K72" s="2" t="n">
-        <v>1346.02</v>
+        <v>52.77</v>
+      </c>
+      <c r="K72" s="4" t="n">
+        <v>-5.23</v>
       </c>
       <c r="L72" t="n">
-        <v>9.9</v>
+        <v>5</v>
       </c>
       <c r="M72" t="n">
-        <v>161.37</v>
-      </c>
-      <c r="N72" s="2" t="n">
-        <v>151.47</v>
+        <v>5.38</v>
+      </c>
+      <c r="N72" s="4" t="n">
+        <v>0.38</v>
       </c>
     </row>
     <row r="73">
@@ -3374,92 +3292,92 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>JQ6439</t>
+          <t>LA7682</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>116.21</v>
+        <v>25</v>
       </c>
       <c r="D73" t="n">
-        <v>310.0873</v>
-      </c>
-      <c r="E73" s="2" t="n">
-        <v>193.8773</v>
+        <v>15.3</v>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>-9.699999999999999</v>
       </c>
       <c r="F73" t="n">
-        <v>116.21</v>
+        <v>45</v>
       </c>
       <c r="G73" t="n">
-        <v>1456.95</v>
-      </c>
-      <c r="H73" s="2" t="n">
-        <v>1340.74</v>
+        <v>50.57</v>
+      </c>
+      <c r="H73" s="4" t="n">
+        <v>5.57</v>
       </c>
       <c r="I73" t="n">
-        <v>79.59999999999999</v>
+        <v>53</v>
       </c>
       <c r="J73" t="n">
-        <v>1686.19</v>
-      </c>
-      <c r="K73" s="2" t="n">
-        <v>1606.59</v>
+        <v>47.82</v>
+      </c>
+      <c r="K73" s="4" t="n">
+        <v>-5.18</v>
       </c>
       <c r="L73" t="n">
-        <v>9.9</v>
+        <v>5</v>
       </c>
       <c r="M73" t="n">
-        <v>161.37</v>
-      </c>
-      <c r="N73" s="2" t="n">
-        <v>151.47</v>
+        <v>5.38</v>
+      </c>
+      <c r="N73" s="4" t="n">
+        <v>0.38</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADISTAR XLG 2.0 W Target Output : 960 Prs/8H (120 </t>
+          <t>GHOST SPRINT W Target Output : 960 Prs / 8H (120 P</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>KJ7824</t>
+          <t>JQ6439</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>79.83</v>
+        <v>22.5</v>
       </c>
       <c r="D74" t="n">
-        <v>210.4731</v>
-      </c>
-      <c r="E74" s="2" t="n">
-        <v>130.6431</v>
+        <v>10.34</v>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>-12.16</v>
       </c>
       <c r="F74" t="n">
-        <v>69.95999999999999</v>
+        <v>45</v>
       </c>
       <c r="G74" t="n">
-        <v>1031.28</v>
-      </c>
-      <c r="H74" s="2" t="n">
-        <v>961.3200000000001</v>
+        <v>48.57</v>
+      </c>
+      <c r="H74" s="4" t="n">
+        <v>3.57</v>
       </c>
       <c r="I74" t="n">
-        <v>50.1</v>
+        <v>61</v>
       </c>
       <c r="J74" t="n">
-        <v>1147.74</v>
-      </c>
-      <c r="K74" s="2" t="n">
-        <v>1097.64</v>
+        <v>56.21</v>
+      </c>
+      <c r="K74" s="4" t="n">
+        <v>-4.79</v>
       </c>
       <c r="L74" t="n">
-        <v>45.2</v>
+        <v>5</v>
       </c>
       <c r="M74" t="n">
-        <v>867.24</v>
-      </c>
-      <c r="N74" s="2" t="n">
-        <v>822.04</v>
+        <v>5.38</v>
+      </c>
+      <c r="N74" s="4" t="n">
+        <v>0.38</v>
       </c>
     </row>
     <row r="75">
@@ -3470,44 +3388,44 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>KJ9163</t>
+          <t>KJ7824</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>87.37</v>
+        <v>10.5</v>
       </c>
       <c r="D75" t="n">
-        <v>210.4231</v>
-      </c>
-      <c r="E75" s="2" t="n">
-        <v>123.0531</v>
+        <v>7.02</v>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>-3.48</v>
       </c>
       <c r="F75" t="n">
-        <v>69.95999999999999</v>
+        <v>36.5</v>
       </c>
       <c r="G75" t="n">
-        <v>1031.28</v>
-      </c>
-      <c r="H75" s="2" t="n">
-        <v>961.3200000000001</v>
+        <v>34.38</v>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>-2.12</v>
       </c>
       <c r="I75" t="n">
-        <v>45.22</v>
+        <v>44</v>
       </c>
       <c r="J75" t="n">
-        <v>1147.74</v>
-      </c>
-      <c r="K75" s="2" t="n">
-        <v>1102.52</v>
+        <v>38.26</v>
+      </c>
+      <c r="K75" s="4" t="n">
+        <v>-5.74</v>
       </c>
       <c r="L75" t="n">
-        <v>50.1</v>
+        <v>31</v>
       </c>
       <c r="M75" t="n">
-        <v>857.34</v>
-      </c>
-      <c r="N75" s="2" t="n">
-        <v>807.24</v>
+        <v>28.91</v>
+      </c>
+      <c r="N75" s="4" t="n">
+        <v>-2.09</v>
       </c>
     </row>
     <row r="76">
@@ -3518,44 +3436,44 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>KZ9155</t>
+          <t>KJ9163</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>80.95</v>
+        <v>10.5</v>
       </c>
       <c r="D76" t="n">
-        <v>320.4717</v>
-      </c>
-      <c r="E76" s="2" t="n">
-        <v>239.5217</v>
+        <v>7.01</v>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>-3.49</v>
       </c>
       <c r="F76" t="n">
-        <v>72.7467</v>
+        <v>36.5</v>
       </c>
       <c r="G76" t="n">
-        <v>1031.28</v>
-      </c>
-      <c r="H76" s="2" t="n">
-        <v>958.5333000000001</v>
+        <v>34.38</v>
+      </c>
+      <c r="H76" s="4" t="n">
+        <v>-2.12</v>
       </c>
       <c r="I76" t="n">
-        <v>50.1</v>
+        <v>44</v>
       </c>
       <c r="J76" t="n">
-        <v>1147.74</v>
-      </c>
-      <c r="K76" s="2" t="n">
-        <v>1097.64</v>
+        <v>38.26</v>
+      </c>
+      <c r="K76" s="4" t="n">
+        <v>-5.74</v>
       </c>
       <c r="L76" t="n">
-        <v>45.22</v>
+        <v>31</v>
       </c>
       <c r="M76" t="n">
-        <v>857.34</v>
-      </c>
-      <c r="N76" s="2" t="n">
-        <v>812.12</v>
+        <v>28.58</v>
+      </c>
+      <c r="N76" s="4" t="n">
+        <v>-2.42</v>
       </c>
     </row>
     <row r="77">
@@ -3566,116 +3484,140 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>LA1813</t>
+          <t>KZ9155</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>87.37</v>
+        <v>14.5</v>
       </c>
       <c r="D77" t="n">
-        <v>259.1831</v>
-      </c>
-      <c r="E77" s="2" t="n">
-        <v>171.8131</v>
+        <v>10.68</v>
+      </c>
+      <c r="E77" s="4" t="n">
+        <v>-3.82</v>
       </c>
       <c r="F77" t="n">
-        <v>69.95999999999999</v>
+        <v>36.5</v>
       </c>
       <c r="G77" t="n">
-        <v>1330.33</v>
-      </c>
-      <c r="H77" s="2" t="n">
-        <v>1260.37</v>
+        <v>34.38</v>
+      </c>
+      <c r="H77" s="4" t="n">
+        <v>-2.12</v>
       </c>
       <c r="I77" t="n">
-        <v>50.1</v>
+        <v>44</v>
       </c>
       <c r="J77" t="n">
-        <v>1153.79</v>
-      </c>
-      <c r="K77" s="2" t="n">
-        <v>1103.69</v>
+        <v>38.26</v>
+      </c>
+      <c r="K77" s="4" t="n">
+        <v>-5.74</v>
       </c>
       <c r="L77" t="n">
-        <v>45.22</v>
+        <v>31</v>
       </c>
       <c r="M77" t="n">
-        <v>857.34</v>
-      </c>
-      <c r="N77" s="2" t="n">
-        <v>812.12</v>
+        <v>28.58</v>
+      </c>
+      <c r="N77" s="4" t="n">
+        <v>-2.42</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>GHOST SPRINT BALLET Target Output: 960 Prs/8H (120</t>
+          <t xml:space="preserve">ADISTAR XLG 2.0 W Target Output : 960 Prs/8H (120 </t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>HQ7636</t>
+          <t>LA1813</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>85.78</v>
+        <v>11</v>
       </c>
       <c r="D78" t="n">
-        <v>320.3386</v>
-      </c>
-      <c r="E78" s="2" t="n">
-        <v>234.5586</v>
+        <v>8.640000000000001</v>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>-2.36</v>
       </c>
       <c r="F78" t="n">
-        <v>96.8</v>
+        <v>46</v>
       </c>
       <c r="G78" t="n">
-        <v>1414.2712</v>
-      </c>
-      <c r="H78" s="2" t="n">
-        <v>1317.4712</v>
+        <v>44.34</v>
+      </c>
+      <c r="H78" s="4" t="n">
+        <v>-1.66</v>
       </c>
       <c r="I78" t="n">
-        <v>85.09999999999999</v>
+        <v>44</v>
       </c>
       <c r="J78" t="n">
-        <v>1416.14</v>
-      </c>
-      <c r="K78" s="2" t="n">
-        <v>1331.04</v>
+        <v>38.46</v>
+      </c>
+      <c r="K78" s="4" t="n">
+        <v>-5.54</v>
       </c>
       <c r="L78" t="n">
-        <v>9.9</v>
+        <v>31</v>
       </c>
       <c r="M78" t="n">
-        <v>161.37</v>
-      </c>
-      <c r="N78" s="2" t="n">
-        <v>151.47</v>
+        <v>28.58</v>
+      </c>
+      <c r="N78" s="4" t="n">
+        <v>-2.42</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL Target Output : 960 Prs / 8H (120</t>
+          <t>GHOST SPRINT BALLET Target Output: 960 Prs/8H (120</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>KI5241</t>
-        </is>
+          <t>HQ7636</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>17.5</v>
       </c>
       <c r="D79" t="n">
-        <v>194.0584</v>
+        <v>10.68</v>
+      </c>
+      <c r="E79" s="4" t="n">
+        <v>-6.82</v>
+      </c>
+      <c r="F79" t="n">
+        <v>38</v>
       </c>
       <c r="G79" t="n">
-        <v>1057.6</v>
+        <v>47.14</v>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="I79" t="n">
+        <v>51.5</v>
       </c>
       <c r="J79" t="n">
-        <v>842.039</v>
+        <v>47.2</v>
+      </c>
+      <c r="K79" s="4" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="L79" t="n">
+        <v>5</v>
       </c>
       <c r="M79" t="n">
-        <v>120.516</v>
+        <v>5.38</v>
+      </c>
+      <c r="N79" s="4" t="n">
+        <v>0.38</v>
       </c>
     </row>
     <row r="80">
@@ -3686,140 +3628,116 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>KK3028</t>
+          <t>KI5241</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>212.4645</v>
+        <v>6.47</v>
       </c>
       <c r="G80" t="n">
-        <v>1114.91</v>
+        <v>35.25</v>
       </c>
       <c r="J80" t="n">
-        <v>773.509</v>
+        <v>28.07</v>
       </c>
       <c r="M80" t="n">
-        <v>120.516</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TOKYO W  Target Output : 960 Prs / 8H (120 Prs / H</t>
+          <t>HANDBALL SPEZIAL Target Output : 960 Prs / 8H (120</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>HQ9511</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>168.2267</v>
+          <t>KK3028</t>
+        </is>
       </c>
       <c r="D81" t="n">
-        <v>350.39</v>
-      </c>
-      <c r="E81" s="2" t="n">
-        <v>182.1633</v>
-      </c>
-      <c r="F81" t="n">
-        <v>168.2267</v>
+        <v>7.08</v>
       </c>
       <c r="G81" t="n">
-        <v>1656.88</v>
-      </c>
-      <c r="H81" s="2" t="n">
-        <v>1488.6533</v>
-      </c>
-      <c r="I81" t="n">
-        <v>51.1</v>
+        <v>37.16</v>
       </c>
       <c r="J81" t="n">
-        <v>991.87</v>
-      </c>
-      <c r="K81" s="2" t="n">
-        <v>940.77</v>
-      </c>
-      <c r="L81" t="n">
-        <v>4.9</v>
+        <v>25.78</v>
       </c>
       <c r="M81" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N81" s="2" t="n">
-        <v>18.42</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TOKYO W  Target Output: 960 Prs / 8H (120 Prs / Ho</t>
+          <t>TOKYO W  Target Output : 960 Prs / 8H (120 Prs / H</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>KJ7539</t>
-        </is>
+          <t>HQ9511</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>11</v>
       </c>
       <c r="D82" t="n">
-        <v>153.284</v>
+        <v>11.68</v>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F82" t="n">
+        <v>36</v>
       </c>
       <c r="G82" t="n">
-        <v>939.13</v>
+        <v>55.23</v>
+      </c>
+      <c r="H82" s="4" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="I82" t="n">
+        <v>38.5</v>
       </c>
       <c r="J82" t="n">
-        <v>982.08</v>
+        <v>33.06</v>
+      </c>
+      <c r="K82" s="4" t="n">
+        <v>-5.44</v>
+      </c>
+      <c r="L82" t="n">
+        <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>23.32</v>
+        <v>0.78</v>
+      </c>
+      <c r="N82" s="4" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TOKYO W  Target Output : 960 Prs / 8H (120 Prs / H</t>
+          <t>TOKYO W  Target Output: 960 Prs / 8H (120 Prs / Ho</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>KJ8367</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>72.88</v>
+          <t>KJ7539</t>
+        </is>
       </c>
       <c r="D83" t="n">
-        <v>361.2838</v>
-      </c>
-      <c r="E83" s="2" t="n">
-        <v>288.4038</v>
-      </c>
-      <c r="F83" t="n">
-        <v>168.2267</v>
+        <v>5.11</v>
       </c>
       <c r="G83" t="n">
-        <v>1075.53</v>
-      </c>
-      <c r="H83" s="2" t="n">
-        <v>907.3033</v>
-      </c>
-      <c r="I83" t="n">
-        <v>51.1</v>
+        <v>31.3</v>
       </c>
       <c r="J83" t="n">
-        <v>991.87</v>
-      </c>
-      <c r="K83" s="2" t="n">
-        <v>940.77</v>
-      </c>
-      <c r="L83" t="n">
-        <v>4.9</v>
+        <v>32.74</v>
       </c>
       <c r="M83" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N83" s="2" t="n">
-        <v>18.42</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="84">
@@ -3830,44 +3748,44 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>KK0030</t>
+          <t>KJ8367</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>168.2267</v>
+        <v>16</v>
       </c>
       <c r="D84" t="n">
-        <v>333.4714</v>
-      </c>
-      <c r="E84" s="2" t="n">
-        <v>165.2447</v>
+        <v>12.04</v>
+      </c>
+      <c r="E84" s="4" t="n">
+        <v>-3.96</v>
       </c>
       <c r="F84" t="n">
-        <v>168.2267</v>
+        <v>28</v>
       </c>
       <c r="G84" t="n">
-        <v>1124.81</v>
-      </c>
-      <c r="H84" s="2" t="n">
-        <v>956.5833</v>
+        <v>35.85</v>
+      </c>
+      <c r="H84" s="4" t="n">
+        <v>7.85</v>
       </c>
       <c r="I84" t="n">
-        <v>51.1</v>
+        <v>38.5</v>
       </c>
       <c r="J84" t="n">
-        <v>991.87</v>
-      </c>
-      <c r="K84" s="2" t="n">
-        <v>940.77</v>
+        <v>33.06</v>
+      </c>
+      <c r="K84" s="4" t="n">
+        <v>-5.44</v>
       </c>
       <c r="L84" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N84" s="2" t="n">
-        <v>18.42</v>
+        <v>0.78</v>
+      </c>
+      <c r="N84" s="4" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="85">
@@ -3878,92 +3796,92 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>KK2621</t>
+          <t>KK0030</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>164.1167</v>
+        <v>11.5</v>
       </c>
       <c r="D85" t="n">
-        <v>361.4905</v>
-      </c>
-      <c r="E85" s="2" t="n">
-        <v>197.3738</v>
+        <v>11.12</v>
+      </c>
+      <c r="E85" s="4" t="n">
+        <v>-0.38</v>
       </c>
       <c r="F85" t="n">
-        <v>164.1167</v>
+        <v>29</v>
       </c>
       <c r="G85" t="n">
-        <v>2340.5336</v>
-      </c>
-      <c r="H85" s="2" t="n">
-        <v>2176.417</v>
+        <v>37.49</v>
+      </c>
+      <c r="H85" s="4" t="n">
+        <v>8.49</v>
       </c>
       <c r="I85" t="n">
-        <v>51.1</v>
+        <v>38.5</v>
       </c>
       <c r="J85" t="n">
-        <v>926.97</v>
-      </c>
-      <c r="K85" s="2" t="n">
-        <v>875.87</v>
+        <v>33.06</v>
+      </c>
+      <c r="K85" s="4" t="n">
+        <v>-5.44</v>
       </c>
       <c r="L85" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N85" s="2" t="n">
-        <v>18.42</v>
+        <v>0.78</v>
+      </c>
+      <c r="N85" s="4" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W Target Output : 960 Prs / 8H (120 P</t>
+          <t>TOKYO W  Target Output : 960 Prs / 8H (120 Prs / H</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>HQ3330</t>
+          <t>KK2621</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>123.25</v>
+        <v>12.5</v>
       </c>
       <c r="D86" t="n">
-        <v>611.5984999999999</v>
-      </c>
-      <c r="E86" s="2" t="n">
-        <v>488.3485</v>
+        <v>12.05</v>
+      </c>
+      <c r="E86" s="4" t="n">
+        <v>-0.45</v>
       </c>
       <c r="F86" t="n">
-        <v>225.7933</v>
+        <v>38</v>
       </c>
       <c r="G86" t="n">
-        <v>1641.95</v>
-      </c>
-      <c r="H86" s="2" t="n">
-        <v>1416.1567</v>
+        <v>78.02</v>
+      </c>
+      <c r="H86" s="4" t="n">
+        <v>40.02</v>
       </c>
       <c r="I86" t="n">
-        <v>90.09999999999999</v>
+        <v>35.5</v>
       </c>
       <c r="J86" t="n">
-        <v>1574.32</v>
-      </c>
-      <c r="K86" s="2" t="n">
-        <v>1484.22</v>
+        <v>30.9</v>
+      </c>
+      <c r="K86" s="4" t="n">
+        <v>-4.6</v>
       </c>
       <c r="L86" t="n">
-        <v>9.9</v>
+        <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>161.37</v>
-      </c>
-      <c r="N86" s="2" t="n">
-        <v>151.47</v>
+        <v>0.78</v>
+      </c>
+      <c r="N86" s="4" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="87">
@@ -3978,40 +3896,40 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>123.25</v>
+        <v>23.5</v>
       </c>
       <c r="D87" t="n">
-        <v>611.5984999999999</v>
-      </c>
-      <c r="E87" s="2" t="n">
-        <v>488.3485</v>
+        <v>20.39</v>
+      </c>
+      <c r="E87" s="4" t="n">
+        <v>-3.11</v>
       </c>
       <c r="F87" t="n">
-        <v>225.7933</v>
+        <v>45</v>
       </c>
       <c r="G87" t="n">
-        <v>1641.95</v>
-      </c>
-      <c r="H87" s="2" t="n">
-        <v>1416.1567</v>
+        <v>54.73</v>
+      </c>
+      <c r="H87" s="4" t="n">
+        <v>9.73</v>
       </c>
       <c r="I87" t="n">
-        <v>90.09999999999999</v>
+        <v>58</v>
       </c>
       <c r="J87" t="n">
-        <v>1574.32</v>
-      </c>
-      <c r="K87" s="2" t="n">
-        <v>1484.22</v>
+        <v>52.48</v>
+      </c>
+      <c r="K87" s="4" t="n">
+        <v>-5.52</v>
       </c>
       <c r="L87" t="n">
-        <v>9.9</v>
+        <v>5</v>
       </c>
       <c r="M87" t="n">
-        <v>161.37</v>
-      </c>
-      <c r="N87" s="2" t="n">
-        <v>151.47</v>
+        <v>5.38</v>
+      </c>
+      <c r="N87" s="4" t="n">
+        <v>0.38</v>
       </c>
     </row>
     <row r="88">
@@ -4022,44 +3940,44 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>KI4567</t>
+          <t>HQ3330</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>102.27</v>
+        <v>23.5</v>
       </c>
       <c r="D88" t="n">
-        <v>544.5099</v>
-      </c>
-      <c r="E88" s="2" t="n">
-        <v>442.2399</v>
+        <v>20.39</v>
+      </c>
+      <c r="E88" s="4" t="n">
+        <v>-3.11</v>
       </c>
       <c r="F88" t="n">
-        <v>236.5</v>
+        <v>45</v>
       </c>
       <c r="G88" t="n">
-        <v>1571.51</v>
-      </c>
-      <c r="H88" s="2" t="n">
-        <v>1335.01</v>
+        <v>54.73</v>
+      </c>
+      <c r="H88" s="4" t="n">
+        <v>9.73</v>
       </c>
       <c r="I88" t="n">
-        <v>88.59999999999999</v>
+        <v>58</v>
       </c>
       <c r="J88" t="n">
-        <v>1583.12</v>
-      </c>
-      <c r="K88" s="2" t="n">
-        <v>1494.52</v>
+        <v>52.48</v>
+      </c>
+      <c r="K88" s="4" t="n">
+        <v>-5.52</v>
       </c>
       <c r="L88" t="n">
-        <v>9.9</v>
+        <v>5</v>
       </c>
       <c r="M88" t="n">
-        <v>138.05</v>
-      </c>
-      <c r="N88" s="2" t="n">
-        <v>128.15</v>
+        <v>5.38</v>
+      </c>
+      <c r="N88" s="4" t="n">
+        <v>0.38</v>
       </c>
     </row>
     <row r="89">
@@ -4070,38 +3988,44 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>KI4569</t>
+          <t>KI4567</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>129.61</v>
+        <v>17.5</v>
       </c>
       <c r="D89" t="n">
-        <v>1988.5988</v>
-      </c>
-      <c r="E89" s="2" t="n">
-        <v>1858.9888</v>
+        <v>18.15</v>
+      </c>
+      <c r="E89" s="4" t="n">
+        <v>0.65</v>
       </c>
       <c r="F89" t="n">
-        <v>130.46</v>
+        <v>47</v>
       </c>
       <c r="G89" t="n">
-        <v>1589.38</v>
-      </c>
-      <c r="H89" s="2" t="n">
-        <v>1458.92</v>
+        <v>52.38</v>
+      </c>
+      <c r="H89" s="4" t="n">
+        <v>5.38</v>
       </c>
       <c r="I89" t="n">
-        <v>91.59999999999999</v>
+        <v>57</v>
       </c>
       <c r="J89" t="n">
-        <v>1565.52</v>
-      </c>
-      <c r="K89" s="2" t="n">
-        <v>1473.92</v>
+        <v>52.77</v>
+      </c>
+      <c r="K89" s="4" t="n">
+        <v>-4.23</v>
       </c>
       <c r="L89" t="n">
-        <v>9.9</v>
+        <v>5</v>
+      </c>
+      <c r="M89" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N89" s="4" t="n">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="90">
@@ -4112,314 +4036,290 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>KI4571</t>
+          <t>KI4569</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>118.09</v>
+        <v>29.5</v>
       </c>
       <c r="D90" t="n">
-        <v>306.7094</v>
-      </c>
-      <c r="E90" s="2" t="n">
-        <v>188.6194</v>
+        <v>66.29000000000001</v>
+      </c>
+      <c r="E90" s="4" t="n">
+        <v>36.79</v>
       </c>
       <c r="F90" t="n">
-        <v>96.8</v>
+        <v>46</v>
       </c>
       <c r="G90" t="n">
-        <v>1547.75</v>
-      </c>
-      <c r="H90" s="2" t="n">
-        <v>1450.95</v>
+        <v>52.98</v>
+      </c>
+      <c r="H90" s="4" t="n">
+        <v>6.98</v>
       </c>
       <c r="I90" t="n">
-        <v>91.59999999999999</v>
+        <v>58</v>
       </c>
       <c r="J90" t="n">
-        <v>1686.19</v>
-      </c>
-      <c r="K90" s="2" t="n">
-        <v>1594.59</v>
+        <v>52.18</v>
+      </c>
+      <c r="K90" s="4" t="n">
+        <v>-5.82</v>
       </c>
       <c r="L90" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="M90" t="n">
-        <v>161.37</v>
-      </c>
-      <c r="N90" s="2" t="n">
-        <v>151.47</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>W/ GAZELLE GOLF Target Output : 480 Prs / 8H 60 Pr</t>
+          <t>GHOST SPRINT W Target Output : 960 Prs / 8H (120 P</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>KH8402</t>
+          <t>KI4571</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>108.46</v>
+        <v>23.5</v>
       </c>
       <c r="D91" t="n">
-        <v>318.3562</v>
-      </c>
-      <c r="E91" s="2" t="n">
-        <v>209.8962</v>
+        <v>10.22</v>
+      </c>
+      <c r="E91" s="4" t="n">
+        <v>-13.28</v>
       </c>
       <c r="F91" t="n">
-        <v>108.46</v>
+        <v>46</v>
       </c>
       <c r="G91" t="n">
-        <v>1147.817</v>
-      </c>
-      <c r="H91" s="2" t="n">
-        <v>1039.357</v>
+        <v>51.59</v>
+      </c>
+      <c r="H91" s="4" t="n">
+        <v>5.59</v>
       </c>
       <c r="I91" t="n">
-        <v>48.65</v>
+        <v>61</v>
       </c>
       <c r="J91" t="n">
-        <v>973.0599999999999</v>
-      </c>
-      <c r="K91" s="2" t="n">
-        <v>924.41</v>
+        <v>56.21</v>
+      </c>
+      <c r="K91" s="4" t="n">
+        <v>-4.79</v>
       </c>
       <c r="L91" t="n">
-        <v>26.31</v>
+        <v>5</v>
+      </c>
+      <c r="M91" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="N91" s="4" t="n">
+        <v>0.38</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>OZGAIA W Target Output : 960 Prs / 8H (120 Prs / H</t>
+          <t>W GAZELLE GOLF Target Output : 960 Prs / 8H (120 P</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>IG6044</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>239.8497</v>
-      </c>
-      <c r="G92" t="n">
-        <v>1210.7659</v>
-      </c>
-      <c r="J92" t="n">
-        <v>913.1331</v>
-      </c>
-      <c r="M92" t="n">
-        <v>612.8099999999999</v>
+          <t>KH8402</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F92" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="I92" t="n">
+        <v>38</v>
+      </c>
+      <c r="L92" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>OZWEEGO  Target Output :960 Prs / 8H (120 Prs / Ho</t>
+          <t>OZGAIA W Target Output : 960 Prs / 8H (120 Prs / H</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EE6999</t>
+          <t>IG6044</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>314.8636</v>
+        <v>7.99</v>
       </c>
       <c r="G93" t="n">
-        <v>970.5151</v>
+        <v>40.36</v>
       </c>
       <c r="J93" t="n">
-        <v>912.3124</v>
+        <v>30.44</v>
       </c>
       <c r="M93" t="n">
-        <v>416.44</v>
+        <v>20.43</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>OZWEEGO  Target Output : 960 Prs / 8H (120 Prs / H</t>
+          <t>OZWEEGO  Target Output :960 Prs / 8H (120 Prs / Ho</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>JR5933</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>105.84</v>
+          <t>EE6999</t>
+        </is>
       </c>
       <c r="D94" t="n">
-        <v>225.7416</v>
-      </c>
-      <c r="E94" s="2" t="n">
-        <v>119.9016</v>
-      </c>
-      <c r="F94" t="n">
-        <v>134.42</v>
+        <v>10.5</v>
       </c>
       <c r="G94" t="n">
-        <v>1509.7851</v>
-      </c>
-      <c r="H94" s="2" t="n">
-        <v>1375.3651</v>
-      </c>
-      <c r="I94" t="n">
-        <v>45.1</v>
+        <v>32.35</v>
       </c>
       <c r="J94" t="n">
-        <v>839.4452</v>
-      </c>
-      <c r="K94" s="2" t="n">
-        <v>794.3452</v>
-      </c>
-      <c r="L94" t="n">
-        <v>26.25</v>
+        <v>30.41</v>
+      </c>
+      <c r="M94" t="n">
+        <v>13.88</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GOLFLITE MAX  Target Output :960 Prs / 8H (120 Prs</t>
+          <t>OZWEEGO  Target Output : 960 Prs / 8H (120 Prs / H</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>IF3040</t>
+          <t>JR5933</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>76.18000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="D95" t="n">
-        <v>8294.9128</v>
-      </c>
-      <c r="E95" s="2" t="n">
-        <v>8218.7328</v>
+        <v>7.52</v>
+      </c>
+      <c r="E95" s="4" t="n">
+        <v>-5.98</v>
       </c>
       <c r="F95" t="n">
-        <v>76.18000000000001</v>
+        <v>54</v>
       </c>
       <c r="G95" t="n">
-        <v>873.1799999999999</v>
-      </c>
-      <c r="H95" s="2" t="n">
-        <v>797</v>
+        <v>50.33</v>
+      </c>
+      <c r="H95" s="4" t="n">
+        <v>-3.67</v>
       </c>
       <c r="I95" t="n">
-        <v>48.9</v>
+        <v>35</v>
       </c>
       <c r="J95" t="n">
-        <v>906.4931</v>
-      </c>
-      <c r="K95" s="2" t="n">
-        <v>857.5931</v>
+        <v>27.98</v>
+      </c>
+      <c r="K95" s="4" t="n">
+        <v>-7.02</v>
       </c>
       <c r="L95" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="M95" t="n">
-        <v>377.641</v>
-      </c>
-      <c r="N95" s="2" t="n">
-        <v>356.051</v>
+        <v>17</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SAMBA (RE) Target Output : 960 Prs / 8H (120 Prs /</t>
+          <t>GOLFLITE MAX  Target Output :960 Prs / 8H (120 Prs</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>IH6000</t>
+          <t>IF3040</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>197.78</v>
+        <v>13</v>
       </c>
       <c r="D96" t="n">
-        <v>583.6872</v>
-      </c>
-      <c r="E96" s="2" t="n">
-        <v>385.9072</v>
+        <v>276.5</v>
+      </c>
+      <c r="E96" s="4" t="n">
+        <v>263.5</v>
       </c>
       <c r="F96" t="n">
-        <v>197.78</v>
+        <v>30.5</v>
       </c>
       <c r="G96" t="n">
-        <v>943.83</v>
-      </c>
-      <c r="H96" s="2" t="n">
-        <v>746.05</v>
+        <v>29.11</v>
+      </c>
+      <c r="H96" s="4" t="n">
+        <v>-1.39</v>
       </c>
       <c r="I96" t="n">
-        <v>47.9</v>
+        <v>36.5</v>
       </c>
       <c r="J96" t="n">
-        <v>955.309</v>
-      </c>
-      <c r="K96" s="2" t="n">
-        <v>907.409</v>
+        <v>30.22</v>
+      </c>
+      <c r="K96" s="4" t="n">
+        <v>-6.28</v>
       </c>
       <c r="L96" t="n">
-        <v>4.9</v>
+        <v>14</v>
+      </c>
+      <c r="M96" t="n">
+        <v>12.59</v>
+      </c>
+      <c r="N96" s="4" t="n">
+        <v>-1.41</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>TOKYO W MJ Target Output : 960 Prs / 8H (120 Prs /</t>
+          <t>SAMBA (RE) Target Output : 960 Prs / 8H (120 Prs /</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>KI4312</t>
+          <t>IH6000</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>102.91</v>
+        <v>16</v>
       </c>
       <c r="D97" t="n">
-        <v>566.7285000000001</v>
-      </c>
-      <c r="E97" s="2" t="n">
-        <v>463.8185</v>
+        <v>19.46</v>
+      </c>
+      <c r="E97" s="4" t="n">
+        <v>3.46</v>
       </c>
       <c r="F97" t="n">
-        <v>157.3</v>
+        <v>28</v>
       </c>
       <c r="G97" t="n">
-        <v>1421.36</v>
-      </c>
-      <c r="H97" s="2" t="n">
-        <v>1264.06</v>
+        <v>31.46</v>
+      </c>
+      <c r="H97" s="4" t="n">
+        <v>3.46</v>
       </c>
       <c r="I97" t="n">
-        <v>46.6</v>
+        <v>39</v>
       </c>
       <c r="J97" t="n">
-        <v>946.77</v>
-      </c>
-      <c r="K97" s="2" t="n">
-        <v>900.17</v>
+        <v>31.84</v>
+      </c>
+      <c r="K97" s="4" t="n">
+        <v>-7.16</v>
       </c>
       <c r="L97" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M97" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N97" s="2" t="n">
-        <v>18.42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -4430,44 +4330,20 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>KI5323</t>
+          <t>KI4312</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>101.4</v>
-      </c>
-      <c r="D98" t="n">
-        <v>566.7285000000001</v>
-      </c>
-      <c r="E98" s="2" t="n">
-        <v>465.3285</v>
+        <v>20</v>
       </c>
       <c r="F98" t="n">
-        <v>157.3</v>
-      </c>
-      <c r="G98" t="n">
-        <v>1476.91</v>
-      </c>
-      <c r="H98" s="2" t="n">
-        <v>1319.61</v>
+        <v>36</v>
       </c>
       <c r="I98" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="J98" t="n">
-        <v>946.77</v>
-      </c>
-      <c r="K98" s="2" t="n">
-        <v>900.17</v>
+        <v>37</v>
       </c>
       <c r="L98" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M98" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N98" s="2" t="n">
-        <v>18.42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -4478,164 +4354,152 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>KJ8377</t>
+          <t>KI5323</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>181.5</v>
+        <v>20</v>
       </c>
       <c r="D99" t="n">
-        <v>566.478</v>
-      </c>
-      <c r="E99" s="2" t="n">
-        <v>384.978</v>
+        <v>25.09</v>
+      </c>
+      <c r="E99" s="4" t="n">
+        <v>5.09</v>
       </c>
       <c r="F99" t="n">
-        <v>161.4067</v>
+        <v>38</v>
       </c>
       <c r="G99" t="n">
-        <v>1653.25</v>
-      </c>
-      <c r="H99" s="2" t="n">
-        <v>1491.8433</v>
+        <v>49.23</v>
+      </c>
+      <c r="H99" s="4" t="n">
+        <v>11.23</v>
       </c>
       <c r="I99" t="n">
-        <v>46.6</v>
+        <v>37</v>
       </c>
       <c r="J99" t="n">
-        <v>878.5700000000001</v>
-      </c>
-      <c r="K99" s="2" t="n">
-        <v>831.97</v>
+        <v>33.33</v>
+      </c>
+      <c r="K99" s="4" t="n">
+        <v>-3.67</v>
       </c>
       <c r="L99" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N99" s="2" t="n">
-        <v>18.42</v>
+        <v>0.78</v>
+      </c>
+      <c r="N99" s="4" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>TOKYO W  Target Output : 960 Prs / 8H (120 Prs / H</t>
+          <t>TOKYO W MJ Target Output : 960 Prs / 8H (120 Prs /</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>IH6609</t>
+          <t>KJ8377</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>79.03</v>
+        <v>18.5</v>
       </c>
       <c r="D100" t="n">
-        <v>143.3496</v>
-      </c>
-      <c r="E100" s="2" t="n">
-        <v>64.31959999999999</v>
+        <v>18.88</v>
+      </c>
+      <c r="E100" s="4" t="n">
+        <v>0.38</v>
       </c>
       <c r="F100" t="n">
-        <v>161.4067</v>
+        <v>38</v>
       </c>
       <c r="G100" t="n">
-        <v>1159.68</v>
-      </c>
-      <c r="H100" s="2" t="n">
-        <v>998.2732999999999</v>
+        <v>55.11</v>
+      </c>
+      <c r="H100" s="4" t="n">
+        <v>17.11</v>
       </c>
       <c r="I100" t="n">
-        <v>51.1</v>
+        <v>35</v>
       </c>
       <c r="J100" t="n">
-        <v>982.1900000000001</v>
-      </c>
-      <c r="K100" s="2" t="n">
-        <v>931.09</v>
+        <v>29.29</v>
+      </c>
+      <c r="K100" s="4" t="n">
+        <v>-5.71</v>
       </c>
       <c r="L100" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N100" s="2" t="n">
-        <v>18.42</v>
+        <v>0.78</v>
+      </c>
+      <c r="N100" s="4" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>TOKYO W  Target Output: 480 Prs / 8H (60 Prs / Hou</t>
+          <t>TOKYO W  Target Output : 960 Prs / 8H (120 Prs / H</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>JI0182</t>
-        </is>
+          <t>IH6609</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>17</v>
       </c>
       <c r="D101" t="n">
-        <v>179.8307</v>
+        <v>4.78</v>
+      </c>
+      <c r="E101" s="4" t="n">
+        <v>-12.22</v>
+      </c>
+      <c r="F101" t="n">
+        <v>31</v>
       </c>
       <c r="G101" t="n">
-        <v>939.13</v>
+        <v>38.66</v>
+      </c>
+      <c r="H101" s="4" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="I101" t="n">
+        <v>38.5</v>
       </c>
       <c r="J101" t="n">
-        <v>982.08</v>
+        <v>32.74</v>
+      </c>
+      <c r="K101" s="4" t="n">
+        <v>-5.76</v>
+      </c>
+      <c r="L101" t="n">
+        <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>23.32</v>
+        <v>0.78</v>
+      </c>
+      <c r="N101" s="4" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>TOKYO W  Target Output : 960 Prs / 8H (120 Prs / H</t>
+          <t>TOKYO W  Target Output: 960 Prs / 8H (120 Prs / Ho</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>JI3300</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>78.08</v>
-      </c>
-      <c r="D102" t="n">
-        <v>385.4396</v>
-      </c>
-      <c r="E102" s="2" t="n">
-        <v>307.3596</v>
-      </c>
-      <c r="F102" t="n">
-        <v>161.4067</v>
-      </c>
-      <c r="G102" t="n">
-        <v>1075.53</v>
-      </c>
-      <c r="H102" s="2" t="n">
-        <v>914.1233</v>
-      </c>
-      <c r="I102" t="n">
-        <v>51.1</v>
-      </c>
-      <c r="J102" t="n">
-        <v>991.87</v>
-      </c>
-      <c r="K102" s="2" t="n">
-        <v>940.77</v>
-      </c>
-      <c r="L102" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M102" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N102" s="2" t="n">
-        <v>18.42</v>
+          <t>JI0182</t>
+        </is>
       </c>
     </row>
     <row r="103">
@@ -4646,44 +4510,44 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>JQ0585</t>
+          <t>JI3300</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>84.38</v>
+        <v>18</v>
       </c>
       <c r="D103" t="n">
-        <v>385.4396</v>
-      </c>
-      <c r="E103" s="2" t="n">
-        <v>301.0596</v>
+        <v>12.85</v>
+      </c>
+      <c r="E103" s="4" t="n">
+        <v>-5.15</v>
       </c>
       <c r="F103" t="n">
-        <v>217.008</v>
+        <v>28</v>
       </c>
       <c r="G103" t="n">
-        <v>1117.33</v>
-      </c>
-      <c r="H103" s="2" t="n">
-        <v>900.322</v>
+        <v>35.85</v>
+      </c>
+      <c r="H103" s="4" t="n">
+        <v>7.85</v>
       </c>
       <c r="I103" t="n">
-        <v>51.1</v>
+        <v>38.5</v>
       </c>
       <c r="J103" t="n">
-        <v>991.87</v>
-      </c>
-      <c r="K103" s="2" t="n">
-        <v>940.77</v>
+        <v>33.06</v>
+      </c>
+      <c r="K103" s="4" t="n">
+        <v>-5.44</v>
       </c>
       <c r="L103" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N103" s="2" t="n">
-        <v>18.42</v>
+        <v>0.78</v>
+      </c>
+      <c r="N103" s="4" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="104">
@@ -4694,44 +4558,44 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>JQ0595</t>
+          <t>JQ0585</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>87.19</v>
+        <v>18</v>
       </c>
       <c r="D104" t="n">
-        <v>178.0895</v>
-      </c>
-      <c r="E104" s="2" t="n">
-        <v>90.8995</v>
+        <v>12.85</v>
+      </c>
+      <c r="E104" s="4" t="n">
+        <v>-5.15</v>
       </c>
       <c r="F104" t="n">
-        <v>161.4067</v>
+        <v>28</v>
       </c>
       <c r="G104" t="n">
-        <v>1214.02</v>
-      </c>
-      <c r="H104" s="2" t="n">
-        <v>1052.6133</v>
+        <v>37.24</v>
+      </c>
+      <c r="H104" s="4" t="n">
+        <v>9.24</v>
       </c>
       <c r="I104" t="n">
-        <v>51.1</v>
+        <v>38.5</v>
       </c>
       <c r="J104" t="n">
-        <v>1081.41</v>
-      </c>
-      <c r="K104" s="2" t="n">
-        <v>1030.31</v>
+        <v>33.06</v>
+      </c>
+      <c r="K104" s="4" t="n">
+        <v>-5.44</v>
       </c>
       <c r="L104" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N104" s="2" t="n">
-        <v>18.42</v>
+        <v>0.78</v>
+      </c>
+      <c r="N104" s="4" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="105">
@@ -4742,44 +4606,44 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>JQ0597</t>
+          <t>JQ0595</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>87.19</v>
+        <v>21</v>
       </c>
       <c r="D105" t="n">
-        <v>179.781</v>
-      </c>
-      <c r="E105" s="2" t="n">
-        <v>92.59099999999999</v>
+        <v>5.94</v>
+      </c>
+      <c r="E105" s="4" t="n">
+        <v>-15.06</v>
       </c>
       <c r="F105" t="n">
-        <v>161.4067</v>
+        <v>31.5</v>
       </c>
       <c r="G105" t="n">
-        <v>1159.68</v>
-      </c>
-      <c r="H105" s="2" t="n">
-        <v>998.2732999999999</v>
+        <v>40.47</v>
+      </c>
+      <c r="H105" s="4" t="n">
+        <v>8.970000000000001</v>
       </c>
       <c r="I105" t="n">
-        <v>51.1</v>
+        <v>41.5</v>
       </c>
       <c r="J105" t="n">
-        <v>1130.36</v>
-      </c>
-      <c r="K105" s="2" t="n">
-        <v>1079.26</v>
+        <v>36.05</v>
+      </c>
+      <c r="K105" s="4" t="n">
+        <v>-5.45</v>
       </c>
       <c r="L105" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N105" s="2" t="n">
-        <v>18.42</v>
+        <v>0.78</v>
+      </c>
+      <c r="N105" s="4" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="106">
@@ -4790,44 +4654,44 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>JR1271</t>
+          <t>JQ0597</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>168.2267</v>
+        <v>21</v>
       </c>
       <c r="D106" t="n">
-        <v>155.6262</v>
-      </c>
-      <c r="E106" s="2" t="n">
-        <v>-12.6005</v>
+        <v>5.99</v>
+      </c>
+      <c r="E106" s="4" t="n">
+        <v>-15.01</v>
       </c>
       <c r="F106" t="n">
-        <v>168.2267</v>
+        <v>31</v>
       </c>
       <c r="G106" t="n">
-        <v>1184.65</v>
-      </c>
-      <c r="H106" s="2" t="n">
-        <v>1016.4233</v>
+        <v>38.66</v>
+      </c>
+      <c r="H106" s="4" t="n">
+        <v>7.66</v>
       </c>
       <c r="I106" t="n">
-        <v>52.6</v>
+        <v>40.5</v>
       </c>
       <c r="J106" t="n">
-        <v>1047.75</v>
-      </c>
-      <c r="K106" s="2" t="n">
-        <v>995.15</v>
+        <v>37.68</v>
+      </c>
+      <c r="K106" s="4" t="n">
+        <v>-2.82</v>
       </c>
       <c r="L106" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N106" s="2" t="n">
-        <v>18.42</v>
+        <v>0.78</v>
+      </c>
+      <c r="N106" s="4" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="107">
@@ -4838,44 +4702,44 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>JR1494</t>
+          <t>JR1271</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>81.47</v>
+        <v>17.5</v>
       </c>
       <c r="D107" t="n">
-        <v>399.3188</v>
-      </c>
-      <c r="E107" s="2" t="n">
-        <v>317.8488</v>
+        <v>5.19</v>
+      </c>
+      <c r="E107" s="4" t="n">
+        <v>-12.31</v>
       </c>
       <c r="F107" t="n">
-        <v>161.4067</v>
+        <v>32</v>
       </c>
       <c r="G107" t="n">
-        <v>1122.06</v>
-      </c>
-      <c r="H107" s="2" t="n">
-        <v>960.6532999999999</v>
+        <v>39.49</v>
+      </c>
+      <c r="H107" s="4" t="n">
+        <v>7.49</v>
       </c>
       <c r="I107" t="n">
-        <v>51.1</v>
+        <v>40.5</v>
       </c>
       <c r="J107" t="n">
-        <v>1079.54</v>
-      </c>
-      <c r="K107" s="2" t="n">
-        <v>1028.44</v>
+        <v>34.92</v>
+      </c>
+      <c r="K107" s="4" t="n">
+        <v>-5.58</v>
       </c>
       <c r="L107" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="M107" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N107" s="2" t="n">
-        <v>18.42</v>
+        <v>0.78</v>
+      </c>
+      <c r="N107" s="4" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="108">
@@ -4886,260 +4750,236 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>JR2251</t>
+          <t>JR1494</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>70.42</v>
+        <v>18</v>
       </c>
       <c r="D108" t="n">
-        <v>383.5895</v>
-      </c>
-      <c r="E108" s="2" t="n">
-        <v>313.1695</v>
+        <v>13.31</v>
+      </c>
+      <c r="E108" s="4" t="n">
+        <v>-4.69</v>
       </c>
       <c r="F108" t="n">
-        <v>161.4067</v>
+        <v>29.5</v>
       </c>
       <c r="G108" t="n">
-        <v>1172.88</v>
-      </c>
-      <c r="H108" s="2" t="n">
-        <v>1011.4733</v>
+        <v>37.4</v>
+      </c>
+      <c r="H108" s="4" t="n">
+        <v>7.9</v>
       </c>
       <c r="I108" t="n">
-        <v>52.6</v>
+        <v>41</v>
       </c>
       <c r="J108" t="n">
-        <v>991.87</v>
-      </c>
-      <c r="K108" s="2" t="n">
-        <v>939.27</v>
+        <v>35.98</v>
+      </c>
+      <c r="K108" s="4" t="n">
+        <v>-5.02</v>
       </c>
       <c r="L108" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N108" s="2" t="n">
-        <v>18.42</v>
+        <v>0.78</v>
+      </c>
+      <c r="N108" s="4" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>TOKYO W -.. -. -..  Target Output : 960 Prs / 8H (</t>
+          <t>TOKYO W  Target Output : 960 Prs / 8H (120 Prs / H</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>KH6076</t>
+          <t>JR2251</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>94.98999999999999</v>
+        <v>16</v>
       </c>
       <c r="D109" t="n">
-        <v>180.6423</v>
-      </c>
-      <c r="E109" s="2" t="n">
-        <v>85.6523</v>
+        <v>12.79</v>
+      </c>
+      <c r="E109" s="4" t="n">
+        <v>-3.21</v>
       </c>
       <c r="F109" t="n">
-        <v>161.4067</v>
+        <v>30.5</v>
       </c>
       <c r="G109" t="n">
-        <v>1249.88</v>
-      </c>
-      <c r="H109" s="2" t="n">
-        <v>1088.4733</v>
+        <v>39.1</v>
+      </c>
+      <c r="H109" s="4" t="n">
+        <v>8.6</v>
       </c>
       <c r="I109" t="n">
-        <v>52.6</v>
+        <v>38.5</v>
       </c>
       <c r="J109" t="n">
-        <v>1100.66</v>
-      </c>
-      <c r="K109" s="2" t="n">
-        <v>1048.06</v>
+        <v>33.06</v>
+      </c>
+      <c r="K109" s="4" t="n">
+        <v>-5.44</v>
       </c>
       <c r="L109" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N109" s="2" t="n">
-        <v>18.42</v>
+        <v>0.78</v>
+      </c>
+      <c r="N109" s="4" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>TOKYO W  Target Output : 960 Prs / 8H (120 Prs / H</t>
+          <t>TOKYO W -.. -. -..  Target Output : 960 Prs / 8H (</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>KI4173</t>
+          <t>KH6076</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>88.64</v>
+        <v>20.5</v>
       </c>
       <c r="D110" t="n">
-        <v>358.0871</v>
-      </c>
-      <c r="E110" s="2" t="n">
-        <v>269.4471</v>
+        <v>6.02</v>
+      </c>
+      <c r="E110" s="4" t="n">
+        <v>-14.48</v>
       </c>
       <c r="F110" t="n">
-        <v>161.4067</v>
+        <v>34</v>
       </c>
       <c r="G110" t="n">
-        <v>1177.83</v>
-      </c>
-      <c r="H110" s="2" t="n">
-        <v>1016.4233</v>
+        <v>41.66</v>
+      </c>
+      <c r="H110" s="4" t="n">
+        <v>7.66</v>
       </c>
       <c r="I110" t="n">
-        <v>51.1</v>
+        <v>40.5</v>
       </c>
       <c r="J110" t="n">
-        <v>1137.84</v>
-      </c>
-      <c r="K110" s="2" t="n">
-        <v>1086.74</v>
+        <v>36.69</v>
+      </c>
+      <c r="K110" s="4" t="n">
+        <v>-3.81</v>
       </c>
       <c r="L110" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N110" s="2" t="n">
-        <v>18.42</v>
+        <v>0.78</v>
+      </c>
+      <c r="N110" s="4" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>TOKYO W  Target Output : 480 Prs / 8H (60 Prs / Ho</t>
+          <t>TOKYO W  Target Output : 960 Prs / 8H (120 Prs / H</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>KI4300</t>
+          <t>KI4173</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>87.98999999999999</v>
+        <v>21</v>
       </c>
       <c r="D111" t="n">
-        <v>358.0871</v>
-      </c>
-      <c r="E111" s="2" t="n">
-        <v>270.0971</v>
+        <v>11.94</v>
+      </c>
+      <c r="E111" s="4" t="n">
+        <v>-9.06</v>
       </c>
       <c r="F111" t="n">
-        <v>161.4067</v>
+        <v>32</v>
       </c>
       <c r="G111" t="n">
-        <v>1171.56</v>
-      </c>
-      <c r="H111" s="2" t="n">
-        <v>1010.1533</v>
+        <v>39.26</v>
+      </c>
+      <c r="H111" s="4" t="n">
+        <v>7.26</v>
       </c>
       <c r="I111" t="n">
-        <v>52.6</v>
+        <v>43.5</v>
       </c>
       <c r="J111" t="n">
-        <v>1220.56</v>
-      </c>
-      <c r="K111" s="2" t="n">
-        <v>1167.96</v>
+        <v>37.93</v>
+      </c>
+      <c r="K111" s="4" t="n">
+        <v>-5.57</v>
       </c>
       <c r="L111" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N111" s="2" t="n">
-        <v>18.42</v>
+        <v>0.78</v>
+      </c>
+      <c r="N111" s="4" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>TOKYO W  Target Output: 960 Prs / 8H (120 Prs / Ho</t>
+          <t>TOKYO W  Target Output : 960 Prs / 8H (120 Prs / H</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>KJ7499</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>179.8307</v>
-      </c>
-      <c r="G112" t="n">
-        <v>939.13</v>
-      </c>
-      <c r="J112" t="n">
-        <v>982.08</v>
-      </c>
-      <c r="M112" t="n">
-        <v>23.32</v>
+          <t>KI4300</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>21</v>
+      </c>
+      <c r="F112" t="n">
+        <v>31</v>
+      </c>
+      <c r="I112" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="L112" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>TOKYO W  Target Output : 960 Prs / 8H (120 Prs / H</t>
+          <t>TOKYO W  Target Output: 960 Prs / 8H (120 Prs / Ho</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>KJ7522</t>
-        </is>
-      </c>
-      <c r="C113" t="n">
-        <v>78.08</v>
+          <t>KJ7499</t>
+        </is>
       </c>
       <c r="D113" t="n">
-        <v>385.4396</v>
-      </c>
-      <c r="E113" s="2" t="n">
-        <v>307.3596</v>
-      </c>
-      <c r="F113" t="n">
-        <v>161.4067</v>
+        <v>5.99</v>
       </c>
       <c r="G113" t="n">
-        <v>1075.53</v>
-      </c>
-      <c r="H113" s="2" t="n">
-        <v>914.1233</v>
-      </c>
-      <c r="I113" t="n">
-        <v>51.1</v>
+        <v>31.3</v>
       </c>
       <c r="J113" t="n">
-        <v>991.87</v>
-      </c>
-      <c r="K113" s="2" t="n">
-        <v>940.77</v>
-      </c>
-      <c r="L113" t="n">
-        <v>4.9</v>
+        <v>32.74</v>
       </c>
       <c r="M113" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N113" s="2" t="n">
-        <v>18.42</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="114">
@@ -5150,44 +4990,44 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>KJ7541</t>
+          <t>KJ7522</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>87.19</v>
+        <v>18</v>
       </c>
       <c r="D114" t="n">
-        <v>532.7797</v>
-      </c>
-      <c r="E114" s="2" t="n">
-        <v>445.5897</v>
+        <v>12.85</v>
+      </c>
+      <c r="E114" s="4" t="n">
+        <v>-5.15</v>
       </c>
       <c r="F114" t="n">
-        <v>161.4067</v>
+        <v>28</v>
       </c>
       <c r="G114" t="n">
-        <v>1222.38</v>
-      </c>
-      <c r="H114" s="2" t="n">
-        <v>1060.9733</v>
+        <v>35.85</v>
+      </c>
+      <c r="H114" s="4" t="n">
+        <v>7.85</v>
       </c>
       <c r="I114" t="n">
-        <v>53.1</v>
+        <v>38.5</v>
       </c>
       <c r="J114" t="n">
-        <v>1113.31</v>
-      </c>
-      <c r="K114" s="2" t="n">
-        <v>1060.21</v>
+        <v>33.06</v>
+      </c>
+      <c r="K114" s="4" t="n">
+        <v>-5.44</v>
       </c>
       <c r="L114" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N114" s="2" t="n">
-        <v>18.42</v>
+        <v>0.78</v>
+      </c>
+      <c r="N114" s="4" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="115">
@@ -5198,44 +5038,44 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>KJ7551</t>
+          <t>KJ7541</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>87.19</v>
+        <v>20</v>
       </c>
       <c r="D115" t="n">
-        <v>181.4625</v>
-      </c>
-      <c r="E115" s="2" t="n">
-        <v>94.27249999999999</v>
+        <v>17.76</v>
+      </c>
+      <c r="E115" s="4" t="n">
+        <v>-2.24</v>
       </c>
       <c r="F115" t="n">
-        <v>161.4067</v>
+        <v>31.5</v>
       </c>
       <c r="G115" t="n">
-        <v>1159.68</v>
-      </c>
-      <c r="H115" s="2" t="n">
-        <v>998.2732999999999</v>
+        <v>40.75</v>
+      </c>
+      <c r="H115" s="4" t="n">
+        <v>9.25</v>
       </c>
       <c r="I115" t="n">
-        <v>51.1</v>
+        <v>43.5</v>
       </c>
       <c r="J115" t="n">
-        <v>1047.64</v>
-      </c>
-      <c r="K115" s="2" t="n">
-        <v>996.54</v>
+        <v>37.11</v>
+      </c>
+      <c r="K115" s="4" t="n">
+        <v>-6.39</v>
       </c>
       <c r="L115" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N115" s="2" t="n">
-        <v>18.42</v>
+        <v>0.78</v>
+      </c>
+      <c r="N115" s="4" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="116">
@@ -5246,206 +5086,164 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>KK0036</t>
+          <t>KJ7551</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>66.93000000000001</v>
+        <v>20</v>
       </c>
       <c r="D116" t="n">
-        <v>337.0505</v>
-      </c>
-      <c r="E116" s="2" t="n">
-        <v>270.1205</v>
+        <v>6.05</v>
+      </c>
+      <c r="E116" s="4" t="n">
+        <v>-13.95</v>
       </c>
       <c r="F116" t="n">
-        <v>66.93000000000001</v>
+        <v>31</v>
       </c>
       <c r="G116" t="n">
-        <v>867.21</v>
-      </c>
-      <c r="H116" s="2" t="n">
-        <v>800.28</v>
+        <v>38.66</v>
+      </c>
+      <c r="H116" s="4" t="n">
+        <v>7.66</v>
       </c>
       <c r="I116" t="n">
-        <v>51.1</v>
+        <v>40.5</v>
       </c>
       <c r="J116" t="n">
-        <v>926.97</v>
-      </c>
-      <c r="K116" s="2" t="n">
-        <v>875.87</v>
+        <v>34.92</v>
+      </c>
+      <c r="K116" s="4" t="n">
+        <v>-5.58</v>
       </c>
       <c r="L116" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N116" s="2" t="n">
-        <v>18.42</v>
+        <v>0.78</v>
+      </c>
+      <c r="N116" s="4" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>TOKYO W  Target Output : 480 Prs / 8H (60 Prs / Ho</t>
+          <t>TOKYO W  Target Output : 960 Prs / 8H (120 Prs / H</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>KK2765</t>
+          <t>KK0036</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>88.98</v>
+        <v>14</v>
       </c>
       <c r="D117" t="n">
-        <v>174.4085</v>
-      </c>
-      <c r="E117" s="2" t="n">
-        <v>85.4285</v>
+        <v>11.24</v>
+      </c>
+      <c r="E117" s="4" t="n">
+        <v>-2.76</v>
       </c>
       <c r="F117" t="n">
-        <v>161.4067</v>
+        <v>23</v>
       </c>
       <c r="G117" t="n">
-        <v>1159.68</v>
-      </c>
-      <c r="H117" s="2" t="n">
-        <v>998.2732999999999</v>
+        <v>28.91</v>
+      </c>
+      <c r="H117" s="4" t="n">
+        <v>5.91</v>
       </c>
       <c r="I117" t="n">
-        <v>52.6</v>
+        <v>36.5</v>
       </c>
       <c r="J117" t="n">
-        <v>1100.66</v>
-      </c>
-      <c r="K117" s="2" t="n">
-        <v>1048.06</v>
+        <v>30.9</v>
+      </c>
+      <c r="K117" s="4" t="n">
+        <v>-5.6</v>
       </c>
       <c r="L117" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N117" s="2" t="n">
-        <v>18.42</v>
+        <v>0.78</v>
+      </c>
+      <c r="N117" s="4" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>GAZELLE GOLF  Target Output : 480 Prs / 8H (60 Prs</t>
+          <t>TOKYO W  Target Output : 960 Prs / 8H (120 Prs / H</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>IH2267</t>
+          <t>KK2765</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>108.46</v>
-      </c>
-      <c r="D118" t="n">
-        <v>336.3166</v>
-      </c>
-      <c r="E118" s="2" t="n">
-        <v>227.8566</v>
+        <v>20.5</v>
       </c>
       <c r="F118" t="n">
-        <v>108.46</v>
-      </c>
-      <c r="G118" t="n">
-        <v>1140.59</v>
-      </c>
-      <c r="H118" s="2" t="n">
-        <v>1032.13</v>
+        <v>31</v>
       </c>
       <c r="I118" t="n">
-        <v>48.65</v>
-      </c>
-      <c r="J118" t="n">
-        <v>888.36</v>
-      </c>
-      <c r="K118" s="2" t="n">
-        <v>839.71</v>
+        <v>40.5</v>
       </c>
       <c r="L118" t="n">
-        <v>26.31</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMPUS 00s GOLF Target Output : 960 Prs / 8H (120 </t>
+          <t xml:space="preserve">W/ GAZELLE GOLF Target Output : 960 Prs / 8H (120 </t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>JQ6804</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>238.1211</v>
-      </c>
-      <c r="G119" t="n">
-        <v>1134.5566</v>
-      </c>
-      <c r="J119" t="n">
-        <v>891.5901</v>
-      </c>
-      <c r="M119" t="n">
-        <v>222.64</v>
+          <t>IH2267</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>17</v>
+      </c>
+      <c r="F119" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="I119" t="n">
+        <v>35</v>
+      </c>
+      <c r="L119" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>TOKYO W MJ Target Output : 960 Prs / 8H (120 Prs /</t>
+          <t xml:space="preserve">CAMPUS 00s GOLF Target Output : 960 Prs / 8H (120 </t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>IH3999</t>
-        </is>
-      </c>
-      <c r="C120" t="n">
-        <v>93.5</v>
+          <t>JQ6804</t>
+        </is>
       </c>
       <c r="D120" t="n">
-        <v>565.2639</v>
-      </c>
-      <c r="E120" s="2" t="n">
-        <v>471.7639</v>
-      </c>
-      <c r="F120" t="n">
-        <v>161.4067</v>
+        <v>7.94</v>
       </c>
       <c r="G120" t="n">
-        <v>1553.15</v>
-      </c>
-      <c r="H120" s="2" t="n">
-        <v>1391.7433</v>
-      </c>
-      <c r="I120" t="n">
-        <v>46.6</v>
+        <v>37.82</v>
       </c>
       <c r="J120" t="n">
-        <v>878.5700000000001</v>
-      </c>
-      <c r="K120" s="2" t="n">
-        <v>831.97</v>
-      </c>
-      <c r="L120" t="n">
-        <v>4.9</v>
+        <v>29.72</v>
       </c>
       <c r="M120" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N120" s="2" t="n">
-        <v>18.42</v>
+        <v>7.42</v>
       </c>
     </row>
     <row r="121">
@@ -5456,44 +5254,44 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>KH5551</t>
+          <t>IH3999</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>99.73</v>
+        <v>19</v>
       </c>
       <c r="D121" t="n">
-        <v>561.5337</v>
-      </c>
-      <c r="E121" s="2" t="n">
-        <v>461.8037</v>
+        <v>18.84</v>
+      </c>
+      <c r="E121" s="4" t="n">
+        <v>-0.16</v>
       </c>
       <c r="F121" t="n">
-        <v>157.3</v>
+        <v>38</v>
       </c>
       <c r="G121" t="n">
-        <v>1447.54</v>
-      </c>
-      <c r="H121" s="2" t="n">
-        <v>1290.24</v>
+        <v>51.77</v>
+      </c>
+      <c r="H121" s="4" t="n">
+        <v>13.77</v>
       </c>
       <c r="I121" t="n">
-        <v>46.6</v>
+        <v>35</v>
       </c>
       <c r="J121" t="n">
-        <v>970.42</v>
-      </c>
-      <c r="K121" s="2" t="n">
-        <v>923.8200000000001</v>
+        <v>29.29</v>
+      </c>
+      <c r="K121" s="4" t="n">
+        <v>-5.71</v>
       </c>
       <c r="L121" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N121" s="2" t="n">
-        <v>18.42</v>
+        <v>0.78</v>
+      </c>
+      <c r="N121" s="4" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="122">
@@ -5504,464 +5302,368 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>KI3025</t>
+          <t>KH5551</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>102.51</v>
-      </c>
-      <c r="D122" t="n">
-        <v>561.5337</v>
-      </c>
-      <c r="E122" s="2" t="n">
-        <v>459.0237</v>
+        <v>20</v>
       </c>
       <c r="F122" t="n">
-        <v>157.3</v>
-      </c>
-      <c r="G122" t="n">
-        <v>1443.14</v>
-      </c>
-      <c r="H122" s="2" t="n">
-        <v>1285.84</v>
+        <v>37</v>
       </c>
       <c r="I122" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="J122" t="n">
-        <v>1000.12</v>
-      </c>
-      <c r="K122" s="2" t="n">
-        <v>953.52</v>
+        <v>36</v>
       </c>
       <c r="L122" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M122" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N122" s="2" t="n">
-        <v>18.42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">BB F50 GHOST SPRINT  Target Output : 960 Prs / 8H </t>
+          <t>TOKYO W MJ Target Output : 960 Prs / 8H (120 Prs /</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>KI9450</t>
+          <t>KI3025</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>79.40000000000001</v>
-      </c>
-      <c r="D123" t="n">
-        <v>355.7837</v>
-      </c>
-      <c r="E123" s="2" t="n">
-        <v>276.3837</v>
+        <v>20</v>
       </c>
       <c r="F123" t="n">
-        <v>79.40000000000001</v>
-      </c>
-      <c r="G123" t="n">
-        <v>1209.45</v>
-      </c>
-      <c r="H123" s="2" t="n">
-        <v>1130.05</v>
+        <v>37</v>
       </c>
       <c r="I123" t="n">
-        <v>93.09999999999999</v>
-      </c>
-      <c r="J123" t="n">
-        <v>1558.33</v>
-      </c>
-      <c r="K123" s="2" t="n">
-        <v>1465.23</v>
+        <v>36</v>
       </c>
       <c r="L123" t="n">
-        <v>9.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRAXION LITE MAX  BOA Target Output :960 Prs / 8H </t>
+          <t xml:space="preserve">BB F50 GHOST SPRINT  Target Output : 960 Prs / 8H </t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>IH2248</t>
+          <t>KI9450</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>73.56</v>
+        <v>9.5</v>
       </c>
       <c r="D124" t="n">
-        <v>5631.2009</v>
-      </c>
-      <c r="E124" s="2" t="n">
-        <v>5557.6409</v>
+        <v>11.86</v>
+      </c>
+      <c r="E124" s="4" t="n">
+        <v>2.36</v>
       </c>
       <c r="F124" t="n">
-        <v>73.56</v>
+        <v>39</v>
       </c>
       <c r="G124" t="n">
-        <v>971.7499</v>
-      </c>
-      <c r="H124" s="2" t="n">
-        <v>898.1899</v>
+        <v>40.32</v>
+      </c>
+      <c r="H124" s="4" t="n">
+        <v>1.32</v>
       </c>
       <c r="I124" t="n">
-        <v>51.1</v>
+        <v>58</v>
       </c>
       <c r="J124" t="n">
-        <v>905.63</v>
-      </c>
-      <c r="K124" s="2" t="n">
-        <v>854.53</v>
+        <v>51.94</v>
+      </c>
+      <c r="K124" s="4" t="n">
+        <v>-6.06</v>
       </c>
       <c r="L124" t="n">
-        <v>17.96</v>
-      </c>
-      <c r="M124" t="n">
-        <v>363</v>
-      </c>
-      <c r="N124" s="2" t="n">
-        <v>345.04</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>TRAXION RESPONSE Target Output : 960 Prs/8H (120 P</t>
+          <t xml:space="preserve">TRAXION LITE MAX  BOA Target Output :960 Prs / 8H </t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>IH2250</t>
+          <t>IH2248</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>74.25</v>
+        <v>20</v>
       </c>
       <c r="D125" t="n">
-        <v>464.2032</v>
-      </c>
-      <c r="E125" s="2" t="n">
-        <v>389.9532</v>
+        <v>187.71</v>
+      </c>
+      <c r="E125" s="4" t="n">
+        <v>167.71</v>
       </c>
       <c r="F125" t="n">
-        <v>74.25</v>
+        <v>39</v>
       </c>
       <c r="G125" t="n">
-        <v>1005.0799</v>
-      </c>
-      <c r="H125" s="2" t="n">
-        <v>930.8299</v>
+        <v>32.39</v>
+      </c>
+      <c r="H125" s="4" t="n">
+        <v>-6.61</v>
       </c>
       <c r="I125" t="n">
-        <v>51.1</v>
+        <v>37</v>
       </c>
       <c r="J125" t="n">
-        <v>986.15</v>
-      </c>
-      <c r="K125" s="2" t="n">
-        <v>935.05</v>
+        <v>30.19</v>
+      </c>
+      <c r="K125" s="4" t="n">
+        <v>-6.81</v>
       </c>
       <c r="L125" t="n">
-        <v>20.88</v>
+        <v>14</v>
       </c>
       <c r="M125" t="n">
-        <v>363</v>
-      </c>
-      <c r="N125" s="2" t="n">
-        <v>342.12</v>
+        <v>12.1</v>
+      </c>
+      <c r="N125" s="4" t="n">
+        <v>-1.9</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">W S2G VENT Target Output : 480 Prs / 8H (60 Prs / </t>
+          <t>TRAXION RESPONSE Target Output : 960 Prs/8H (120 P</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>KI8401</t>
+          <t>IH2250</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>96.36</v>
+        <v>21.5</v>
       </c>
       <c r="D126" t="n">
-        <v>329.3496</v>
-      </c>
-      <c r="E126" s="2" t="n">
-        <v>232.9896</v>
+        <v>15.47</v>
+      </c>
+      <c r="E126" s="4" t="n">
+        <v>-6.03</v>
       </c>
       <c r="F126" t="n">
-        <v>183.1133</v>
+        <v>39</v>
       </c>
       <c r="G126" t="n">
-        <v>1149.4</v>
-      </c>
-      <c r="H126" s="2" t="n">
-        <v>966.2867</v>
+        <v>33.5</v>
+      </c>
+      <c r="H126" s="4" t="n">
+        <v>-5.5</v>
       </c>
       <c r="I126" t="n">
-        <v>45.1</v>
+        <v>38.5</v>
       </c>
       <c r="J126" t="n">
-        <v>876.26</v>
-      </c>
-      <c r="K126" s="2" t="n">
-        <v>831.16</v>
+        <v>32.87</v>
+      </c>
+      <c r="K126" s="4" t="n">
+        <v>-5.63</v>
       </c>
       <c r="L126" t="n">
-        <v>26.05</v>
+        <v>14</v>
       </c>
       <c r="M126" t="n">
-        <v>456.94</v>
-      </c>
-      <c r="N126" s="2" t="n">
-        <v>430.89</v>
+        <v>12.1</v>
+      </c>
+      <c r="N126" s="4" t="n">
+        <v>-1.9</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>JR CODECHAOS BOA 27 Target Output : 480 Prs / 8H (</t>
+          <t xml:space="preserve">W S2G VENT Target Output : 480 Prs / 8H (60 Prs / </t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>KI5746</t>
+          <t>KI8401</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>99.09</v>
+        <v>13.5</v>
       </c>
       <c r="D127" t="n">
-        <v>367.2197</v>
-      </c>
-      <c r="E127" s="2" t="n">
-        <v>268.1297</v>
+        <v>10.98</v>
+      </c>
+      <c r="E127" s="4" t="n">
+        <v>-2.52</v>
       </c>
       <c r="F127" t="n">
-        <v>99.09</v>
+        <v>21</v>
       </c>
       <c r="G127" t="n">
-        <v>771.54</v>
-      </c>
-      <c r="H127" s="2" t="n">
-        <v>672.45</v>
+        <v>38.31</v>
+      </c>
+      <c r="H127" s="4" t="n">
+        <v>17.31</v>
       </c>
       <c r="I127" t="n">
-        <v>45.6</v>
+        <v>19.5</v>
       </c>
       <c r="J127" t="n">
-        <v>919.6</v>
-      </c>
-      <c r="K127" s="2" t="n">
-        <v>874</v>
+        <v>29.21</v>
+      </c>
+      <c r="K127" s="4" t="n">
+        <v>9.710000000000001</v>
       </c>
       <c r="L127" t="n">
-        <v>18.18</v>
+        <v>9</v>
       </c>
       <c r="M127" t="n">
-        <v>328.13</v>
-      </c>
-      <c r="N127" s="2" t="n">
-        <v>309.95</v>
+        <v>15.23</v>
+      </c>
+      <c r="N127" s="4" t="n">
+        <v>6.23</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S2G 24  Target Output : 480 Prs / 8H (60 Prs / Hou</t>
+          <t>JR CODECHAOS BOA 27 Target Output : 960 Prs / 8H (</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>IF0292</t>
+          <t>KI5746</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>110.33</v>
-      </c>
-      <c r="D128" t="n">
-        <v>143.8348</v>
-      </c>
-      <c r="E128" s="2" t="n">
-        <v>33.5048</v>
+        <v>8.5</v>
       </c>
       <c r="F128" t="n">
-        <v>110.33</v>
-      </c>
-      <c r="G128" t="n">
-        <v>1282.62</v>
-      </c>
-      <c r="H128" s="2" t="n">
-        <v>1172.29</v>
+        <v>16</v>
       </c>
       <c r="I128" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="J128" t="n">
-        <v>1100.42</v>
-      </c>
-      <c r="K128" s="2" t="n">
-        <v>1050.32</v>
+        <v>21</v>
       </c>
       <c r="L128" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOKYO CONTEMPO W Target Output : 480 Prs / 8H (60 </t>
+          <t>S2G 24  Target Output : 480 Prs / 8H (60 Prs / Hou</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>KI4866</t>
+          <t>IF0292</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>57.63</v>
+        <v>9</v>
       </c>
       <c r="D129" t="n">
-        <v>95.79170000000001</v>
-      </c>
-      <c r="E129" s="2" t="n">
-        <v>38.1617</v>
+        <v>4.79</v>
+      </c>
+      <c r="E129" s="4" t="n">
+        <v>-4.21</v>
       </c>
       <c r="F129" t="n">
-        <v>64.45999999999999</v>
+        <v>25</v>
       </c>
       <c r="G129" t="n">
-        <v>2870.5</v>
-      </c>
-      <c r="H129" s="2" t="n">
-        <v>2806.04</v>
+        <v>42.75</v>
+      </c>
+      <c r="H129" s="4" t="n">
+        <v>17.75</v>
       </c>
       <c r="I129" t="n">
-        <v>44.1</v>
+        <v>22</v>
       </c>
       <c r="J129" t="n">
-        <v>860.3099999999999</v>
-      </c>
-      <c r="K129" s="2" t="n">
-        <v>816.21</v>
+        <v>36.68</v>
+      </c>
+      <c r="K129" s="4" t="n">
+        <v>14.68</v>
       </c>
       <c r="L129" t="n">
-        <v>18.37</v>
-      </c>
-      <c r="M129" t="n">
-        <v>290.73</v>
-      </c>
-      <c r="N129" s="2" t="n">
-        <v>272.36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ADIPOWER 26 SL Target Output : 480 Prs / 8H (60 Pr</t>
+          <t xml:space="preserve">TOKYO CONTEMPO W Target Output : 480 Prs / 8H (60 </t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>JP8395</t>
+          <t>KI4866</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>128.19</v>
+        <v>5.5</v>
       </c>
       <c r="D130" t="n">
-        <v>192.4317</v>
-      </c>
-      <c r="E130" s="2" t="n">
-        <v>64.24169999999999</v>
+        <v>3.19</v>
+      </c>
+      <c r="E130" s="4" t="n">
+        <v>-2.31</v>
       </c>
       <c r="F130" t="n">
-        <v>121.66</v>
+        <v>13</v>
       </c>
       <c r="G130" t="n">
-        <v>3455.67</v>
-      </c>
-      <c r="H130" s="2" t="n">
-        <v>3334.01</v>
+        <v>95.68000000000001</v>
+      </c>
+      <c r="H130" s="4" t="n">
+        <v>82.68000000000001</v>
       </c>
       <c r="I130" t="n">
-        <v>58.1</v>
+        <v>17.5</v>
       </c>
       <c r="J130" t="n">
-        <v>1157.75</v>
-      </c>
-      <c r="K130" s="2" t="n">
-        <v>1099.65</v>
+        <v>28.68</v>
+      </c>
+      <c r="K130" s="4" t="n">
+        <v>11.18</v>
       </c>
       <c r="L130" t="n">
-        <v>32.32</v>
+        <v>6</v>
       </c>
       <c r="M130" t="n">
-        <v>521.62</v>
-      </c>
-      <c r="N130" s="2" t="n">
-        <v>489.3</v>
+        <v>9.69</v>
+      </c>
+      <c r="N130" s="4" t="n">
+        <v>3.69</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>TAEKWONDO MEI ELITE W  Target Output : 480 Prs / 8</t>
+          <t>ADIPOWER 26 SL Target Output : 960 Prs / 8H (120 P</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>IH9387</t>
+          <t>JP8395</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>114.47</v>
-      </c>
-      <c r="D131" t="n">
-        <v>341.1336</v>
-      </c>
-      <c r="E131" s="2" t="n">
-        <v>226.6636</v>
+        <v>12</v>
       </c>
       <c r="F131" t="n">
-        <v>188.3933</v>
-      </c>
-      <c r="G131" t="n">
-        <v>1416.3</v>
-      </c>
-      <c r="H131" s="2" t="n">
-        <v>1227.9067</v>
+        <v>25.5</v>
       </c>
       <c r="I131" t="n">
-        <v>62.4</v>
-      </c>
-      <c r="J131" t="n">
-        <v>1169.63</v>
-      </c>
-      <c r="K131" s="2" t="n">
-        <v>1107.23</v>
+        <v>24</v>
       </c>
       <c r="L131" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="M131" t="n">
-        <v>113.52</v>
-      </c>
-      <c r="N131" s="2" t="n">
-        <v>103.62</v>
+        <v>10</v>
       </c>
     </row>
     <row r="132">
@@ -5972,44 +5674,44 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>KK2523</t>
+          <t>IH9387</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>118.64</v>
+        <v>9.5</v>
       </c>
       <c r="D132" t="n">
-        <v>215.1805</v>
-      </c>
-      <c r="E132" s="2" t="n">
-        <v>96.54049999999999</v>
+        <v>11.37</v>
+      </c>
+      <c r="E132" s="4" t="n">
+        <v>1.87</v>
       </c>
       <c r="F132" t="n">
-        <v>176.2933</v>
+        <v>23</v>
       </c>
       <c r="G132" t="n">
-        <v>1572.5</v>
-      </c>
-      <c r="H132" s="2" t="n">
-        <v>1396.2067</v>
+        <v>47.21</v>
+      </c>
+      <c r="H132" s="4" t="n">
+        <v>24.21</v>
       </c>
       <c r="I132" t="n">
-        <v>62.4</v>
+        <v>23.5</v>
       </c>
       <c r="J132" t="n">
-        <v>1180.63</v>
-      </c>
-      <c r="K132" s="2" t="n">
-        <v>1118.23</v>
+        <v>38.99</v>
+      </c>
+      <c r="K132" s="4" t="n">
+        <v>15.49</v>
       </c>
       <c r="L132" t="n">
-        <v>9.9</v>
+        <v>2</v>
       </c>
       <c r="M132" t="n">
-        <v>113.52</v>
-      </c>
-      <c r="N132" s="2" t="n">
-        <v>103.62</v>
+        <v>3.78</v>
+      </c>
+      <c r="N132" s="4" t="n">
+        <v>1.78</v>
       </c>
     </row>
     <row r="133">
@@ -6020,44 +5722,44 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>KK2573</t>
+          <t>KK2523</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>113.39</v>
+        <v>11.5</v>
       </c>
       <c r="D133" t="n">
-        <v>351.8222</v>
-      </c>
-      <c r="E133" s="2" t="n">
-        <v>238.4322</v>
+        <v>7.17</v>
+      </c>
+      <c r="E133" s="4" t="n">
+        <v>-4.33</v>
       </c>
       <c r="F133" t="n">
-        <v>188.3933</v>
+        <v>26</v>
       </c>
       <c r="G133" t="n">
-        <v>1436.1</v>
-      </c>
-      <c r="H133" s="2" t="n">
-        <v>1247.7067</v>
+        <v>52.42</v>
+      </c>
+      <c r="H133" s="4" t="n">
+        <v>26.42</v>
       </c>
       <c r="I133" t="n">
-        <v>62.4</v>
+        <v>23.5</v>
       </c>
       <c r="J133" t="n">
-        <v>1191.63</v>
-      </c>
-      <c r="K133" s="2" t="n">
-        <v>1129.23</v>
+        <v>39.35</v>
+      </c>
+      <c r="K133" s="4" t="n">
+        <v>15.85</v>
       </c>
       <c r="L133" t="n">
-        <v>9.9</v>
+        <v>2</v>
       </c>
       <c r="M133" t="n">
-        <v>93.5</v>
-      </c>
-      <c r="N133" s="2" t="n">
-        <v>83.59999999999999</v>
+        <v>3.78</v>
+      </c>
+      <c r="N133" s="4" t="n">
+        <v>1.78</v>
       </c>
     </row>
     <row r="134">
@@ -6068,320 +5770,299 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>KK2575</t>
+          <t>KK2573</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>118.64</v>
+        <v>10</v>
       </c>
       <c r="D134" t="n">
-        <v>229.1911</v>
-      </c>
-      <c r="E134" s="2" t="n">
-        <v>110.5511</v>
+        <v>11.73</v>
+      </c>
+      <c r="E134" s="4" t="n">
+        <v>1.73</v>
       </c>
       <c r="F134" t="n">
-        <v>176.2933</v>
+        <v>23.5</v>
       </c>
       <c r="G134" t="n">
-        <v>1572.5</v>
-      </c>
-      <c r="H134" s="2" t="n">
-        <v>1396.2067</v>
+        <v>47.87</v>
+      </c>
+      <c r="H134" s="4" t="n">
+        <v>24.37</v>
       </c>
       <c r="I134" t="n">
-        <v>62.4</v>
+        <v>23.5</v>
       </c>
       <c r="J134" t="n">
-        <v>1180.63</v>
-      </c>
-      <c r="K134" s="2" t="n">
-        <v>1118.23</v>
+        <v>39.72</v>
+      </c>
+      <c r="K134" s="4" t="n">
+        <v>16.22</v>
       </c>
       <c r="L134" t="n">
-        <v>9.9</v>
+        <v>2</v>
       </c>
       <c r="M134" t="n">
-        <v>113.52</v>
-      </c>
-      <c r="N134" s="2" t="n">
-        <v>103.62</v>
+        <v>3.12</v>
+      </c>
+      <c r="N134" s="4" t="n">
+        <v>1.12</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>W/ ADIPOWER 26 SL BOA Target Output : 480 Prs / 8H</t>
+          <t>TAEKWONDO MEI ELITE W  Target Output : 480 Prs / 8</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>JS4140</t>
-        </is>
+          <t>KK2575</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>12</v>
       </c>
       <c r="D135" t="n">
-        <v>283.0558</v>
+        <v>7.64</v>
+      </c>
+      <c r="E135" s="4" t="n">
+        <v>-4.36</v>
+      </c>
+      <c r="F135" t="n">
+        <v>26</v>
       </c>
       <c r="G135" t="n">
-        <v>1285.13</v>
+        <v>52.42</v>
+      </c>
+      <c r="H135" s="4" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="I135" t="n">
+        <v>23.5</v>
       </c>
       <c r="J135" t="n">
-        <v>1100.11</v>
+        <v>39.35</v>
+      </c>
+      <c r="K135" s="4" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="L135" t="n">
+        <v>2</v>
+      </c>
+      <c r="M135" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="N135" s="4" t="n">
+        <v>1.78</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">W/S2G 26 LEATHER Target Output : 480 Prs / 8H (60 </t>
+          <t>W/ ADIPOWER 26 SL BOA Target Output : 960 Prs / 8H</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>HP7087</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>227.2921</v>
-      </c>
-      <c r="G136" t="n">
-        <v>1665.03</v>
-      </c>
-      <c r="J136" t="n">
-        <v>906.4</v>
+          <t>JS4140</t>
+        </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">W/S2G 26 BOA Target Output : 480 Prs / 8H (60 Prs </t>
+          <t xml:space="preserve">W/S2G 26 LEATHER Target Output : 480 Prs / 8H (60 </t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>JR1887</t>
-        </is>
-      </c>
-      <c r="C137" t="n">
-        <v>116.48</v>
+          <t>HP7087</t>
+        </is>
       </c>
       <c r="D137" t="n">
-        <v>236.36</v>
-      </c>
-      <c r="E137" s="2" t="n">
-        <v>119.88</v>
-      </c>
-      <c r="F137" t="n">
-        <v>190.8133</v>
+        <v>7.58</v>
       </c>
       <c r="G137" t="n">
-        <v>1481.74</v>
-      </c>
-      <c r="H137" s="2" t="n">
-        <v>1290.9267</v>
-      </c>
-      <c r="I137" t="n">
-        <v>45.6</v>
+        <v>55.5</v>
       </c>
       <c r="J137" t="n">
-        <v>957.88</v>
-      </c>
-      <c r="K137" s="2" t="n">
-        <v>912.28</v>
-      </c>
-      <c r="L137" t="n">
-        <v>26.05</v>
+        <v>30.21</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">W/S2G 26 TEX Target Output : 480 Prs / 8H (60 Prs </t>
+          <t xml:space="preserve">W/S2G 26 BOA Target Output : 480 Prs / 8H (60 Prs </t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>KI1128</t>
+          <t>JR1887</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>88.03</v>
+        <v>8</v>
       </c>
       <c r="D138" t="n">
-        <v>249.1272</v>
-      </c>
-      <c r="E138" s="2" t="n">
-        <v>161.0972</v>
+        <v>7.88</v>
+      </c>
+      <c r="E138" s="4" t="n">
+        <v>-0.12</v>
       </c>
       <c r="F138" t="n">
-        <v>183.9933</v>
+        <v>26</v>
       </c>
       <c r="G138" t="n">
-        <v>1295.95</v>
-      </c>
-      <c r="H138" s="2" t="n">
-        <v>1111.9567</v>
+        <v>49.39</v>
+      </c>
+      <c r="H138" s="4" t="n">
+        <v>23.39</v>
       </c>
       <c r="I138" t="n">
-        <v>50.1</v>
+        <v>21</v>
       </c>
       <c r="J138" t="n">
-        <v>924.319</v>
-      </c>
-      <c r="K138" s="2" t="n">
-        <v>874.2190000000001</v>
+        <v>31.93</v>
+      </c>
+      <c r="K138" s="4" t="n">
+        <v>10.93</v>
       </c>
       <c r="L138" t="n">
-        <v>26.05</v>
-      </c>
-      <c r="M138" t="n">
-        <v>456.72</v>
-      </c>
-      <c r="N138" s="2" t="n">
-        <v>430.67</v>
+        <v>9</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>W/CODECHAOS 27 Target Output : 480 Prs / 8H (60 Pr</t>
+          <t xml:space="preserve">W/S2G 26 TEX Target Output : 480 Prs / 8H (60 Prs </t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>KI1388</t>
-        </is>
+          <t>KI1128</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>9.5</v>
       </c>
       <c r="D139" t="n">
-        <v>243.2455</v>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="E139" s="4" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="F139" t="n">
+        <v>23</v>
       </c>
       <c r="G139" t="n">
-        <v>939.917</v>
+        <v>43.2</v>
+      </c>
+      <c r="H139" s="4" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="I139" t="n">
+        <v>20</v>
       </c>
       <c r="J139" t="n">
-        <v>1015.52</v>
+        <v>30.81</v>
+      </c>
+      <c r="K139" s="4" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="L139" t="n">
+        <v>9</v>
       </c>
       <c r="M139" t="n">
-        <v>663.3</v>
+        <v>15.22</v>
+      </c>
+      <c r="N139" s="4" t="n">
+        <v>6.22</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>W/ GAZELLE GOLF Target Output : 480 Prs / 8H 60 Pr</t>
+          <t>W/CODECHAOS 27 Target Output : 960 Prs / 8H (120 P</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>KH8402</t>
+          <t>KI1388</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>152.8116</v>
+        <v>7.59</v>
       </c>
       <c r="G140" t="n">
-        <v>1041.12</v>
+        <v>31.33</v>
       </c>
       <c r="J140" t="n">
-        <v>922.3896</v>
+        <v>33.85</v>
       </c>
       <c r="M140" t="n">
-        <v>649.5133</v>
+        <v>22.11</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">GHOST MOTO LOW W Target Output : 480 Prs / 8H (60 </t>
+          <t>W GAZELLE GOLF Target Output : 960 Prs / 8H (120 P</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>KI4565</t>
-        </is>
-      </c>
-      <c r="C141" t="n">
-        <v>112.33</v>
-      </c>
-      <c r="D141" t="n">
-        <v>639.9009</v>
-      </c>
-      <c r="E141" s="2" t="n">
-        <v>527.5709000000001</v>
-      </c>
-      <c r="F141" t="n">
-        <v>112.33</v>
-      </c>
-      <c r="G141" t="n">
-        <v>1524.28</v>
-      </c>
-      <c r="H141" s="2" t="n">
-        <v>1411.95</v>
-      </c>
-      <c r="I141" t="n">
-        <v>88.09999999999999</v>
-      </c>
-      <c r="J141" t="n">
-        <v>1490.94</v>
-      </c>
-      <c r="K141" s="2" t="n">
-        <v>1402.84</v>
-      </c>
-      <c r="L141" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="M141" t="n">
-        <v>161.37</v>
-      </c>
-      <c r="N141" s="2" t="n">
-        <v>151.47</v>
+          <t>KH8402</t>
+        </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>TOKYO W MJ Target Output : 960 Prs / 8H (120 Prs /</t>
+          <t xml:space="preserve">GHOST MOTO LOW W Target Output : 480 Prs / 8H (60 </t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>KH5551</t>
+          <t>KI4565</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>99.73</v>
+        <v>13</v>
       </c>
       <c r="D142" t="n">
-        <v>561.5337</v>
-      </c>
-      <c r="E142" s="2" t="n">
-        <v>461.8037</v>
+        <v>21.33</v>
+      </c>
+      <c r="E142" s="4" t="n">
+        <v>8.33</v>
       </c>
       <c r="F142" t="n">
-        <v>157.3</v>
+        <v>29</v>
       </c>
       <c r="G142" t="n">
-        <v>1443.14</v>
-      </c>
-      <c r="H142" s="2" t="n">
-        <v>1285.84</v>
+        <v>50.81</v>
+      </c>
+      <c r="H142" s="4" t="n">
+        <v>21.81</v>
       </c>
       <c r="I142" t="n">
-        <v>46.6</v>
+        <v>28</v>
       </c>
       <c r="J142" t="n">
-        <v>1000.12</v>
-      </c>
-      <c r="K142" s="2" t="n">
-        <v>953.52</v>
+        <v>49.7</v>
+      </c>
+      <c r="K142" s="4" t="n">
+        <v>21.7</v>
       </c>
       <c r="L142" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="M142" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N142" s="2" t="n">
-        <v>18.42</v>
+        <v>5.38</v>
+      </c>
+      <c r="N142" s="4" t="n">
+        <v>2.38</v>
       </c>
     </row>
     <row r="143">
@@ -6392,44 +6073,20 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>KI3025</t>
+          <t>KH5551</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>102.51</v>
-      </c>
-      <c r="D143" t="n">
-        <v>561.5337</v>
-      </c>
-      <c r="E143" s="2" t="n">
-        <v>459.0237</v>
+        <v>10.5</v>
       </c>
       <c r="F143" t="n">
-        <v>157.3</v>
-      </c>
-      <c r="G143" t="n">
-        <v>1443.14</v>
-      </c>
-      <c r="H143" s="2" t="n">
-        <v>1285.84</v>
+        <v>19.6</v>
       </c>
       <c r="I143" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="J143" t="n">
-        <v>1000.12</v>
-      </c>
-      <c r="K143" s="2" t="n">
-        <v>953.52</v>
+        <v>21</v>
       </c>
       <c r="L143" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M143" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N143" s="2" t="n">
-        <v>18.42</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="144">
@@ -6440,44 +6097,20 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>KI4312</t>
+          <t>KI3025</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>102.91</v>
-      </c>
-      <c r="D144" t="n">
-        <v>761.7366</v>
-      </c>
-      <c r="E144" s="2" t="n">
-        <v>658.8266</v>
+        <v>10.5</v>
       </c>
       <c r="F144" t="n">
-        <v>157.3</v>
-      </c>
-      <c r="G144" t="n">
-        <v>1421.36</v>
-      </c>
-      <c r="H144" s="2" t="n">
-        <v>1264.06</v>
+        <v>20</v>
       </c>
       <c r="I144" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="J144" t="n">
-        <v>999.79</v>
-      </c>
-      <c r="K144" s="2" t="n">
-        <v>953.1900000000001</v>
+        <v>21</v>
       </c>
       <c r="L144" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M144" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N144" s="2" t="n">
-        <v>18.42</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="145">
@@ -6488,44 +6121,20 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>KI5323</t>
+          <t>KI4312</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>101.4</v>
-      </c>
-      <c r="D145" t="n">
-        <v>752.6457</v>
-      </c>
-      <c r="E145" s="2" t="n">
-        <v>651.2457000000001</v>
+        <v>10.5</v>
       </c>
       <c r="F145" t="n">
-        <v>157.3</v>
-      </c>
-      <c r="G145" t="n">
-        <v>1476.91</v>
-      </c>
-      <c r="H145" s="2" t="n">
-        <v>1319.61</v>
+        <v>19</v>
       </c>
       <c r="I145" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="J145" t="n">
-        <v>999.79</v>
-      </c>
-      <c r="K145" s="2" t="n">
-        <v>953.1900000000001</v>
+        <v>21.5</v>
       </c>
       <c r="L145" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M145" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N145" s="2" t="n">
-        <v>18.42</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="146">
@@ -6536,428 +6145,413 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>KJ5221</t>
+          <t>KI5323</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>100.72</v>
+        <v>10.5</v>
       </c>
       <c r="D146" t="n">
-        <v>560.3171</v>
-      </c>
-      <c r="E146" s="2" t="n">
-        <v>459.5971</v>
+        <v>25.09</v>
+      </c>
+      <c r="E146" s="4" t="n">
+        <v>14.59</v>
       </c>
       <c r="F146" t="n">
-        <v>157.3</v>
+        <v>20</v>
       </c>
       <c r="G146" t="n">
-        <v>1443.14</v>
-      </c>
-      <c r="H146" s="2" t="n">
-        <v>1285.84</v>
+        <v>49.23</v>
+      </c>
+      <c r="H146" s="4" t="n">
+        <v>29.23</v>
       </c>
       <c r="I146" t="n">
-        <v>46.6</v>
+        <v>21.5</v>
       </c>
       <c r="J146" t="n">
-        <v>1090.32</v>
-      </c>
-      <c r="K146" s="2" t="n">
-        <v>1043.72</v>
+        <v>33.33</v>
+      </c>
+      <c r="K146" s="4" t="n">
+        <v>11.83</v>
       </c>
       <c r="L146" t="n">
-        <v>4.9</v>
+        <v>0.5</v>
       </c>
       <c r="M146" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N146" s="2" t="n">
-        <v>18.42</v>
+        <v>0.78</v>
+      </c>
+      <c r="N146" s="4" t="n">
+        <v>0.28</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>TOKYO W  Target Output: 480 Prs / 8H (60 Prs / Hou</t>
+          <t>TOKYO W MJ Target Output : 960 Prs / 8H (120 Prs /</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>JI0182</t>
-        </is>
+          <t>KJ5221</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>10.5</v>
       </c>
       <c r="D147" t="n">
-        <v>178.7439</v>
+        <v>18.68</v>
+      </c>
+      <c r="E147" s="4" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="F147" t="n">
+        <v>20</v>
       </c>
       <c r="G147" t="n">
-        <v>939.13</v>
+        <v>48.1</v>
+      </c>
+      <c r="H147" s="4" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="I147" t="n">
+        <v>22.5</v>
       </c>
       <c r="J147" t="n">
-        <v>982.08</v>
+        <v>36.34</v>
+      </c>
+      <c r="K147" s="4" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="L147" t="n">
+        <v>0.5</v>
       </c>
       <c r="M147" t="n">
-        <v>23.32</v>
+        <v>0.78</v>
+      </c>
+      <c r="N147" s="4" t="n">
+        <v>0.28</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>TOKYO W  Target Output : 480 Prs / 8H (60 Prs / Ho</t>
+          <t>TOKYO W  Target Output: 960 Prs / 8H (120 Prs / Ho</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>KI4300</t>
-        </is>
-      </c>
-      <c r="C148" t="n">
-        <v>80.84</v>
-      </c>
-      <c r="D148" t="n">
-        <v>331.5695</v>
-      </c>
-      <c r="E148" s="2" t="n">
-        <v>250.7295</v>
-      </c>
-      <c r="F148" t="n">
-        <v>164.7067</v>
-      </c>
-      <c r="G148" t="n">
-        <v>1168.36</v>
-      </c>
-      <c r="H148" s="2" t="n">
-        <v>1003.6533</v>
-      </c>
-      <c r="I148" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="J148" t="n">
-        <v>1220.56</v>
-      </c>
-      <c r="K148" s="2" t="n">
-        <v>1167.96</v>
-      </c>
-      <c r="L148" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M148" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N148" s="2" t="n">
-        <v>18.42</v>
+          <t>JI0182</t>
+        </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>TOKYO W  Target Output : 480 Prs / 8H (60 Prs / Ho</t>
+          <t>TOKYO W  Target Output : 960 Prs / 8H (120 Prs / H</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>KK2765</t>
+          <t>KI4300</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>88.98</v>
-      </c>
-      <c r="D149" t="n">
-        <v>174.4085</v>
-      </c>
-      <c r="E149" s="2" t="n">
-        <v>85.4285</v>
+        <v>10</v>
       </c>
       <c r="F149" t="n">
-        <v>161.4067</v>
-      </c>
-      <c r="G149" t="n">
-        <v>1159.68</v>
-      </c>
-      <c r="H149" s="2" t="n">
-        <v>998.2732999999999</v>
+        <v>17</v>
       </c>
       <c r="I149" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="J149" t="n">
-        <v>1100.66</v>
-      </c>
-      <c r="K149" s="2" t="n">
-        <v>1048.06</v>
+        <v>24</v>
       </c>
       <c r="L149" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M149" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="N149" s="2" t="n">
-        <v>18.42</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>GAZELLE GOLF  Target Output : 480 Prs / 8H (60 Prs</t>
+          <t>TOKYO W  Target Output : 960 Prs / 8H (120 Prs / H</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>IH2267</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>336.5147</v>
-      </c>
-      <c r="G150" t="n">
-        <v>1140.59</v>
-      </c>
-      <c r="J150" t="n">
-        <v>885.5</v>
+          <t>KK2765</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F150" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="I150" t="n">
+        <v>23</v>
+      </c>
+      <c r="L150" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ADICHILL Target Output : 960 Prs / 8H (120 Prs / H</t>
+          <t xml:space="preserve">W/ GAZELLE GOLF Target Output : 960 Prs / 8H (120 </t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>KJ0835</t>
-        </is>
-      </c>
-      <c r="C151" t="n">
-        <v>85.37</v>
-      </c>
-      <c r="D151" t="n">
-        <v>306.3262</v>
-      </c>
-      <c r="E151" s="2" t="n">
-        <v>220.9562</v>
-      </c>
-      <c r="F151" t="n">
-        <v>203.72</v>
-      </c>
-      <c r="G151" t="n">
-        <v>906.73</v>
-      </c>
-      <c r="H151" s="2" t="n">
-        <v>703.01</v>
-      </c>
-      <c r="I151" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="J151" t="n">
-        <v>2045.45</v>
-      </c>
-      <c r="K151" s="2" t="n">
-        <v>2003.75</v>
-      </c>
-      <c r="L151" t="n">
-        <v>18.53</v>
-      </c>
-      <c r="M151" t="n">
-        <v>341.44</v>
-      </c>
-      <c r="N151" s="2" t="n">
-        <v>322.91</v>
+          <t>IH2267</t>
+        </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>MEGARIDE F50 Target Output : 960 Prs / 8H (120 Prs</t>
+          <t>ADICHILL Target Output : 960 Prs / 8H (120 Prs / H</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>KZ8772</t>
+          <t>KJ0835</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>86.58</v>
+        <v>20.5</v>
       </c>
       <c r="D152" t="n">
-        <v>144.541</v>
-      </c>
-      <c r="E152" s="2" t="n">
-        <v>57.961</v>
+        <v>10.21</v>
+      </c>
+      <c r="E152" s="4" t="n">
+        <v>-10.29</v>
       </c>
       <c r="F152" t="n">
-        <v>86.58</v>
+        <v>29</v>
       </c>
       <c r="G152" t="n">
-        <v>1245.2</v>
-      </c>
-      <c r="H152" s="2" t="n">
-        <v>1158.62</v>
+        <v>30.22</v>
+      </c>
+      <c r="H152" s="4" t="n">
+        <v>1.22</v>
       </c>
       <c r="I152" t="n">
-        <v>120.4</v>
+        <v>24</v>
       </c>
       <c r="J152" t="n">
-        <v>3313.09</v>
-      </c>
-      <c r="K152" s="2" t="n">
-        <v>3192.69</v>
+        <v>68.18000000000001</v>
+      </c>
+      <c r="K152" s="4" t="n">
+        <v>44.18</v>
       </c>
       <c r="L152" t="n">
-        <v>65.54000000000001</v>
+        <v>15</v>
       </c>
       <c r="M152" t="n">
-        <v>1185.8</v>
-      </c>
-      <c r="N152" s="2" t="n">
-        <v>1120.26</v>
+        <v>11.38</v>
+      </c>
+      <c r="N152" s="4" t="n">
+        <v>-3.62</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>KITH MEGARIDE F50 BLUE/ WHITE/ COCA COLA Target Ou</t>
+          <t>MEGARIDE F50 Target Output : 960 Prs / 8H (120 Prs</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>KK4660</t>
+          <t>KZ8772</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>83.28</v>
+        <v>12.5</v>
       </c>
       <c r="D153" t="n">
-        <v>144.541</v>
-      </c>
-      <c r="E153" s="2" t="n">
-        <v>61.261</v>
+        <v>4.82</v>
+      </c>
+      <c r="E153" s="4" t="n">
+        <v>-7.68</v>
       </c>
       <c r="F153" t="n">
-        <v>83.28</v>
+        <v>45.5</v>
       </c>
       <c r="G153" t="n">
-        <v>1188.33</v>
-      </c>
-      <c r="H153" s="2" t="n">
-        <v>1105.05</v>
+        <v>41.51</v>
+      </c>
+      <c r="H153" s="4" t="n">
+        <v>-3.99</v>
       </c>
       <c r="I153" t="n">
-        <v>123.9</v>
+        <v>73.5</v>
       </c>
       <c r="J153" t="n">
-        <v>3382.83</v>
-      </c>
-      <c r="K153" s="2" t="n">
-        <v>3258.93</v>
+        <v>110.44</v>
+      </c>
+      <c r="K153" s="4" t="n">
+        <v>36.94</v>
       </c>
       <c r="L153" t="n">
-        <v>65.54000000000001</v>
+        <v>42</v>
       </c>
       <c r="M153" t="n">
-        <v>1185.8</v>
-      </c>
-      <c r="N153" s="2" t="n">
-        <v>1120.26</v>
+        <v>39.53</v>
+      </c>
+      <c r="N153" s="4" t="n">
+        <v>-2.47</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>MEGARIDE F50 RAYQUAZA Target Output : 960 Prs / 8H</t>
+          <t>KITH MEGARIDE F50 BLUE/ WHITE/ COCA COLA Target Ou</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>KI5325</t>
+          <t>KK4660</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>106.38</v>
+        <v>12.5</v>
       </c>
       <c r="D154" t="n">
-        <v>132.9998</v>
-      </c>
-      <c r="E154" s="2" t="n">
-        <v>26.6198</v>
+        <v>4.82</v>
+      </c>
+      <c r="E154" s="4" t="n">
+        <v>-7.68</v>
       </c>
       <c r="F154" t="n">
-        <v>90.8233</v>
+        <v>43.5</v>
       </c>
       <c r="G154" t="n">
-        <v>1383.05</v>
-      </c>
-      <c r="H154" s="2" t="n">
-        <v>1292.2267</v>
+        <v>39.61</v>
+      </c>
+      <c r="H154" s="4" t="n">
+        <v>-3.89</v>
       </c>
       <c r="I154" t="n">
-        <v>115.9</v>
+        <v>75.5</v>
       </c>
       <c r="J154" t="n">
-        <v>3142.81</v>
-      </c>
-      <c r="K154" s="2" t="n">
-        <v>3026.91</v>
+        <v>112.76</v>
+      </c>
+      <c r="K154" s="4" t="n">
+        <v>37.26</v>
       </c>
       <c r="L154" t="n">
-        <v>65.54000000000001</v>
+        <v>42</v>
       </c>
       <c r="M154" t="n">
-        <v>1185.8</v>
-      </c>
-      <c r="N154" s="2" t="n">
-        <v>1120.26</v>
+        <v>39.53</v>
+      </c>
+      <c r="N154" s="4" t="n">
+        <v>-2.47</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
+          <t>MEGARIDE F50 RAYQUAZA Target Output : 960 Prs / 8H</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>KI5325</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="D155" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="E155" s="4" t="n">
+        <v>-10.07</v>
+      </c>
+      <c r="F155" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="G155" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="H155" s="4" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="I155" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="J155" t="n">
+        <v>104.76</v>
+      </c>
+      <c r="K155" s="4" t="n">
+        <v>37.26</v>
+      </c>
+      <c r="L155" t="n">
+        <v>42</v>
+      </c>
+      <c r="M155" t="n">
+        <v>39.53</v>
+      </c>
+      <c r="N155" s="4" t="n">
+        <v>-2.47</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
           <t>MEGARIDE F50 Target Output : 960 Prs / 8H (120 Prs</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="B156" t="inlineStr">
         <is>
           <t>JR4632</t>
         </is>
       </c>
-      <c r="C155" t="n">
-        <v>83.28</v>
-      </c>
-      <c r="D155" t="n">
-        <v>144.541</v>
-      </c>
-      <c r="E155" s="2" t="n">
-        <v>61.261</v>
-      </c>
-      <c r="F155" t="n">
-        <v>83.28</v>
-      </c>
-      <c r="G155" t="n">
-        <v>1188.33</v>
-      </c>
-      <c r="H155" s="2" t="n">
-        <v>1105.05</v>
-      </c>
-      <c r="I155" t="n">
-        <v>120.4</v>
-      </c>
-      <c r="J155" t="n">
-        <v>3306.27</v>
-      </c>
-      <c r="K155" s="2" t="n">
-        <v>3185.87</v>
-      </c>
-      <c r="L155" t="n">
-        <v>65.54000000000001</v>
-      </c>
-      <c r="M155" t="n">
-        <v>1185.8</v>
-      </c>
-      <c r="N155" s="2" t="n">
-        <v>1120.26</v>
+      <c r="C156" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="D156" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="E156" s="4" t="n">
+        <v>-7.68</v>
+      </c>
+      <c r="F156" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="G156" t="n">
+        <v>39.61</v>
+      </c>
+      <c r="H156" s="4" t="n">
+        <v>-3.89</v>
+      </c>
+      <c r="I156" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="J156" t="n">
+        <v>110.21</v>
+      </c>
+      <c r="K156" s="4" t="n">
+        <v>36.71</v>
+      </c>
+      <c r="L156" t="n">
+        <v>42</v>
+      </c>
+      <c r="M156" t="n">
+        <v>39.53</v>
+      </c>
+      <c r="N156" s="4" t="n">
+        <v>-2.47</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>